--- a/Практические работы/exel/1.xlsx
+++ b/Практические работы/exel/1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="7" activeTab="12"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="10" activeTab="14"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,20 @@
     <sheet name="Изменение биоритмов человека" sheetId="9" r:id="rId10"/>
     <sheet name="Ну и погода" sheetId="11" r:id="rId11"/>
     <sheet name="Магазин" sheetId="12" r:id="rId12"/>
-    <sheet name="Лист4" sheetId="13" r:id="rId13"/>
+    <sheet name="Зарплата" sheetId="13" r:id="rId13"/>
+    <sheet name="Сортировка" sheetId="14" r:id="rId14"/>
+    <sheet name="Лист3" sheetId="15" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">Лист4!$D$1:$D$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">Зарплата!$A$1:$H$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">Сортировка!$A$44:$H$62</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="166">
   <si>
     <t>Учащиеся</t>
   </si>
@@ -474,17 +477,72 @@
   <si>
     <t>Гл. бухгалтер</t>
   </si>
+  <si>
+    <t xml:space="preserve"> Сортировка Отдел, Начислено по убыванию.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Сортировка Отдел, Ф.И.О. по возрастанию.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Сортировка Отдел, Должность, Ф.И.О.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Сортировка Отдел, Должность, Таб. Номер.</t>
+  </si>
+  <si>
+    <t>Склад</t>
+  </si>
+  <si>
+    <t>Продукты</t>
+  </si>
+  <si>
+    <t>Срок реализации</t>
+  </si>
+  <si>
+    <t>Истек</t>
+  </si>
+  <si>
+    <t>Количество</t>
+  </si>
+  <si>
+    <t>Марс</t>
+  </si>
+  <si>
+    <t>Сникерс</t>
+  </si>
+  <si>
+    <t>Мармелад</t>
+  </si>
+  <si>
+    <t>Рондо</t>
+  </si>
+  <si>
+    <t>Твикс</t>
+  </si>
+  <si>
+    <t>Пастила</t>
+  </si>
+  <si>
+    <t>Баунти</t>
+  </si>
+  <si>
+    <t>Шок</t>
+  </si>
+  <si>
+    <t>Зефир</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="166" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0\ &quot;₽&quot;"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -549,7 +607,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -666,12 +724,169 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -817,24 +1032,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -877,6 +1074,99 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -946,7 +1236,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1081,9 +1370,7 @@
               </c:spPr>
             </c:leaderLines>
             <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-              </c:ext>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
             </c:extLst>
           </c:dLbls>
           <c:cat>
@@ -1143,7 +1430,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1806,11 +2092,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="245563136"/>
-        <c:axId val="245550624"/>
+        <c:axId val="1078112400"/>
+        <c:axId val="1078103696"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="245563136"/>
+        <c:axId val="1078112400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1853,7 +2139,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="245550624"/>
+        <c:crossAx val="1078103696"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1861,7 +2147,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="245550624"/>
+        <c:axId val="1078103696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1912,7 +2198,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="245563136"/>
+        <c:crossAx val="1078112400"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2236,11 +2522,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="245560416"/>
-        <c:axId val="245560960"/>
+        <c:axId val="1078098256"/>
+        <c:axId val="1078099888"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="245560416"/>
+        <c:axId val="1078098256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2297,12 +2583,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="245560960"/>
+        <c:crossAx val="1078099888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="245560960"/>
+        <c:axId val="1078099888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2359,7 +2645,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="245560416"/>
+        <c:crossAx val="1078098256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2501,100 +2787,100 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>46146</c:v>
+                  <c:v>46149</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46147</c:v>
+                  <c:v>46150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46148</c:v>
+                  <c:v>46151</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46149</c:v>
+                  <c:v>46152</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46150</c:v>
+                  <c:v>46153</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46151</c:v>
+                  <c:v>46154</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46152</c:v>
+                  <c:v>46155</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46153</c:v>
+                  <c:v>46156</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46154</c:v>
+                  <c:v>46157</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46155</c:v>
+                  <c:v>46158</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46156</c:v>
+                  <c:v>46159</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46157</c:v>
+                  <c:v>46160</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46158</c:v>
+                  <c:v>46161</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46159</c:v>
+                  <c:v>46162</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46160</c:v>
+                  <c:v>46163</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46161</c:v>
+                  <c:v>46164</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46162</c:v>
+                  <c:v>46165</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46163</c:v>
+                  <c:v>46166</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46164</c:v>
+                  <c:v>46167</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46165</c:v>
+                  <c:v>46168</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46166</c:v>
+                  <c:v>46169</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46167</c:v>
+                  <c:v>46170</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46168</c:v>
+                  <c:v>46171</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46169</c:v>
+                  <c:v>46172</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46170</c:v>
+                  <c:v>46173</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46171</c:v>
+                  <c:v>46174</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46172</c:v>
+                  <c:v>46175</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46173</c:v>
+                  <c:v>46176</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46174</c:v>
+                  <c:v>46177</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46175</c:v>
+                  <c:v>46178</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46176</c:v>
+                  <c:v>46179</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46177</c:v>
+                  <c:v>46180</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2606,100 +2892,100 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>-0.64591161429061494</c:v>
+                  <c:v>-1.310530984569209E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.4551254558414477</c:v>
+                  <c:v>0.21490838694551764</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-0.24043055587956047</c:v>
+                  <c:v>0.43163247335348037</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-1.310530984569209E-2</c:v>
+                  <c:v>0.62568195630383827</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.21490838694551764</c:v>
+                  <c:v>0.78686298952995681</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.43163247335348037</c:v>
+                  <c:v>0.90670837874215282</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.62568195630383827</c:v>
+                  <c:v>0.97892238197578552</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.78686298952995681</c:v>
+                  <c:v>0.99971143876226276</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.90670837874215282</c:v>
+                  <c:v>0.96798345421102339</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.97892238197578552</c:v>
+                  <c:v>0.88540516915474554</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.99971143876226276</c:v>
+                  <c:v>0.75631460258748828</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.96798345421102339</c:v>
+                  <c:v>0.58749316598398182</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.88540516915474554</c:v>
+                  <c:v>0.38780942082950592</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.75631460258748828</c:v>
+                  <c:v>0.16775319358317134</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.58749316598398182</c:v>
+                  <c:v>-6.1115477996687456E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.38780942082950592</c:v>
+                  <c:v>-0.28677361905753684</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.16775319358317134</c:v>
+                  <c:v>-0.49736691098015484</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-6.1115477996687456E-2</c:v>
+                  <c:v>-0.68183242481331585</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-0.28677361905753684</c:v>
+                  <c:v>-0.83047978127666067</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-0.49736691098015484</c:v>
+                  <c:v>-0.93550020769467779</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-0.68183242481331585</c:v>
+                  <c:v>-0.99137675001463232</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-0.83047978127666067</c:v>
+                  <c:v>-0.99517409053305272</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-0.93550020769467779</c:v>
+                  <c:v>-0.94669274659870006</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-0.99137675001463232</c:v>
+                  <c:v>-0.84847954987272134</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-0.99517409053305272</c:v>
+                  <c:v>-0.7056938556559238</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-0.94669274659870006</c:v>
+                  <c:v>-0.52583651060970782</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-0.84847954987272134</c:v>
+                  <c:v>-0.31835581676799474</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-0.7056938556559238</c:v>
+                  <c:v>-9.4151191461850053E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-0.52583651060970782</c:v>
+                  <c:v>0.13499940307505373</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-0.31835581676799474</c:v>
+                  <c:v>0.35705818195524541</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-9.4151191461850053E-2</c:v>
+                  <c:v>0.56035990897729226</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.13499940307505373</c:v>
+                  <c:v>0.73422469713462291</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2739,100 +3025,100 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>46146</c:v>
+                  <c:v>46149</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46147</c:v>
+                  <c:v>46150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46148</c:v>
+                  <c:v>46151</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46149</c:v>
+                  <c:v>46152</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46150</c:v>
+                  <c:v>46153</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46151</c:v>
+                  <c:v>46154</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46152</c:v>
+                  <c:v>46155</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46153</c:v>
+                  <c:v>46156</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46154</c:v>
+                  <c:v>46157</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46155</c:v>
+                  <c:v>46158</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46156</c:v>
+                  <c:v>46159</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46157</c:v>
+                  <c:v>46160</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46158</c:v>
+                  <c:v>46161</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46159</c:v>
+                  <c:v>46162</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46160</c:v>
+                  <c:v>46163</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46161</c:v>
+                  <c:v>46164</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46162</c:v>
+                  <c:v>46165</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46163</c:v>
+                  <c:v>46166</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46164</c:v>
+                  <c:v>46167</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46165</c:v>
+                  <c:v>46168</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46166</c:v>
+                  <c:v>46169</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46167</c:v>
+                  <c:v>46170</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46168</c:v>
+                  <c:v>46171</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46169</c:v>
+                  <c:v>46172</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46170</c:v>
+                  <c:v>46173</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46171</c:v>
+                  <c:v>46174</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46172</c:v>
+                  <c:v>46175</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46173</c:v>
+                  <c:v>46176</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46174</c:v>
+                  <c:v>46177</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46175</c:v>
+                  <c:v>46178</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46176</c:v>
+                  <c:v>46179</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46177</c:v>
+                  <c:v>46180</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2844,100 +3130,100 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>-0.31530397242525959</c:v>
+                  <c:v>-0.77507420075117528</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.48770776003281746</c:v>
+                  <c:v>-0.87983632219958507</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-0.64279958025437878</c:v>
+                  <c:v>-0.95336724545588347</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-0.77507420075117528</c:v>
+                  <c:v>-0.99305687273331744</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-0.87983632219958507</c:v>
+                  <c:v>-0.99749635719846896</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-0.95336724545588347</c:v>
+                  <c:v>-0.96652811224653945</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-0.99305687273331744</c:v>
+                  <c:v>-0.90125140528845571</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-0.99749635719846896</c:v>
+                  <c:v>-0.80398333749508066</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-0.96652811224653945</c:v>
+                  <c:v>-0.678176594583485</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-0.90125140528845571</c:v>
+                  <c:v>-0.52829688821080356</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-0.80398333749508066</c:v>
+                  <c:v>-0.35966443839709628</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-0.678176594583485</c:v>
+                  <c:v>-0.17826512380018317</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-0.52829688821080356</c:v>
+                  <c:v>9.4619966302357094E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-0.35966443839709628</c:v>
+                  <c:v>0.19685324834894555</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-0.17826512380018317</c:v>
+                  <c:v>0.37725687900811905</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>9.4619966302357094E-3</c:v>
+                  <c:v>0.54426917305272549</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.19685324834894555</c:v>
+                  <c:v>0.69196176184658986</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.37725687900811905</c:v>
+                  <c:v>0.81509206060802042</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.54426917305272549</c:v>
+                  <c:v>0.90928936234788582</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.69196176184658986</c:v>
+                  <c:v>0.97120998310409967</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.81509206060802042</c:v>
+                  <c:v>0.99865595135611995</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.90928936234788582</c:v>
+                  <c:v>0.990653028540603</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.97120998310409967</c:v>
+                  <c:v>0.94748529120921043</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.99865595135611995</c:v>
+                  <c:v>0.87068504727742035</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.990653028540603</c:v>
+                  <c:v>0.76297844430097561</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.94748529120921043</c:v>
+                  <c:v>0.62818870050726971</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.87068504727742035</c:v>
+                  <c:v>0.47110039354450584</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.76297844430097561</c:v>
+                  <c:v>0.29728962424790423</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.62818870050726971</c:v>
+                  <c:v>0.11292608400667616</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.47110039354450584</c:v>
+                  <c:v>-7.5445948291718232E-2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.29728962424790423</c:v>
+                  <c:v>-0.26113990592504333</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.11292608400667616</c:v>
+                  <c:v>-0.43756428471508418</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2977,100 +3263,100 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>46146</c:v>
+                  <c:v>46149</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46147</c:v>
+                  <c:v>46150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46148</c:v>
+                  <c:v>46151</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46149</c:v>
+                  <c:v>46152</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46150</c:v>
+                  <c:v>46153</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46151</c:v>
+                  <c:v>46154</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46152</c:v>
+                  <c:v>46155</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46153</c:v>
+                  <c:v>46156</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46154</c:v>
+                  <c:v>46157</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46155</c:v>
+                  <c:v>46158</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46156</c:v>
+                  <c:v>46159</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46157</c:v>
+                  <c:v>46160</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46158</c:v>
+                  <c:v>46161</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46159</c:v>
+                  <c:v>46162</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46160</c:v>
+                  <c:v>46163</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46161</c:v>
+                  <c:v>46164</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46162</c:v>
+                  <c:v>46165</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46163</c:v>
+                  <c:v>46166</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46164</c:v>
+                  <c:v>46167</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46165</c:v>
+                  <c:v>46168</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46166</c:v>
+                  <c:v>46169</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46167</c:v>
+                  <c:v>46170</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46168</c:v>
+                  <c:v>46171</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46169</c:v>
+                  <c:v>46172</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46170</c:v>
+                  <c:v>46173</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46171</c:v>
+                  <c:v>46174</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46172</c:v>
+                  <c:v>46175</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46173</c:v>
+                  <c:v>46176</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46174</c:v>
+                  <c:v>46177</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46175</c:v>
+                  <c:v>46178</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46176</c:v>
+                  <c:v>46179</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46177</c:v>
+                  <c:v>46180</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3082,100 +3368,100 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>0.69973262889059451</c:v>
+                  <c:v>0.29048494528460334</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.57689860744021515</c:v>
+                  <c:v>0.13423067729996951</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.43930971260255341</c:v>
+                  <c:v>-2.5456701150971761E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.29048494528460334</c:v>
+                  <c:v>-0.18449299395978283</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.13423067729996951</c:v>
+                  <c:v>-0.33881065730293269</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-2.5456701150971761E-2</c:v>
+                  <c:v>-0.48446283196870732</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-0.18449299395978283</c:v>
+                  <c:v>-0.61772428900342335</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-0.33881065730293269</c:v>
+                  <c:v>-0.7351867069089989</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-0.48446283196870732</c:v>
+                  <c:v>-0.83384584355066604</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-0.61772428900342335</c:v>
+                  <c:v>-0.91117837325136475</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-0.7351867069089989</c:v>
+                  <c:v>-0.96520642386727651</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-0.83384584355066604</c:v>
+                  <c:v>-0.99454816324394801</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-0.91117837325136475</c:v>
+                  <c:v>-0.99845314122621887</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-0.96520642386727651</c:v>
+                  <c:v>-0.97682148332147356</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-0.99454816324394801</c:v>
+                  <c:v>-0.93020644510950601</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-0.99845314122621887</c:v>
+                  <c:v>-0.85980026206697457</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-0.97682148332147356</c:v>
+                  <c:v>-0.76740365671946287</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-0.93020644510950601</c:v>
+                  <c:v>-0.65537978299965449</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-0.85980026206697457</c:v>
+                  <c:v>-0.52659378575583204</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-0.76740365671946287</c:v>
+                  <c:v>-0.38433952123739623</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-0.65537978299965449</c:v>
+                  <c:v>-0.2322553127713233</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-0.52659378575583204</c:v>
+                  <c:v>-7.4230896288972642E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-0.38433952123739623</c:v>
+                  <c:v>8.5692064343151839E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-0.2322553127713233</c:v>
+                  <c:v>0.24342334771453841</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-7.4230896288972642E-2</c:v>
+                  <c:v>0.39492878718768215</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>8.5692064343151839E-2</c:v>
+                  <c:v>0.53633344954541018</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.24342334771453841</c:v>
+                  <c:v>0.66402074105397657</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.39492878718768215</c:v>
+                  <c:v>0.77472490617723277</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.53633344954541018</c:v>
+                  <c:v>0.86561455319766278</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.66402074105397657</c:v>
+                  <c:v>0.93436507044745232</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.77472490617723277</c:v>
+                  <c:v>0.97921808103946584</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.86561455319766278</c:v>
+                  <c:v>0.99902641546557536</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3191,11 +3477,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="245564224"/>
-        <c:axId val="245551712"/>
+        <c:axId val="1078106960"/>
+        <c:axId val="1078109680"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="245564224"/>
+        <c:axId val="1078106960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3238,14 +3524,14 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="245551712"/>
+        <c:crossAx val="1078109680"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="245551712"/>
+        <c:axId val="1078109680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3296,7 +3582,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="245564224"/>
+        <c:crossAx val="1078106960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8279,11 +8565,11 @@
       <c r="B1" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="60" t="s">
+      <c r="D1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="37">
@@ -8305,7 +8591,7 @@
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="37">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="B3" s="38" t="s">
         <v>55</v>
@@ -8323,7 +8609,7 @@
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="35">
         <f ca="1">A3-A2</f>
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="B4" s="38" t="s">
         <v>56</v>
@@ -8339,13 +8625,13 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
     </row>
     <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
@@ -8367,705 +8653,705 @@
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="40">
         <f ca="1">A3</f>
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="B7" s="41">
         <f ca="1">A4</f>
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="C7" s="42">
         <f ca="1">SIN((2*PI()*A7-B7)/$D$2)</f>
-        <v>-0.64591161429061494</v>
+        <v>-1.310530984569209E-2</v>
       </c>
       <c r="D7" s="42">
         <f ca="1">SIN((2*PI()*A7-B7)/$D$3)</f>
-        <v>-0.31530397242525959</v>
+        <v>-0.77507420075117528</v>
       </c>
       <c r="E7" s="42">
         <f ca="1">SIN((2*PI()*A7-B7)/$D$4)</f>
-        <v>0.69973262889059451</v>
+        <v>0.29048494528460334</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="40">
         <f ca="1">A7+1</f>
-        <v>46147</v>
+        <v>46150</v>
       </c>
       <c r="B8" s="41">
         <f ca="1">B7+1</f>
-        <v>6426</v>
+        <v>6429</v>
       </c>
       <c r="C8" s="42">
         <f ca="1">SIN((2*PI()*A8-B8)/$D$2)</f>
-        <v>-0.4551254558414477</v>
+        <v>0.21490838694551764</v>
       </c>
       <c r="D8" s="42">
         <f t="shared" ref="D8:D38" ca="1" si="0">SIN((2*PI()*A8-B8)/$D$3)</f>
-        <v>-0.48770776003281746</v>
+        <v>-0.87983632219958507</v>
       </c>
       <c r="E8" s="42">
         <f t="shared" ref="E8:E38" ca="1" si="1">SIN((2*PI()*A8-B8)/$D$4)</f>
-        <v>0.57689860744021515</v>
+        <v>0.13423067729996951</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="40">
         <f t="shared" ref="A9:A38" ca="1" si="2">A8+1</f>
-        <v>46148</v>
+        <v>46151</v>
       </c>
       <c r="B9" s="41">
         <f t="shared" ref="B9:B38" ca="1" si="3">B8+1</f>
-        <v>6427</v>
+        <v>6430</v>
       </c>
       <c r="C9" s="42">
         <f t="shared" ref="C9:C38" ca="1" si="4">SIN((2*PI()*A9-B9)/$D$2)</f>
-        <v>-0.24043055587956047</v>
+        <v>0.43163247335348037</v>
       </c>
       <c r="D9" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.64279958025437878</v>
+        <v>-0.95336724545588347</v>
       </c>
       <c r="E9" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>0.43930971260255341</v>
+        <v>-2.5456701150971761E-2</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46149</v>
+        <v>46152</v>
       </c>
       <c r="B10" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6428</v>
+        <v>6431</v>
       </c>
       <c r="C10" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-1.310530984569209E-2</v>
+        <v>0.62568195630383827</v>
       </c>
       <c r="D10" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.77507420075117528</v>
+        <v>-0.99305687273331744</v>
       </c>
       <c r="E10" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>0.29048494528460334</v>
+        <v>-0.18449299395978283</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B11" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6429</v>
+        <v>6432</v>
       </c>
       <c r="C11" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.21490838694551764</v>
+        <v>0.78686298952995681</v>
       </c>
       <c r="D11" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.87983632219958507</v>
+        <v>-0.99749635719846896</v>
       </c>
       <c r="E11" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>0.13423067729996951</v>
+        <v>-0.33881065730293269</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46151</v>
+        <v>46154</v>
       </c>
       <c r="B12" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6430</v>
+        <v>6433</v>
       </c>
       <c r="C12" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.43163247335348037</v>
+        <v>0.90670837874215282</v>
       </c>
       <c r="D12" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.95336724545588347</v>
+        <v>-0.96652811224653945</v>
       </c>
       <c r="E12" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-2.5456701150971761E-2</v>
+        <v>-0.48446283196870732</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46152</v>
+        <v>46155</v>
       </c>
       <c r="B13" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6431</v>
+        <v>6434</v>
       </c>
       <c r="C13" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.62568195630383827</v>
+        <v>0.97892238197578552</v>
       </c>
       <c r="D13" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.99305687273331744</v>
+        <v>-0.90125140528845571</v>
       </c>
       <c r="E13" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.18449299395978283</v>
+        <v>-0.61772428900342335</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="B14" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6432</v>
+        <v>6435</v>
       </c>
       <c r="C14" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.78686298952995681</v>
+        <v>0.99971143876226276</v>
       </c>
       <c r="D14" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.99749635719846896</v>
+        <v>-0.80398333749508066</v>
       </c>
       <c r="E14" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.33881065730293269</v>
+        <v>-0.7351867069089989</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="B15" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6433</v>
+        <v>6436</v>
       </c>
       <c r="C15" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.90670837874215282</v>
+        <v>0.96798345421102339</v>
       </c>
       <c r="D15" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.96652811224653945</v>
+        <v>-0.678176594583485</v>
       </c>
       <c r="E15" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.48446283196870732</v>
+        <v>-0.83384584355066604</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46155</v>
+        <v>46158</v>
       </c>
       <c r="B16" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6434</v>
+        <v>6437</v>
       </c>
       <c r="C16" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.97892238197578552</v>
+        <v>0.88540516915474554</v>
       </c>
       <c r="D16" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.90125140528845571</v>
+        <v>-0.52829688821080356</v>
       </c>
       <c r="E16" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.61772428900342335</v>
+        <v>-0.91117837325136475</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46156</v>
+        <v>46159</v>
       </c>
       <c r="B17" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6435</v>
+        <v>6438</v>
       </c>
       <c r="C17" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.99971143876226276</v>
+        <v>0.75631460258748828</v>
       </c>
       <c r="D17" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.80398333749508066</v>
+        <v>-0.35966443839709628</v>
       </c>
       <c r="E17" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.7351867069089989</v>
+        <v>-0.96520642386727651</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B18" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6436</v>
+        <v>6439</v>
       </c>
       <c r="C18" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.96798345421102339</v>
+        <v>0.58749316598398182</v>
       </c>
       <c r="D18" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.678176594583485</v>
+        <v>-0.17826512380018317</v>
       </c>
       <c r="E18" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.83384584355066604</v>
+        <v>-0.99454816324394801</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46158</v>
+        <v>46161</v>
       </c>
       <c r="B19" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="C19" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.88540516915474554</v>
+        <v>0.38780942082950592</v>
       </c>
       <c r="D19" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.52829688821080356</v>
+        <v>9.4619966302357094E-3</v>
       </c>
       <c r="E19" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.91117837325136475</v>
+        <v>-0.99845314122621887</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46159</v>
+        <v>46162</v>
       </c>
       <c r="B20" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6438</v>
+        <v>6441</v>
       </c>
       <c r="C20" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.75631460258748828</v>
+        <v>0.16775319358317134</v>
       </c>
       <c r="D20" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.35966443839709628</v>
+        <v>0.19685324834894555</v>
       </c>
       <c r="E20" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.96520642386727651</v>
+        <v>-0.97682148332147356</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46160</v>
+        <v>46163</v>
       </c>
       <c r="B21" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6439</v>
+        <v>6442</v>
       </c>
       <c r="C21" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.58749316598398182</v>
+        <v>-6.1115477996687456E-2</v>
       </c>
       <c r="D21" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.17826512380018317</v>
+        <v>0.37725687900811905</v>
       </c>
       <c r="E21" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.99454816324394801</v>
+        <v>-0.93020644510950601</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <f ca="1">A21+1</f>
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="B22" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6440</v>
+        <v>6443</v>
       </c>
       <c r="C22" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.38780942082950592</v>
+        <v>-0.28677361905753684</v>
       </c>
       <c r="D22" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>9.4619966302357094E-3</v>
+        <v>0.54426917305272549</v>
       </c>
       <c r="E22" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.99845314122621887</v>
+        <v>-0.85980026206697457</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46162</v>
+        <v>46165</v>
       </c>
       <c r="B23" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6441</v>
+        <v>6444</v>
       </c>
       <c r="C23" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.16775319358317134</v>
+        <v>-0.49736691098015484</v>
       </c>
       <c r="D23" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.19685324834894555</v>
+        <v>0.69196176184658986</v>
       </c>
       <c r="E23" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.97682148332147356</v>
+        <v>-0.76740365671946287</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46163</v>
+        <v>46166</v>
       </c>
       <c r="B24" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6442</v>
+        <v>6445</v>
       </c>
       <c r="C24" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-6.1115477996687456E-2</v>
+        <v>-0.68183242481331585</v>
       </c>
       <c r="D24" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.37725687900811905</v>
+        <v>0.81509206060802042</v>
       </c>
       <c r="E24" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.93020644510950601</v>
+        <v>-0.65537978299965449</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="40">
         <f ca="1">A24+1</f>
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B25" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6443</v>
+        <v>6446</v>
       </c>
       <c r="C25" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.28677361905753684</v>
+        <v>-0.83047978127666067</v>
       </c>
       <c r="D25" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.54426917305272549</v>
+        <v>0.90928936234788582</v>
       </c>
       <c r="E25" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.85980026206697457</v>
+        <v>-0.52659378575583204</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46165</v>
+        <v>46168</v>
       </c>
       <c r="B26" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6444</v>
+        <v>6447</v>
       </c>
       <c r="C26" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.49736691098015484</v>
+        <v>-0.93550020769467779</v>
       </c>
       <c r="D26" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.69196176184658986</v>
+        <v>0.97120998310409967</v>
       </c>
       <c r="E26" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.76740365671946287</v>
+        <v>-0.38433952123739623</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46166</v>
+        <v>46169</v>
       </c>
       <c r="B27" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6445</v>
+        <v>6448</v>
       </c>
       <c r="C27" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.68183242481331585</v>
+        <v>-0.99137675001463232</v>
       </c>
       <c r="D27" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.81509206060802042</v>
+        <v>0.99865595135611995</v>
       </c>
       <c r="E27" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.65537978299965449</v>
+        <v>-0.2322553127713233</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="B28" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6446</v>
+        <v>6449</v>
       </c>
       <c r="C28" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.83047978127666067</v>
+        <v>-0.99517409053305272</v>
       </c>
       <c r="D28" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.90928936234788582</v>
+        <v>0.990653028540603</v>
       </c>
       <c r="E28" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.52659378575583204</v>
+        <v>-7.4230896288972642E-2</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="40">
         <f ca="1">A28+1</f>
-        <v>46168</v>
+        <v>46171</v>
       </c>
       <c r="B29" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6447</v>
+        <v>6450</v>
       </c>
       <c r="C29" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.93550020769467779</v>
+        <v>-0.94669274659870006</v>
       </c>
       <c r="D29" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.97120998310409967</v>
+        <v>0.94748529120921043</v>
       </c>
       <c r="E29" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.38433952123739623</v>
+        <v>8.5692064343151839E-2</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46169</v>
+        <v>46172</v>
       </c>
       <c r="B30" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6448</v>
+        <v>6451</v>
       </c>
       <c r="C30" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.99137675001463232</v>
+        <v>-0.84847954987272134</v>
       </c>
       <c r="D30" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.99865595135611995</v>
+        <v>0.87068504727742035</v>
       </c>
       <c r="E30" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.2322553127713233</v>
+        <v>0.24342334771453841</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46170</v>
+        <v>46173</v>
       </c>
       <c r="B31" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6449</v>
+        <v>6452</v>
       </c>
       <c r="C31" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.99517409053305272</v>
+        <v>-0.7056938556559238</v>
       </c>
       <c r="D31" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.990653028540603</v>
+        <v>0.76297844430097561</v>
       </c>
       <c r="E31" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-7.4230896288972642E-2</v>
+        <v>0.39492878718768215</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B32" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="C32" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.94669274659870006</v>
+        <v>-0.52583651060970782</v>
       </c>
       <c r="D32" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.94748529120921043</v>
+        <v>0.62818870050726971</v>
       </c>
       <c r="E32" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>8.5692064343151839E-2</v>
+        <v>0.53633344954541018</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46172</v>
+        <v>46175</v>
       </c>
       <c r="B33" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6451</v>
+        <v>6454</v>
       </c>
       <c r="C33" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.84847954987272134</v>
+        <v>-0.31835581676799474</v>
       </c>
       <c r="D33" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.87068504727742035</v>
+        <v>0.47110039354450584</v>
       </c>
       <c r="E33" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>0.24342334771453841</v>
+        <v>0.66402074105397657</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46173</v>
+        <v>46176</v>
       </c>
       <c r="B34" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6452</v>
+        <v>6455</v>
       </c>
       <c r="C34" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.7056938556559238</v>
+        <v>-9.4151191461850053E-2</v>
       </c>
       <c r="D34" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.76297844430097561</v>
+        <v>0.29728962424790423</v>
       </c>
       <c r="E34" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>0.39492878718768215</v>
+        <v>0.77472490617723277</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46174</v>
+        <v>46177</v>
       </c>
       <c r="B35" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="C35" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.52583651060970782</v>
+        <v>0.13499940307505373</v>
       </c>
       <c r="D35" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.62818870050726971</v>
+        <v>0.11292608400667616</v>
       </c>
       <c r="E35" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>0.53633344954541018</v>
+        <v>0.86561455319766278</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="B36" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6454</v>
+        <v>6457</v>
       </c>
       <c r="C36" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.31835581676799474</v>
+        <v>0.35705818195524541</v>
       </c>
       <c r="D36" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.47110039354450584</v>
+        <v>-7.5445948291718232E-2</v>
       </c>
       <c r="E36" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>0.66402074105397657</v>
+        <v>0.93436507044745232</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46176</v>
+        <v>46179</v>
       </c>
       <c r="B37" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6455</v>
+        <v>6458</v>
       </c>
       <c r="C37" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.4151191461850053E-2</v>
+        <v>0.56035990897729226</v>
       </c>
       <c r="D37" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.29728962424790423</v>
+        <v>-0.26113990592504333</v>
       </c>
       <c r="E37" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77472490617723277</v>
+        <v>0.97921808103946584</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46177</v>
+        <v>46180</v>
       </c>
       <c r="B38" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6456</v>
+        <v>6459</v>
       </c>
       <c r="C38" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.13499940307505373</v>
+        <v>0.73422469713462291</v>
       </c>
       <c r="D38" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.11292608400667616</v>
+        <v>-0.43756428471508418</v>
       </c>
       <c r="E38" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86561455319766278</v>
+        <v>0.99902641546557536</v>
       </c>
     </row>
   </sheetData>
@@ -9089,12 +9375,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="41"/>
@@ -9563,15 +9849,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="77" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
@@ -9747,16 +10033,16 @@
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
     <col min="3" max="3" width="14.5703125" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" style="64" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="58" customWidth="1"/>
     <col min="7" max="7" width="10.85546875" customWidth="1"/>
     <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="59" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="59" t="s">
         <v>111</v>
       </c>
       <c r="C1" s="52" t="s">
@@ -9768,7 +10054,7 @@
       <c r="E1" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="F1" s="66" t="s">
+      <c r="F1" s="60" t="s">
         <v>115</v>
       </c>
       <c r="G1" s="52" t="s">
@@ -9795,30 +10081,30 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="51">
+        <v>6</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="51">
+        <v>11014</v>
+      </c>
+      <c r="D2" s="54">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C2" s="51">
-        <v>11043</v>
-      </c>
-      <c r="D2" s="51">
-        <v>3</v>
-      </c>
       <c r="E2" s="5" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="F2" s="26">
-        <v>3850</v>
-      </c>
-      <c r="G2" s="67">
+        <v>7600</v>
+      </c>
+      <c r="G2" s="61">
         <f>F2*0.14</f>
-        <v>539</v>
-      </c>
-      <c r="H2" s="67">
+        <v>1064</v>
+      </c>
+      <c r="H2" s="61">
         <f>F2-G2</f>
-        <v>3311</v>
+        <v>6536</v>
       </c>
       <c r="I2" s="46"/>
       <c r="J2" s="46"/>
@@ -9855,11 +10141,11 @@
       <c r="F3" s="26">
         <v>4500</v>
       </c>
-      <c r="G3" s="67">
+      <c r="G3" s="61">
         <f>F3*0.14</f>
         <v>630.00000000000011</v>
       </c>
-      <c r="H3" s="67">
+      <c r="H3" s="61">
         <f>F3-G3</f>
         <v>3870</v>
       </c>
@@ -9881,30 +10167,30 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="51">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C4" s="51">
-        <v>11044</v>
+        <v>11019</v>
       </c>
       <c r="D4" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F4" s="26">
-        <v>4200</v>
-      </c>
-      <c r="G4" s="67">
+        <v>6450</v>
+      </c>
+      <c r="G4" s="61">
         <f>F4*0.14</f>
-        <v>588</v>
-      </c>
-      <c r="H4" s="67">
+        <v>903.00000000000011</v>
+      </c>
+      <c r="H4" s="61">
         <f>F4-G4</f>
-        <v>3612</v>
+        <v>5547</v>
       </c>
       <c r="I4" s="46"/>
       <c r="J4" s="46"/>
@@ -9924,30 +10210,30 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="51">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="C5" s="51">
-        <v>11036</v>
+        <v>11045</v>
       </c>
       <c r="D5" s="51">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="F5" s="26">
-        <v>4450</v>
-      </c>
-      <c r="G5" s="67">
+        <v>2800</v>
+      </c>
+      <c r="G5" s="61">
         <f>F5*0.14</f>
-        <v>623.00000000000011</v>
-      </c>
-      <c r="H5" s="67">
+        <v>392.00000000000006</v>
+      </c>
+      <c r="H5" s="61">
         <f>F5-G5</f>
-        <v>3827</v>
+        <v>2408</v>
       </c>
       <c r="I5" s="46"/>
       <c r="J5" s="46"/>
@@ -9967,30 +10253,30 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="51">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="C6" s="51">
-        <v>11017</v>
-      </c>
-      <c r="D6" s="51">
-        <v>3</v>
+        <v>11023</v>
+      </c>
+      <c r="D6" s="39">
+        <v>1</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="F6" s="26">
-        <v>6299</v>
-      </c>
-      <c r="G6" s="67">
+        <v>7200</v>
+      </c>
+      <c r="G6" s="61">
         <f>F6*0.14</f>
-        <v>881.86000000000013</v>
-      </c>
-      <c r="H6" s="67">
+        <v>1008.0000000000001</v>
+      </c>
+      <c r="H6" s="61">
         <f>F6-G6</f>
-        <v>5417.1399999999994</v>
+        <v>6192</v>
       </c>
       <c r="I6" s="46"/>
       <c r="J6" s="46"/>
@@ -10010,30 +10296,30 @@
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="51">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="C7" s="51">
-        <v>11014</v>
-      </c>
-      <c r="D7" s="51">
+        <v>11009</v>
+      </c>
+      <c r="D7" s="54">
         <v>1</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="F7" s="26">
-        <v>7600</v>
-      </c>
-      <c r="G7" s="67">
+        <v>9850</v>
+      </c>
+      <c r="G7" s="61">
         <f>F7*0.14</f>
-        <v>1064</v>
-      </c>
-      <c r="H7" s="67">
+        <v>1379.0000000000002</v>
+      </c>
+      <c r="H7" s="61">
         <f>F7-G7</f>
-        <v>6536</v>
+        <v>8471</v>
       </c>
       <c r="I7" s="46"/>
       <c r="J7" s="46"/>
@@ -10053,30 +10339,30 @@
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="51">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C8" s="51">
-        <v>11025</v>
+        <v>11036</v>
       </c>
       <c r="D8" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F8" s="26">
-        <v>7480</v>
-      </c>
-      <c r="G8" s="67">
+        <v>4450</v>
+      </c>
+      <c r="G8" s="61">
         <f>F8*0.14</f>
-        <v>1047.2</v>
-      </c>
-      <c r="H8" s="67">
+        <v>623.00000000000011</v>
+      </c>
+      <c r="H8" s="61">
         <f>F8-G8</f>
-        <v>6432.8</v>
+        <v>3827</v>
       </c>
       <c r="I8" s="46"/>
       <c r="J8" s="46"/>
@@ -10096,30 +10382,30 @@
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="51">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="C9" s="51">
-        <v>11019</v>
+        <v>11003</v>
       </c>
       <c r="D9" s="51">
         <v>1</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="F9" s="26">
-        <v>6450</v>
-      </c>
-      <c r="G9" s="67">
+        <v>7800</v>
+      </c>
+      <c r="G9" s="61">
         <f>F9*0.14</f>
-        <v>903.00000000000011</v>
-      </c>
-      <c r="H9" s="67">
+        <v>1092</v>
+      </c>
+      <c r="H9" s="61">
         <f>F9-G9</f>
-        <v>5547</v>
+        <v>6708</v>
       </c>
       <c r="I9" s="46"/>
       <c r="J9" s="46"/>
@@ -10139,30 +10425,30 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="51">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C10" s="51">
-        <v>11018</v>
+        <v>11025</v>
       </c>
       <c r="D10" s="51">
         <v>2</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F10" s="26">
-        <v>6840</v>
-      </c>
-      <c r="G10" s="67">
+        <v>7480</v>
+      </c>
+      <c r="G10" s="61">
         <f>F10*0.14</f>
-        <v>957.60000000000014</v>
-      </c>
-      <c r="H10" s="67">
+        <v>1047.2</v>
+      </c>
+      <c r="H10" s="61">
         <f>F10-G10</f>
-        <v>5882.4</v>
+        <v>6432.8</v>
       </c>
       <c r="I10" s="46"/>
       <c r="J10" s="46"/>
@@ -10199,11 +10485,11 @@
       <c r="F11" s="26">
         <v>3460</v>
       </c>
-      <c r="G11" s="67">
+      <c r="G11" s="61">
         <f>F11*0.14</f>
         <v>484.40000000000003</v>
       </c>
-      <c r="H11" s="67">
+      <c r="H11" s="61">
         <f>F11-G11</f>
         <v>2975.6</v>
       </c>
@@ -10225,30 +10511,30 @@
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="51">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="C12" s="51">
-        <v>11012</v>
+        <v>11044</v>
       </c>
       <c r="D12" s="51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="F12" s="26">
-        <v>3950</v>
-      </c>
-      <c r="G12" s="67">
+        <v>4200</v>
+      </c>
+      <c r="G12" s="61">
         <f>F12*0.14</f>
-        <v>553</v>
-      </c>
-      <c r="H12" s="67">
+        <v>588</v>
+      </c>
+      <c r="H12" s="61">
         <f>F12-G12</f>
-        <v>3397</v>
+        <v>3612</v>
       </c>
       <c r="I12" s="46"/>
       <c r="J12" s="46"/>
@@ -10268,30 +10554,30 @@
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C13" s="51">
-        <v>11022</v>
-      </c>
-      <c r="D13" s="51">
-        <v>3</v>
+        <v>11018</v>
+      </c>
+      <c r="D13" s="54">
+        <v>2</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="F13" s="26">
-        <v>3740</v>
-      </c>
-      <c r="G13" s="67">
+        <v>6840</v>
+      </c>
+      <c r="G13" s="61">
         <f>F13*0.14</f>
-        <v>523.6</v>
-      </c>
-      <c r="H13" s="67">
+        <v>957.60000000000014</v>
+      </c>
+      <c r="H13" s="61">
         <f>F13-G13</f>
-        <v>3216.4</v>
+        <v>5882.4</v>
       </c>
       <c r="I13" s="46"/>
       <c r="J13" s="46"/>
@@ -10311,30 +10597,30 @@
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="51">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C14" s="51">
-        <v>11045</v>
-      </c>
-      <c r="D14" s="51">
-        <v>1</v>
+        <v>11002</v>
+      </c>
+      <c r="D14" s="54">
+        <v>2</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F14" s="26">
-        <v>2800</v>
-      </c>
-      <c r="G14" s="67">
+        <v>4100</v>
+      </c>
+      <c r="G14" s="61">
         <f>F14*0.14</f>
-        <v>392.00000000000006</v>
-      </c>
-      <c r="H14" s="67">
+        <v>574</v>
+      </c>
+      <c r="H14" s="61">
         <f>F14-G14</f>
-        <v>2408</v>
+        <v>3526</v>
       </c>
       <c r="I14" s="46"/>
       <c r="J14" s="46"/>
@@ -10354,30 +10640,30 @@
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="51">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="C15" s="51">
-        <v>11023</v>
-      </c>
-      <c r="D15" s="68">
-        <v>1</v>
+        <v>11017</v>
+      </c>
+      <c r="D15" s="80">
+        <v>3</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="F15" s="26">
-        <v>7200</v>
-      </c>
-      <c r="G15" s="67">
+        <v>6299</v>
+      </c>
+      <c r="G15" s="61">
         <f>F15*0.14</f>
-        <v>1008.0000000000001</v>
-      </c>
-      <c r="H15" s="67">
+        <v>881.86000000000013</v>
+      </c>
+      <c r="H15" s="61">
         <f>F15-G15</f>
-        <v>6192</v>
+        <v>5417.1399999999994</v>
       </c>
       <c r="I15" s="46"/>
       <c r="J15" s="46"/>
@@ -10397,13 +10683,13 @@
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="51">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C16" s="51">
-        <v>11010</v>
+        <v>11012</v>
       </c>
       <c r="D16" s="51">
         <v>3</v>
@@ -10412,15 +10698,15 @@
         <v>134</v>
       </c>
       <c r="F16" s="26">
-        <v>3600</v>
-      </c>
-      <c r="G16" s="67">
+        <v>3950</v>
+      </c>
+      <c r="G16" s="61">
         <f>F16*0.14</f>
-        <v>504.00000000000006</v>
-      </c>
-      <c r="H16" s="67">
+        <v>553</v>
+      </c>
+      <c r="H16" s="61">
         <f>F16-G16</f>
-        <v>3096</v>
+        <v>3397</v>
       </c>
       <c r="I16" s="46"/>
       <c r="J16" s="46"/>
@@ -10440,30 +10726,30 @@
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="51">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C17" s="51">
-        <v>11002</v>
+        <v>11022</v>
       </c>
       <c r="D17" s="51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="F17" s="26">
-        <v>4100</v>
-      </c>
-      <c r="G17" s="67">
+        <v>3740</v>
+      </c>
+      <c r="G17" s="61">
         <f>F17*0.14</f>
-        <v>574</v>
-      </c>
-      <c r="H17" s="67">
+        <v>523.6</v>
+      </c>
+      <c r="H17" s="61">
         <f>F17-G17</f>
-        <v>3526</v>
+        <v>3216.4</v>
       </c>
       <c r="I17" s="46"/>
       <c r="J17" s="46"/>
@@ -10483,30 +10769,30 @@
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="51">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="C18" s="51">
-        <v>11009</v>
+        <v>11043</v>
       </c>
       <c r="D18" s="51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="F18" s="26">
-        <v>9850</v>
-      </c>
-      <c r="G18" s="67">
+        <v>3850</v>
+      </c>
+      <c r="G18" s="61">
         <f>F18*0.14</f>
-        <v>1379.0000000000002</v>
-      </c>
-      <c r="H18" s="67">
+        <v>539</v>
+      </c>
+      <c r="H18" s="61">
         <f>F18-G18</f>
-        <v>8471</v>
+        <v>3311</v>
       </c>
       <c r="I18" s="46"/>
       <c r="J18" s="46"/>
@@ -10526,30 +10812,30 @@
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="51">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C19" s="51">
-        <v>11003</v>
-      </c>
-      <c r="D19" s="51">
-        <v>1</v>
+        <v>11010</v>
+      </c>
+      <c r="D19" s="54">
+        <v>3</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="F19" s="26">
-        <v>7800</v>
-      </c>
-      <c r="G19" s="67">
+        <v>3600</v>
+      </c>
+      <c r="G19" s="61">
         <f>F19*0.14</f>
-        <v>1092</v>
-      </c>
-      <c r="H19" s="67">
+        <v>504.00000000000006</v>
+      </c>
+      <c r="H19" s="61">
         <f>F19-G19</f>
-        <v>6708</v>
+        <v>3096</v>
       </c>
       <c r="I19" s="46"/>
       <c r="J19" s="46"/>
@@ -10573,7 +10859,7 @@
       <c r="C20" s="46"/>
       <c r="D20" s="46"/>
       <c r="E20" s="46"/>
-      <c r="F20" s="63"/>
+      <c r="F20" s="57"/>
       <c r="G20" s="46"/>
       <c r="H20" s="46"/>
       <c r="I20" s="46"/>
@@ -10598,7 +10884,7 @@
       <c r="C21" s="46"/>
       <c r="D21" s="46"/>
       <c r="E21" s="46"/>
-      <c r="F21" s="63"/>
+      <c r="F21" s="57"/>
       <c r="G21" s="46"/>
       <c r="H21" s="46"/>
       <c r="I21" s="46"/>
@@ -10618,10 +10904,10 @@
       <c r="W21" s="46"/>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A22" s="65" t="s">
+      <c r="A22" s="59" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="65" t="s">
+      <c r="B22" s="59" t="s">
         <v>111</v>
       </c>
       <c r="C22" s="52" t="s">
@@ -10633,7 +10919,7 @@
       <c r="E22" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="F22" s="66" t="s">
+      <c r="F22" s="60" t="s">
         <v>115</v>
       </c>
       <c r="G22" s="52" t="s">
@@ -10677,10 +10963,10 @@
       <c r="F23" s="26">
         <v>3850</v>
       </c>
-      <c r="G23" s="67">
+      <c r="G23" s="61">
         <v>539</v>
       </c>
-      <c r="H23" s="67">
+      <c r="H23" s="61">
         <v>3311</v>
       </c>
       <c r="I23" s="46"/>
@@ -10718,10 +11004,10 @@
       <c r="F24" s="26">
         <v>3460</v>
       </c>
-      <c r="G24" s="67">
+      <c r="G24" s="61">
         <v>484.40000000000003</v>
       </c>
-      <c r="H24" s="67">
+      <c r="H24" s="61">
         <v>2975.6</v>
       </c>
       <c r="I24" s="46"/>
@@ -10759,10 +11045,10 @@
       <c r="F25" s="26">
         <v>3950</v>
       </c>
-      <c r="G25" s="67">
+      <c r="G25" s="61">
         <v>553</v>
       </c>
-      <c r="H25" s="67">
+      <c r="H25" s="61">
         <v>3397</v>
       </c>
       <c r="I25" s="46"/>
@@ -10800,10 +11086,10 @@
       <c r="F26" s="26">
         <v>3740</v>
       </c>
-      <c r="G26" s="67">
+      <c r="G26" s="61">
         <v>523.6</v>
       </c>
-      <c r="H26" s="67">
+      <c r="H26" s="61">
         <v>3216.4</v>
       </c>
       <c r="I26" s="46"/>
@@ -10841,10 +11127,10 @@
       <c r="F27" s="26">
         <v>2800</v>
       </c>
-      <c r="G27" s="67">
+      <c r="G27" s="61">
         <v>392.00000000000006</v>
       </c>
-      <c r="H27" s="67">
+      <c r="H27" s="61">
         <v>2408</v>
       </c>
       <c r="I27" s="46"/>
@@ -10882,10 +11168,10 @@
       <c r="F28" s="26">
         <v>3600</v>
       </c>
-      <c r="G28" s="67">
+      <c r="G28" s="61">
         <v>504.00000000000006</v>
       </c>
-      <c r="H28" s="67">
+      <c r="H28" s="61">
         <v>3096</v>
       </c>
       <c r="I28" s="46"/>
@@ -10910,7 +11196,7 @@
       <c r="C29" s="46"/>
       <c r="D29" s="46"/>
       <c r="E29" s="46"/>
-      <c r="F29" s="63"/>
+      <c r="F29" s="57"/>
       <c r="G29" s="46"/>
       <c r="H29" s="46"/>
       <c r="I29" s="46"/>
@@ -10930,10 +11216,10 @@
       <c r="W29" s="46"/>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A30" s="65" t="s">
+      <c r="A30" s="59" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="65" t="s">
+      <c r="B30" s="59" t="s">
         <v>111</v>
       </c>
       <c r="C30" s="52" t="s">
@@ -10945,7 +11231,7 @@
       <c r="E30" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="F30" s="66" t="s">
+      <c r="F30" s="60" t="s">
         <v>115</v>
       </c>
       <c r="G30" s="52" t="s">
@@ -10989,10 +11275,10 @@
       <c r="F31" s="26">
         <v>4500</v>
       </c>
-      <c r="G31" s="67">
+      <c r="G31" s="61">
         <v>630.00000000000011</v>
       </c>
-      <c r="H31" s="67">
+      <c r="H31" s="61">
         <v>3870</v>
       </c>
       <c r="I31" s="46"/>
@@ -11030,10 +11316,10 @@
       <c r="F32" s="26">
         <v>4450</v>
       </c>
-      <c r="G32" s="67">
+      <c r="G32" s="61">
         <v>623.00000000000011</v>
       </c>
-      <c r="H32" s="67">
+      <c r="H32" s="61">
         <v>3827</v>
       </c>
       <c r="I32" s="46"/>
@@ -11071,10 +11357,10 @@
       <c r="F33" s="26">
         <v>7600</v>
       </c>
-      <c r="G33" s="67">
+      <c r="G33" s="61">
         <v>1064</v>
       </c>
-      <c r="H33" s="67">
+      <c r="H33" s="61">
         <v>6536</v>
       </c>
       <c r="I33" s="46"/>
@@ -11112,16 +11398,16 @@
       <c r="F34" s="26">
         <v>6450</v>
       </c>
-      <c r="G34" s="67">
+      <c r="G34" s="61">
         <v>903.00000000000011</v>
       </c>
-      <c r="H34" s="67">
+      <c r="H34" s="61">
         <v>5547</v>
       </c>
       <c r="I34" s="46"/>
       <c r="J34" s="46"/>
       <c r="K34" s="46"/>
-      <c r="L34" s="72"/>
+      <c r="L34" s="66"/>
       <c r="M34" s="46"/>
       <c r="N34" s="46"/>
       <c r="O34" s="46"/>
@@ -11153,10 +11439,10 @@
       <c r="F35" s="26">
         <v>2800</v>
       </c>
-      <c r="G35" s="67">
+      <c r="G35" s="61">
         <v>392.00000000000006</v>
       </c>
-      <c r="H35" s="67">
+      <c r="H35" s="61">
         <v>2408</v>
       </c>
       <c r="I35" s="46"/>
@@ -11185,7 +11471,7 @@
       <c r="C36" s="51">
         <v>11023</v>
       </c>
-      <c r="D36" s="68">
+      <c r="D36" s="62">
         <v>1</v>
       </c>
       <c r="E36" s="5" t="s">
@@ -11194,10 +11480,10 @@
       <c r="F36" s="26">
         <v>7200</v>
       </c>
-      <c r="G36" s="67">
+      <c r="G36" s="61">
         <v>1008.0000000000001</v>
       </c>
-      <c r="H36" s="67">
+      <c r="H36" s="61">
         <v>6192</v>
       </c>
       <c r="I36" s="46"/>
@@ -11235,10 +11521,10 @@
       <c r="F37" s="26">
         <v>9850</v>
       </c>
-      <c r="G37" s="67">
+      <c r="G37" s="61">
         <v>1379.0000000000002</v>
       </c>
-      <c r="H37" s="67">
+      <c r="H37" s="61">
         <v>8471</v>
       </c>
       <c r="I37" s="46"/>
@@ -11258,28 +11544,28 @@
       <c r="W37" s="46"/>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A38" s="69">
+      <c r="A38" s="63">
         <v>18</v>
       </c>
-      <c r="B38" s="70" t="s">
+      <c r="B38" s="64" t="s">
         <v>146</v>
       </c>
-      <c r="C38" s="69">
+      <c r="C38" s="63">
         <v>11003</v>
       </c>
-      <c r="D38" s="69">
+      <c r="D38" s="63">
         <v>1</v>
       </c>
-      <c r="E38" s="70" t="s">
+      <c r="E38" s="64" t="s">
         <v>147</v>
       </c>
       <c r="F38" s="30">
         <v>7800</v>
       </c>
-      <c r="G38" s="71">
+      <c r="G38" s="65">
         <v>1092</v>
       </c>
-      <c r="H38" s="71">
+      <c r="H38" s="65">
         <v>6708</v>
       </c>
       <c r="I38" s="46"/>
@@ -11300,14 +11586,14 @@
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" s="45"/>
-      <c r="B39" s="73"/>
+      <c r="B39" s="67"/>
       <c r="C39" s="45"/>
       <c r="D39" s="45"/>
-      <c r="E39" s="73"/>
-      <c r="F39" s="74"/>
-      <c r="G39" s="75"/>
-      <c r="H39" s="75"/>
-      <c r="I39" s="72"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="68"/>
+      <c r="G39" s="69"/>
+      <c r="H39" s="69"/>
+      <c r="I39" s="66"/>
       <c r="J39" s="46"/>
       <c r="K39" s="46"/>
       <c r="L39" s="46"/>
@@ -11324,10 +11610,10 @@
       <c r="W39" s="46"/>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A40" s="65" t="s">
+      <c r="A40" s="59" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="65" t="s">
+      <c r="B40" s="59" t="s">
         <v>111</v>
       </c>
       <c r="C40" s="52" t="s">
@@ -11339,7 +11625,7 @@
       <c r="E40" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="F40" s="66" t="s">
+      <c r="F40" s="60" t="s">
         <v>115</v>
       </c>
       <c r="G40" s="52" t="s">
@@ -11348,7 +11634,7 @@
       <c r="H40" s="52" t="s">
         <v>117</v>
       </c>
-      <c r="I40" s="72"/>
+      <c r="I40" s="66"/>
       <c r="J40" s="46"/>
       <c r="K40" s="46"/>
       <c r="L40" s="46"/>
@@ -11383,13 +11669,13 @@
       <c r="F41" s="26">
         <v>4200</v>
       </c>
-      <c r="G41" s="67">
+      <c r="G41" s="61">
         <v>588</v>
       </c>
-      <c r="H41" s="67">
+      <c r="H41" s="61">
         <v>3612</v>
       </c>
-      <c r="I41" s="72"/>
+      <c r="I41" s="66"/>
       <c r="J41" s="46"/>
       <c r="K41" s="46"/>
       <c r="L41" s="46"/>
@@ -11424,13 +11710,13 @@
       <c r="F42" s="26">
         <v>7480</v>
       </c>
-      <c r="G42" s="67">
+      <c r="G42" s="61">
         <v>1047.2</v>
       </c>
-      <c r="H42" s="67">
+      <c r="H42" s="61">
         <v>6432.8</v>
       </c>
-      <c r="I42" s="72"/>
+      <c r="I42" s="66"/>
       <c r="J42" s="46"/>
       <c r="K42" s="46"/>
       <c r="L42" s="46"/>
@@ -11465,10 +11751,10 @@
       <c r="F43" s="26">
         <v>6840</v>
       </c>
-      <c r="G43" s="67">
+      <c r="G43" s="61">
         <v>957.60000000000014</v>
       </c>
-      <c r="H43" s="67">
+      <c r="H43" s="61">
         <v>5882.4</v>
       </c>
       <c r="I43" s="46"/>
@@ -11506,10 +11792,10 @@
       <c r="F44" s="26">
         <v>3460</v>
       </c>
-      <c r="G44" s="67">
+      <c r="G44" s="61">
         <v>484.40000000000003</v>
       </c>
-      <c r="H44" s="67">
+      <c r="H44" s="61">
         <v>2975.6</v>
       </c>
       <c r="I44" s="46"/>
@@ -11547,10 +11833,10 @@
       <c r="F45" s="26">
         <v>4100</v>
       </c>
-      <c r="G45" s="67">
+      <c r="G45" s="61">
         <v>574</v>
       </c>
-      <c r="H45" s="67">
+      <c r="H45" s="61">
         <v>3526</v>
       </c>
       <c r="I45" s="46"/>
@@ -11575,7 +11861,7 @@
       <c r="C46" s="46"/>
       <c r="D46" s="46"/>
       <c r="E46" s="46"/>
-      <c r="F46" s="63"/>
+      <c r="F46" s="57"/>
       <c r="G46" s="46"/>
       <c r="H46" s="46"/>
       <c r="I46" s="46"/>
@@ -11595,14 +11881,30 @@
       <c r="W46" s="46"/>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A47" s="46"/>
-      <c r="B47" s="46"/>
-      <c r="C47" s="46"/>
-      <c r="D47" s="46"/>
-      <c r="E47" s="46"/>
-      <c r="F47" s="63"/>
-      <c r="G47" s="46"/>
-      <c r="H47" s="46"/>
+      <c r="A47" s="59" t="s">
+        <v>68</v>
+      </c>
+      <c r="B47" s="59" t="s">
+        <v>111</v>
+      </c>
+      <c r="C47" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D47" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="E47" s="55" t="s">
+        <v>114</v>
+      </c>
+      <c r="F47" s="60" t="s">
+        <v>115</v>
+      </c>
+      <c r="G47" s="55" t="s">
+        <v>116</v>
+      </c>
+      <c r="H47" s="55" t="s">
+        <v>117</v>
+      </c>
       <c r="I47" s="46"/>
       <c r="J47" s="46"/>
       <c r="K47" s="46"/>
@@ -11620,14 +11922,30 @@
       <c r="W47" s="46"/>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A48" s="46"/>
-      <c r="B48" s="46"/>
-      <c r="C48" s="46"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="46"/>
-      <c r="F48" s="63"/>
-      <c r="G48" s="46"/>
-      <c r="H48" s="46"/>
+      <c r="A48" s="54">
+        <v>10</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C48" s="54">
+        <v>11033</v>
+      </c>
+      <c r="D48" s="54">
+        <v>2</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F48" s="26">
+        <v>3460</v>
+      </c>
+      <c r="G48" s="61">
+        <v>484.40000000000003</v>
+      </c>
+      <c r="H48" s="61">
+        <v>2975.6</v>
+      </c>
       <c r="I48" s="46"/>
       <c r="J48" s="46"/>
       <c r="K48" s="46"/>
@@ -11645,14 +11963,30 @@
       <c r="W48" s="46"/>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A49" s="46"/>
-      <c r="B49" s="46"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="46"/>
-      <c r="E49" s="46"/>
-      <c r="F49" s="63"/>
-      <c r="G49" s="46"/>
-      <c r="H49" s="46"/>
+      <c r="A49" s="54">
+        <v>11</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C49" s="54">
+        <v>11012</v>
+      </c>
+      <c r="D49" s="54">
+        <v>3</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F49" s="26">
+        <v>3950</v>
+      </c>
+      <c r="G49" s="61">
+        <v>553</v>
+      </c>
+      <c r="H49" s="61">
+        <v>3397</v>
+      </c>
       <c r="I49" s="46"/>
       <c r="J49" s="46"/>
       <c r="K49" s="46"/>
@@ -11670,14 +12004,30 @@
       <c r="W49" s="46"/>
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A50" s="46"/>
-      <c r="B50" s="46"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="46"/>
-      <c r="E50" s="46"/>
-      <c r="F50" s="63"/>
-      <c r="G50" s="46"/>
-      <c r="H50" s="46"/>
+      <c r="A50" s="54">
+        <v>12</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C50" s="54">
+        <v>11022</v>
+      </c>
+      <c r="D50" s="54">
+        <v>3</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F50" s="26">
+        <v>3740</v>
+      </c>
+      <c r="G50" s="61">
+        <v>523.6</v>
+      </c>
+      <c r="H50" s="61">
+        <v>3216.4</v>
+      </c>
       <c r="I50" s="46"/>
       <c r="J50" s="46"/>
       <c r="K50" s="46"/>
@@ -11700,7 +12050,7 @@
       <c r="C51" s="46"/>
       <c r="D51" s="46"/>
       <c r="E51" s="46"/>
-      <c r="F51" s="63"/>
+      <c r="F51" s="57"/>
       <c r="G51" s="46"/>
       <c r="H51" s="46"/>
       <c r="I51" s="46"/>
@@ -11725,7 +12075,7 @@
       <c r="C52" s="46"/>
       <c r="D52" s="46"/>
       <c r="E52" s="46"/>
-      <c r="F52" s="63"/>
+      <c r="F52" s="57"/>
       <c r="G52" s="46"/>
       <c r="H52" s="46"/>
       <c r="I52" s="46"/>
@@ -11750,7 +12100,7 @@
       <c r="C53" s="46"/>
       <c r="D53" s="46"/>
       <c r="E53" s="46"/>
-      <c r="F53" s="63"/>
+      <c r="F53" s="57"/>
       <c r="G53" s="46"/>
       <c r="H53" s="46"/>
       <c r="I53" s="46"/>
@@ -11775,7 +12125,7 @@
       <c r="C54" s="46"/>
       <c r="D54" s="46"/>
       <c r="E54" s="46"/>
-      <c r="F54" s="63"/>
+      <c r="F54" s="57"/>
       <c r="G54" s="46"/>
       <c r="H54" s="46"/>
       <c r="I54" s="46"/>
@@ -11800,7 +12150,7 @@
       <c r="C55" s="46"/>
       <c r="D55" s="46"/>
       <c r="E55" s="46"/>
-      <c r="F55" s="63"/>
+      <c r="F55" s="57"/>
       <c r="G55" s="46"/>
       <c r="H55" s="46"/>
       <c r="I55" s="46"/>
@@ -11825,7 +12175,7 @@
       <c r="C56" s="46"/>
       <c r="D56" s="46"/>
       <c r="E56" s="46"/>
-      <c r="F56" s="63"/>
+      <c r="F56" s="57"/>
       <c r="G56" s="46"/>
       <c r="H56" s="46"/>
       <c r="I56" s="46"/>
@@ -11850,7 +12200,7 @@
       <c r="C57" s="46"/>
       <c r="D57" s="46"/>
       <c r="E57" s="46"/>
-      <c r="F57" s="63"/>
+      <c r="F57" s="57"/>
       <c r="G57" s="46"/>
       <c r="H57" s="46"/>
       <c r="I57" s="46"/>
@@ -11875,7 +12225,7 @@
       <c r="C58" s="46"/>
       <c r="D58" s="46"/>
       <c r="E58" s="46"/>
-      <c r="F58" s="63"/>
+      <c r="F58" s="57"/>
       <c r="G58" s="46"/>
       <c r="H58" s="46"/>
       <c r="I58" s="46"/>
@@ -11900,7 +12250,7 @@
       <c r="C59" s="46"/>
       <c r="D59" s="46"/>
       <c r="E59" s="46"/>
-      <c r="F59" s="63"/>
+      <c r="F59" s="57"/>
       <c r="G59" s="46"/>
       <c r="H59" s="46"/>
       <c r="I59" s="46"/>
@@ -11925,7 +12275,7 @@
       <c r="C60" s="46"/>
       <c r="D60" s="46"/>
       <c r="E60" s="46"/>
-      <c r="F60" s="63"/>
+      <c r="F60" s="57"/>
       <c r="G60" s="46"/>
       <c r="H60" s="46"/>
       <c r="I60" s="46"/>
@@ -11950,7 +12300,7 @@
       <c r="C61" s="46"/>
       <c r="D61" s="46"/>
       <c r="E61" s="46"/>
-      <c r="F61" s="63"/>
+      <c r="F61" s="57"/>
       <c r="G61" s="46"/>
       <c r="H61" s="46"/>
       <c r="I61" s="46"/>
@@ -11975,7 +12325,7 @@
       <c r="C62" s="46"/>
       <c r="D62" s="46"/>
       <c r="E62" s="46"/>
-      <c r="F62" s="63"/>
+      <c r="F62" s="57"/>
       <c r="G62" s="46"/>
       <c r="H62" s="46"/>
       <c r="I62" s="46"/>
@@ -12000,7 +12350,7 @@
       <c r="C63" s="46"/>
       <c r="D63" s="46"/>
       <c r="E63" s="46"/>
-      <c r="F63" s="63"/>
+      <c r="F63" s="57"/>
       <c r="G63" s="46"/>
       <c r="H63" s="46"/>
       <c r="I63" s="46"/>
@@ -12025,7 +12375,7 @@
       <c r="C64" s="46"/>
       <c r="D64" s="46"/>
       <c r="E64" s="46"/>
-      <c r="F64" s="63"/>
+      <c r="F64" s="57"/>
       <c r="G64" s="46"/>
       <c r="H64" s="46"/>
       <c r="I64" s="46"/>
@@ -12050,7 +12400,7 @@
       <c r="C65" s="46"/>
       <c r="D65" s="46"/>
       <c r="E65" s="46"/>
-      <c r="F65" s="63"/>
+      <c r="F65" s="57"/>
       <c r="G65" s="46"/>
       <c r="H65" s="46"/>
       <c r="I65" s="46"/>
@@ -12075,7 +12425,7 @@
       <c r="C66" s="46"/>
       <c r="D66" s="46"/>
       <c r="E66" s="46"/>
-      <c r="F66" s="63"/>
+      <c r="F66" s="57"/>
       <c r="G66" s="46"/>
       <c r="H66" s="46"/>
       <c r="I66" s="46"/>
@@ -12100,7 +12450,7 @@
       <c r="C67" s="46"/>
       <c r="D67" s="46"/>
       <c r="E67" s="46"/>
-      <c r="F67" s="63"/>
+      <c r="F67" s="57"/>
       <c r="G67" s="46"/>
       <c r="H67" s="46"/>
       <c r="I67" s="46"/>
@@ -12125,7 +12475,7 @@
       <c r="C68" s="46"/>
       <c r="D68" s="46"/>
       <c r="E68" s="46"/>
-      <c r="F68" s="63"/>
+      <c r="F68" s="57"/>
       <c r="G68" s="46"/>
       <c r="H68" s="46"/>
       <c r="I68" s="46"/>
@@ -12150,7 +12500,7 @@
       <c r="C69" s="46"/>
       <c r="D69" s="46"/>
       <c r="E69" s="46"/>
-      <c r="F69" s="63"/>
+      <c r="F69" s="57"/>
       <c r="G69" s="46"/>
       <c r="H69" s="46"/>
       <c r="I69" s="46"/>
@@ -12175,7 +12525,7 @@
       <c r="C70" s="46"/>
       <c r="D70" s="46"/>
       <c r="E70" s="46"/>
-      <c r="F70" s="63"/>
+      <c r="F70" s="57"/>
       <c r="G70" s="46"/>
       <c r="H70" s="46"/>
       <c r="I70" s="46"/>
@@ -12200,7 +12550,7 @@
       <c r="C71" s="46"/>
       <c r="D71" s="46"/>
       <c r="E71" s="46"/>
-      <c r="F71" s="63"/>
+      <c r="F71" s="57"/>
       <c r="G71" s="46"/>
       <c r="H71" s="46"/>
       <c r="I71" s="46"/>
@@ -12225,7 +12575,7 @@
       <c r="C72" s="46"/>
       <c r="D72" s="46"/>
       <c r="E72" s="46"/>
-      <c r="F72" s="63"/>
+      <c r="F72" s="57"/>
       <c r="G72" s="46"/>
       <c r="H72" s="46"/>
       <c r="I72" s="46"/>
@@ -12250,7 +12600,7 @@
       <c r="C73" s="46"/>
       <c r="D73" s="46"/>
       <c r="E73" s="46"/>
-      <c r="F73" s="63"/>
+      <c r="F73" s="57"/>
       <c r="G73" s="46"/>
       <c r="H73" s="46"/>
       <c r="I73" s="46"/>
@@ -12275,7 +12625,7 @@
       <c r="C74" s="46"/>
       <c r="D74" s="46"/>
       <c r="E74" s="46"/>
-      <c r="F74" s="63"/>
+      <c r="F74" s="57"/>
       <c r="G74" s="46"/>
       <c r="H74" s="46"/>
       <c r="I74" s="46"/>
@@ -12300,7 +12650,7 @@
       <c r="C75" s="46"/>
       <c r="D75" s="46"/>
       <c r="E75" s="46"/>
-      <c r="F75" s="63"/>
+      <c r="F75" s="57"/>
       <c r="G75" s="46"/>
       <c r="H75" s="46"/>
       <c r="I75" s="46"/>
@@ -12325,7 +12675,7 @@
       <c r="C76" s="46"/>
       <c r="D76" s="46"/>
       <c r="E76" s="46"/>
-      <c r="F76" s="63"/>
+      <c r="F76" s="57"/>
       <c r="G76" s="46"/>
       <c r="H76" s="46"/>
       <c r="I76" s="46"/>
@@ -12350,7 +12700,7 @@
       <c r="C77" s="46"/>
       <c r="D77" s="46"/>
       <c r="E77" s="46"/>
-      <c r="F77" s="63"/>
+      <c r="F77" s="57"/>
       <c r="G77" s="46"/>
       <c r="H77" s="46"/>
       <c r="I77" s="46"/>
@@ -12375,7 +12725,7 @@
       <c r="C78" s="46"/>
       <c r="D78" s="46"/>
       <c r="E78" s="46"/>
-      <c r="F78" s="63"/>
+      <c r="F78" s="57"/>
       <c r="G78" s="46"/>
       <c r="H78" s="46"/>
       <c r="I78" s="46"/>
@@ -12400,7 +12750,7 @@
       <c r="C79" s="46"/>
       <c r="D79" s="46"/>
       <c r="E79" s="46"/>
-      <c r="F79" s="63"/>
+      <c r="F79" s="57"/>
       <c r="G79" s="46"/>
       <c r="H79" s="46"/>
       <c r="I79" s="46"/>
@@ -12425,7 +12775,7 @@
       <c r="C80" s="46"/>
       <c r="D80" s="46"/>
       <c r="E80" s="46"/>
-      <c r="F80" s="63"/>
+      <c r="F80" s="57"/>
       <c r="G80" s="46"/>
       <c r="H80" s="46"/>
       <c r="I80" s="46"/>
@@ -12450,7 +12800,7 @@
       <c r="C81" s="46"/>
       <c r="D81" s="46"/>
       <c r="E81" s="46"/>
-      <c r="F81" s="63"/>
+      <c r="F81" s="57"/>
       <c r="G81" s="46"/>
       <c r="H81" s="46"/>
       <c r="I81" s="46"/>
@@ -12475,7 +12825,7 @@
       <c r="C82" s="46"/>
       <c r="D82" s="46"/>
       <c r="E82" s="46"/>
-      <c r="F82" s="63"/>
+      <c r="F82" s="57"/>
       <c r="G82" s="46"/>
       <c r="H82" s="46"/>
       <c r="I82" s="46"/>
@@ -12500,7 +12850,7 @@
       <c r="C83" s="46"/>
       <c r="D83" s="46"/>
       <c r="E83" s="46"/>
-      <c r="F83" s="63"/>
+      <c r="F83" s="57"/>
       <c r="G83" s="46"/>
       <c r="H83" s="46"/>
       <c r="I83" s="46"/>
@@ -12525,7 +12875,7 @@
       <c r="C84" s="46"/>
       <c r="D84" s="46"/>
       <c r="E84" s="46"/>
-      <c r="F84" s="63"/>
+      <c r="F84" s="57"/>
       <c r="G84" s="46"/>
       <c r="H84" s="46"/>
       <c r="I84" s="46"/>
@@ -12550,7 +12900,7 @@
       <c r="C85" s="46"/>
       <c r="D85" s="46"/>
       <c r="E85" s="46"/>
-      <c r="F85" s="63"/>
+      <c r="F85" s="57"/>
       <c r="G85" s="46"/>
       <c r="H85" s="46"/>
       <c r="I85" s="46"/>
@@ -12575,7 +12925,7 @@
       <c r="C86" s="46"/>
       <c r="D86" s="46"/>
       <c r="E86" s="46"/>
-      <c r="F86" s="63"/>
+      <c r="F86" s="57"/>
       <c r="G86" s="46"/>
       <c r="H86" s="46"/>
       <c r="I86" s="46"/>
@@ -12600,7 +12950,7 @@
       <c r="C87" s="46"/>
       <c r="D87" s="46"/>
       <c r="E87" s="46"/>
-      <c r="F87" s="63"/>
+      <c r="F87" s="57"/>
       <c r="G87" s="46"/>
       <c r="H87" s="46"/>
       <c r="I87" s="46"/>
@@ -12625,7 +12975,7 @@
       <c r="C88" s="46"/>
       <c r="D88" s="46"/>
       <c r="E88" s="46"/>
-      <c r="F88" s="63"/>
+      <c r="F88" s="57"/>
       <c r="G88" s="46"/>
       <c r="H88" s="46"/>
       <c r="I88" s="46"/>
@@ -12650,7 +13000,7 @@
       <c r="C89" s="46"/>
       <c r="D89" s="46"/>
       <c r="E89" s="46"/>
-      <c r="F89" s="63"/>
+      <c r="F89" s="57"/>
       <c r="G89" s="46"/>
       <c r="H89" s="46"/>
       <c r="I89" s="46"/>
@@ -12675,7 +13025,7 @@
       <c r="C90" s="46"/>
       <c r="D90" s="46"/>
       <c r="E90" s="46"/>
-      <c r="F90" s="63"/>
+      <c r="F90" s="57"/>
       <c r="G90" s="46"/>
       <c r="H90" s="46"/>
       <c r="I90" s="46"/>
@@ -12700,7 +13050,7 @@
       <c r="C91" s="46"/>
       <c r="D91" s="46"/>
       <c r="E91" s="46"/>
-      <c r="F91" s="63"/>
+      <c r="F91" s="57"/>
       <c r="G91" s="46"/>
       <c r="H91" s="46"/>
       <c r="I91" s="46"/>
@@ -12725,7 +13075,7 @@
       <c r="C92" s="46"/>
       <c r="D92" s="46"/>
       <c r="E92" s="46"/>
-      <c r="F92" s="63"/>
+      <c r="F92" s="57"/>
       <c r="G92" s="46"/>
       <c r="H92" s="46"/>
       <c r="I92" s="46"/>
@@ -12750,7 +13100,7 @@
       <c r="C93" s="46"/>
       <c r="D93" s="46"/>
       <c r="E93" s="46"/>
-      <c r="F93" s="63"/>
+      <c r="F93" s="57"/>
       <c r="G93" s="46"/>
       <c r="H93" s="46"/>
       <c r="I93" s="46"/>
@@ -12775,7 +13125,7 @@
       <c r="C94" s="46"/>
       <c r="D94" s="46"/>
       <c r="E94" s="46"/>
-      <c r="F94" s="63"/>
+      <c r="F94" s="57"/>
       <c r="G94" s="46"/>
       <c r="H94" s="46"/>
       <c r="I94" s="46"/>
@@ -12800,7 +13150,7 @@
       <c r="C95" s="46"/>
       <c r="D95" s="46"/>
       <c r="E95" s="46"/>
-      <c r="F95" s="63"/>
+      <c r="F95" s="57"/>
       <c r="G95" s="46"/>
       <c r="H95" s="46"/>
       <c r="I95" s="46"/>
@@ -12825,7 +13175,7 @@
       <c r="C96" s="46"/>
       <c r="D96" s="46"/>
       <c r="E96" s="46"/>
-      <c r="F96" s="63"/>
+      <c r="F96" s="57"/>
       <c r="G96" s="46"/>
       <c r="H96" s="46"/>
       <c r="I96" s="46"/>
@@ -12850,7 +13200,7 @@
       <c r="C97" s="46"/>
       <c r="D97" s="46"/>
       <c r="E97" s="46"/>
-      <c r="F97" s="63"/>
+      <c r="F97" s="57"/>
       <c r="G97" s="46"/>
       <c r="H97" s="46"/>
       <c r="I97" s="46"/>
@@ -12875,7 +13225,7 @@
       <c r="C98" s="46"/>
       <c r="D98" s="46"/>
       <c r="E98" s="46"/>
-      <c r="F98" s="63"/>
+      <c r="F98" s="57"/>
       <c r="G98" s="46"/>
       <c r="H98" s="46"/>
       <c r="I98" s="46"/>
@@ -12900,7 +13250,7 @@
       <c r="C99" s="46"/>
       <c r="D99" s="46"/>
       <c r="E99" s="46"/>
-      <c r="F99" s="63"/>
+      <c r="F99" s="57"/>
       <c r="G99" s="46"/>
       <c r="H99" s="46"/>
       <c r="I99" s="46"/>
@@ -12925,7 +13275,7 @@
       <c r="C100" s="46"/>
       <c r="D100" s="46"/>
       <c r="E100" s="46"/>
-      <c r="F100" s="63"/>
+      <c r="F100" s="57"/>
       <c r="G100" s="46"/>
       <c r="H100" s="46"/>
       <c r="I100" s="46"/>
@@ -12950,7 +13300,7 @@
       <c r="C101" s="46"/>
       <c r="D101" s="46"/>
       <c r="E101" s="46"/>
-      <c r="F101" s="63"/>
+      <c r="F101" s="57"/>
       <c r="G101" s="46"/>
       <c r="H101" s="46"/>
       <c r="I101" s="46"/>
@@ -12975,7 +13325,7 @@
       <c r="C102" s="46"/>
       <c r="D102" s="46"/>
       <c r="E102" s="46"/>
-      <c r="F102" s="63"/>
+      <c r="F102" s="57"/>
       <c r="G102" s="46"/>
       <c r="H102" s="46"/>
       <c r="I102" s="46"/>
@@ -13000,7 +13350,7 @@
       <c r="C103" s="46"/>
       <c r="D103" s="46"/>
       <c r="E103" s="46"/>
-      <c r="F103" s="63"/>
+      <c r="F103" s="57"/>
       <c r="G103" s="46"/>
       <c r="H103" s="46"/>
       <c r="I103" s="46"/>
@@ -13025,7 +13375,7 @@
       <c r="C104" s="46"/>
       <c r="D104" s="46"/>
       <c r="E104" s="46"/>
-      <c r="F104" s="63"/>
+      <c r="F104" s="57"/>
       <c r="G104" s="46"/>
       <c r="H104" s="46"/>
       <c r="I104" s="46"/>
@@ -13050,7 +13400,7 @@
       <c r="C105" s="46"/>
       <c r="D105" s="46"/>
       <c r="E105" s="46"/>
-      <c r="F105" s="63"/>
+      <c r="F105" s="57"/>
       <c r="G105" s="46"/>
       <c r="H105" s="46"/>
       <c r="I105" s="46"/>
@@ -13075,7 +13425,7 @@
       <c r="C106" s="46"/>
       <c r="D106" s="46"/>
       <c r="E106" s="46"/>
-      <c r="F106" s="63"/>
+      <c r="F106" s="57"/>
       <c r="G106" s="46"/>
       <c r="H106" s="46"/>
       <c r="I106" s="46"/>
@@ -13100,7 +13450,7 @@
       <c r="C107" s="46"/>
       <c r="D107" s="46"/>
       <c r="E107" s="46"/>
-      <c r="F107" s="63"/>
+      <c r="F107" s="57"/>
       <c r="G107" s="46"/>
       <c r="H107" s="46"/>
       <c r="I107" s="46"/>
@@ -13125,7 +13475,7 @@
       <c r="C108" s="46"/>
       <c r="D108" s="46"/>
       <c r="E108" s="46"/>
-      <c r="F108" s="63"/>
+      <c r="F108" s="57"/>
       <c r="G108" s="46"/>
       <c r="H108" s="46"/>
       <c r="I108" s="46"/>
@@ -13150,7 +13500,7 @@
       <c r="C109" s="46"/>
       <c r="D109" s="46"/>
       <c r="E109" s="46"/>
-      <c r="F109" s="63"/>
+      <c r="F109" s="57"/>
       <c r="G109" s="46"/>
       <c r="H109" s="46"/>
       <c r="I109" s="46"/>
@@ -13175,7 +13525,7 @@
       <c r="C110" s="46"/>
       <c r="D110" s="46"/>
       <c r="E110" s="46"/>
-      <c r="F110" s="63"/>
+      <c r="F110" s="57"/>
       <c r="G110" s="46"/>
       <c r="H110" s="46"/>
       <c r="I110" s="46"/>
@@ -13200,7 +13550,7 @@
       <c r="C111" s="46"/>
       <c r="D111" s="46"/>
       <c r="E111" s="46"/>
-      <c r="F111" s="63"/>
+      <c r="F111" s="57"/>
       <c r="G111" s="46"/>
       <c r="H111" s="46"/>
       <c r="I111" s="46"/>
@@ -13225,7 +13575,7 @@
       <c r="C112" s="46"/>
       <c r="D112" s="46"/>
       <c r="E112" s="46"/>
-      <c r="F112" s="63"/>
+      <c r="F112" s="57"/>
       <c r="G112" s="46"/>
       <c r="H112" s="46"/>
       <c r="I112" s="46"/>
@@ -13250,7 +13600,7 @@
       <c r="C113" s="46"/>
       <c r="D113" s="46"/>
       <c r="E113" s="46"/>
-      <c r="F113" s="63"/>
+      <c r="F113" s="57"/>
       <c r="G113" s="46"/>
       <c r="H113" s="46"/>
       <c r="I113" s="46"/>
@@ -13275,7 +13625,7 @@
       <c r="C114" s="46"/>
       <c r="D114" s="46"/>
       <c r="E114" s="46"/>
-      <c r="F114" s="63"/>
+      <c r="F114" s="57"/>
       <c r="G114" s="46"/>
       <c r="H114" s="46"/>
       <c r="I114" s="46"/>
@@ -13300,7 +13650,7 @@
       <c r="C115" s="46"/>
       <c r="D115" s="46"/>
       <c r="E115" s="46"/>
-      <c r="F115" s="63"/>
+      <c r="F115" s="57"/>
       <c r="G115" s="46"/>
       <c r="H115" s="46"/>
       <c r="I115" s="46"/>
@@ -13325,7 +13675,7 @@
       <c r="C116" s="46"/>
       <c r="D116" s="46"/>
       <c r="E116" s="46"/>
-      <c r="F116" s="63"/>
+      <c r="F116" s="57"/>
       <c r="G116" s="46"/>
       <c r="H116" s="46"/>
       <c r="I116" s="46"/>
@@ -13345,8 +13695,2412 @@
       <c r="W116" s="46"/>
     </row>
   </sheetData>
-  <autoFilter ref="D1:D126"/>
+  <autoFilter ref="A1:H19">
+    <sortState ref="A2:H19">
+      <sortCondition ref="D1:D19"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H83"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="5" width="0" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="16" width="13.85546875" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="94" t="s">
+        <v>149</v>
+      </c>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="96"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="81" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="82" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" s="83" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" s="83" t="s">
+        <v>113</v>
+      </c>
+      <c r="E2" s="83" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2" s="84" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="83" t="s">
+        <v>116</v>
+      </c>
+      <c r="H2" s="85" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="86">
+        <v>18</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" s="54">
+        <v>11003</v>
+      </c>
+      <c r="D3" s="54">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="26">
+        <v>7800</v>
+      </c>
+      <c r="G3" s="61">
+        <f>F3*0.14</f>
+        <v>1092</v>
+      </c>
+      <c r="H3" s="87">
+        <f>F3-G3</f>
+        <v>6708</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="86">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="54">
+        <v>11036</v>
+      </c>
+      <c r="D4" s="54">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4" s="26">
+        <v>4450</v>
+      </c>
+      <c r="G4" s="61">
+        <f>F4*0.14</f>
+        <v>623.00000000000011</v>
+      </c>
+      <c r="H4" s="87">
+        <f>F4-G4</f>
+        <v>3827</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="86">
+        <v>17</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="54">
+        <v>11009</v>
+      </c>
+      <c r="D5" s="54">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F5" s="26">
+        <v>9850</v>
+      </c>
+      <c r="G5" s="61">
+        <f>F5*0.14</f>
+        <v>1379.0000000000002</v>
+      </c>
+      <c r="H5" s="87">
+        <f>F5-G5</f>
+        <v>8471</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="86">
+        <v>16</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" s="54">
+        <v>11002</v>
+      </c>
+      <c r="D6" s="54">
+        <v>2</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F6" s="26">
+        <v>4100</v>
+      </c>
+      <c r="G6" s="61">
+        <f>F6*0.14</f>
+        <v>574</v>
+      </c>
+      <c r="H6" s="87">
+        <f>F6-G6</f>
+        <v>3526</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="86">
+        <v>15</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" s="54">
+        <v>11010</v>
+      </c>
+      <c r="D7" s="54">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F7" s="26">
+        <v>3600</v>
+      </c>
+      <c r="G7" s="61">
+        <f>F7*0.14</f>
+        <v>504.00000000000006</v>
+      </c>
+      <c r="H7" s="87">
+        <f>F7-G7</f>
+        <v>3096</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="86">
+        <v>1</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="54">
+        <v>11043</v>
+      </c>
+      <c r="D8" s="54">
+        <v>3</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="26">
+        <v>3850</v>
+      </c>
+      <c r="G8" s="61">
+        <f>F8*0.14</f>
+        <v>539</v>
+      </c>
+      <c r="H8" s="87">
+        <f>F8-G8</f>
+        <v>3311</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="86">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" s="54">
+        <v>11023</v>
+      </c>
+      <c r="D9" s="39">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F9" s="26">
+        <v>7200</v>
+      </c>
+      <c r="G9" s="61">
+        <f>F9*0.14</f>
+        <v>1008.0000000000001</v>
+      </c>
+      <c r="H9" s="87">
+        <f>F9-G9</f>
+        <v>6192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="86">
+        <v>13</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="54">
+        <v>11045</v>
+      </c>
+      <c r="D10" s="54">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F10" s="26">
+        <v>2800</v>
+      </c>
+      <c r="G10" s="61">
+        <f>F10*0.14</f>
+        <v>392.00000000000006</v>
+      </c>
+      <c r="H10" s="87">
+        <f>F10-G10</f>
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="86">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="54">
+        <v>11018</v>
+      </c>
+      <c r="D11" s="54">
+        <v>2</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" s="26">
+        <v>6840</v>
+      </c>
+      <c r="G11" s="61">
+        <f>F11*0.14</f>
+        <v>957.60000000000014</v>
+      </c>
+      <c r="H11" s="87">
+        <f>F11-G11</f>
+        <v>5882.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="86">
+        <v>3</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="54">
+        <v>11044</v>
+      </c>
+      <c r="D12" s="54">
+        <v>2</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F12" s="26">
+        <v>4200</v>
+      </c>
+      <c r="G12" s="61">
+        <f>F12*0.14</f>
+        <v>588</v>
+      </c>
+      <c r="H12" s="87">
+        <f>F12-G12</f>
+        <v>3612</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="86">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C13" s="54">
+        <v>11022</v>
+      </c>
+      <c r="D13" s="54">
+        <v>3</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F13" s="26">
+        <v>3740</v>
+      </c>
+      <c r="G13" s="61">
+        <f>F13*0.14</f>
+        <v>523.6</v>
+      </c>
+      <c r="H13" s="87">
+        <f>F13-G13</f>
+        <v>3216.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="86">
+        <v>11</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" s="54">
+        <v>11012</v>
+      </c>
+      <c r="D14" s="54">
+        <v>3</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14" s="26">
+        <v>3950</v>
+      </c>
+      <c r="G14" s="61">
+        <f>F14*0.14</f>
+        <v>553</v>
+      </c>
+      <c r="H14" s="87">
+        <f>F14-G14</f>
+        <v>3397</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="86">
+        <v>10</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="54">
+        <v>11033</v>
+      </c>
+      <c r="D15" s="54">
+        <v>2</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F15" s="26">
+        <v>3460</v>
+      </c>
+      <c r="G15" s="61">
+        <f>F15*0.14</f>
+        <v>484.40000000000003</v>
+      </c>
+      <c r="H15" s="87">
+        <f>F15-G15</f>
+        <v>2975.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="86">
+        <v>8</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C16" s="54">
+        <v>11019</v>
+      </c>
+      <c r="D16" s="80">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F16" s="26">
+        <v>6450</v>
+      </c>
+      <c r="G16" s="61">
+        <f>F16*0.14</f>
+        <v>903.00000000000011</v>
+      </c>
+      <c r="H16" s="87">
+        <f>F16-G16</f>
+        <v>5547</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="86">
+        <v>7</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C17" s="54">
+        <v>11025</v>
+      </c>
+      <c r="D17" s="54">
+        <v>2</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F17" s="26">
+        <v>7480</v>
+      </c>
+      <c r="G17" s="61">
+        <f>F17*0.14</f>
+        <v>1047.2</v>
+      </c>
+      <c r="H17" s="87">
+        <f>F17-G17</f>
+        <v>6432.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="86">
+        <v>2</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="54">
+        <v>11028</v>
+      </c>
+      <c r="D18" s="54">
+        <v>1</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F18" s="26">
+        <v>4500</v>
+      </c>
+      <c r="G18" s="61">
+        <f>F18*0.14</f>
+        <v>630.00000000000011</v>
+      </c>
+      <c r="H18" s="87">
+        <f>F18-G18</f>
+        <v>3870</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="86">
+        <v>6</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" s="54">
+        <v>11014</v>
+      </c>
+      <c r="D19" s="54">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F19" s="26">
+        <v>7600</v>
+      </c>
+      <c r="G19" s="61">
+        <f>F19*0.14</f>
+        <v>1064</v>
+      </c>
+      <c r="H19" s="87">
+        <f>F19-G19</f>
+        <v>6536</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="88">
+        <v>5</v>
+      </c>
+      <c r="B20" s="89" t="s">
+        <v>126</v>
+      </c>
+      <c r="C20" s="90">
+        <v>11017</v>
+      </c>
+      <c r="D20" s="90">
+        <v>3</v>
+      </c>
+      <c r="E20" s="89" t="s">
+        <v>127</v>
+      </c>
+      <c r="F20" s="91">
+        <v>6299</v>
+      </c>
+      <c r="G20" s="92">
+        <f>F20*0.14</f>
+        <v>881.86000000000013</v>
+      </c>
+      <c r="H20" s="93">
+        <f>F20-G20</f>
+        <v>5417.1399999999994</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="94" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" s="95"/>
+      <c r="C22" s="95"/>
+      <c r="D22" s="95"/>
+      <c r="E22" s="95"/>
+      <c r="F22" s="95"/>
+      <c r="G22" s="95"/>
+      <c r="H22" s="96"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="81" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="82" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" s="83" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" s="83" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" s="83" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" s="84" t="s">
+        <v>115</v>
+      </c>
+      <c r="G23" s="83" t="s">
+        <v>116</v>
+      </c>
+      <c r="H23" s="85" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="86">
+        <v>5</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C24" s="54">
+        <v>11017</v>
+      </c>
+      <c r="D24" s="54">
+        <v>3</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F24" s="26">
+        <v>6299</v>
+      </c>
+      <c r="G24" s="61">
+        <f>F24*0.14</f>
+        <v>881.86000000000013</v>
+      </c>
+      <c r="H24" s="87">
+        <f>F24-G24</f>
+        <v>5417.1399999999994</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="86">
+        <v>11</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="54">
+        <v>11012</v>
+      </c>
+      <c r="D25" s="54">
+        <v>3</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F25" s="26">
+        <v>3950</v>
+      </c>
+      <c r="G25" s="61">
+        <f>F25*0.14</f>
+        <v>553</v>
+      </c>
+      <c r="H25" s="87">
+        <f>F25-G25</f>
+        <v>3397</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="86">
+        <v>1</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" s="54">
+        <v>11043</v>
+      </c>
+      <c r="D26" s="54">
+        <v>3</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" s="26">
+        <v>3850</v>
+      </c>
+      <c r="G26" s="61">
+        <f>F26*0.14</f>
+        <v>539</v>
+      </c>
+      <c r="H26" s="87">
+        <f>F26-G26</f>
+        <v>3311</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="86">
+        <v>12</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" s="54">
+        <v>11022</v>
+      </c>
+      <c r="D27" s="54">
+        <v>3</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F27" s="26">
+        <v>3740</v>
+      </c>
+      <c r="G27" s="61">
+        <f>F27*0.14</f>
+        <v>523.6</v>
+      </c>
+      <c r="H27" s="87">
+        <f>F27-G27</f>
+        <v>3216.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="86">
+        <v>15</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" s="54">
+        <v>11010</v>
+      </c>
+      <c r="D28" s="54">
+        <v>3</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F28" s="26">
+        <v>3600</v>
+      </c>
+      <c r="G28" s="61">
+        <f>F28*0.14</f>
+        <v>504.00000000000006</v>
+      </c>
+      <c r="H28" s="87">
+        <f>F28-G28</f>
+        <v>3096</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="86">
+        <v>7</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C29" s="54">
+        <v>11025</v>
+      </c>
+      <c r="D29" s="54">
+        <v>2</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F29" s="26">
+        <v>7480</v>
+      </c>
+      <c r="G29" s="61">
+        <f>F29*0.14</f>
+        <v>1047.2</v>
+      </c>
+      <c r="H29" s="87">
+        <f>F29-G29</f>
+        <v>6432.8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="86">
+        <v>9</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C30" s="54">
+        <v>11018</v>
+      </c>
+      <c r="D30" s="54">
+        <v>2</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F30" s="26">
+        <v>6840</v>
+      </c>
+      <c r="G30" s="61">
+        <f>F30*0.14</f>
+        <v>957.60000000000014</v>
+      </c>
+      <c r="H30" s="87">
+        <f>F30-G30</f>
+        <v>5882.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="86">
+        <v>3</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C31" s="54">
+        <v>11044</v>
+      </c>
+      <c r="D31" s="54">
+        <v>2</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F31" s="26">
+        <v>4200</v>
+      </c>
+      <c r="G31" s="61">
+        <f>F31*0.14</f>
+        <v>588</v>
+      </c>
+      <c r="H31" s="87">
+        <f>F31-G31</f>
+        <v>3612</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="86">
+        <v>16</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C32" s="54">
+        <v>11002</v>
+      </c>
+      <c r="D32" s="54">
+        <v>2</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F32" s="26">
+        <v>4100</v>
+      </c>
+      <c r="G32" s="61">
+        <f>F32*0.14</f>
+        <v>574</v>
+      </c>
+      <c r="H32" s="87">
+        <f>F32-G32</f>
+        <v>3526</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="86">
+        <v>10</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C33" s="54">
+        <v>11033</v>
+      </c>
+      <c r="D33" s="54">
+        <v>2</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F33" s="26">
+        <v>3460</v>
+      </c>
+      <c r="G33" s="61">
+        <f>F33*0.14</f>
+        <v>484.40000000000003</v>
+      </c>
+      <c r="H33" s="87">
+        <f>F33-G33</f>
+        <v>2975.6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="86">
+        <v>17</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C34" s="54">
+        <v>11009</v>
+      </c>
+      <c r="D34" s="54">
+        <v>1</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F34" s="26">
+        <v>9850</v>
+      </c>
+      <c r="G34" s="61">
+        <f>F34*0.14</f>
+        <v>1379.0000000000002</v>
+      </c>
+      <c r="H34" s="87">
+        <f>F34-G34</f>
+        <v>8471</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="86">
+        <v>18</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C35" s="54">
+        <v>11003</v>
+      </c>
+      <c r="D35" s="54">
+        <v>1</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F35" s="26">
+        <v>7800</v>
+      </c>
+      <c r="G35" s="61">
+        <f>F35*0.14</f>
+        <v>1092</v>
+      </c>
+      <c r="H35" s="87">
+        <f>F35-G35</f>
+        <v>6708</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="86">
+        <v>6</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C36" s="54">
+        <v>11014</v>
+      </c>
+      <c r="D36" s="54">
+        <v>1</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F36" s="26">
+        <v>7600</v>
+      </c>
+      <c r="G36" s="61">
+        <f>F36*0.14</f>
+        <v>1064</v>
+      </c>
+      <c r="H36" s="87">
+        <f>F36-G36</f>
+        <v>6536</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="86">
+        <v>14</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C37" s="54">
+        <v>11023</v>
+      </c>
+      <c r="D37" s="62">
+        <v>1</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F37" s="26">
+        <v>7200</v>
+      </c>
+      <c r="G37" s="61">
+        <f>F37*0.14</f>
+        <v>1008.0000000000001</v>
+      </c>
+      <c r="H37" s="87">
+        <f>F37-G37</f>
+        <v>6192</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="86">
+        <v>8</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" s="54">
+        <v>11019</v>
+      </c>
+      <c r="D38" s="54">
+        <v>1</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F38" s="26">
+        <v>6450</v>
+      </c>
+      <c r="G38" s="61">
+        <f>F38*0.14</f>
+        <v>903.00000000000011</v>
+      </c>
+      <c r="H38" s="87">
+        <f>F38-G38</f>
+        <v>5547</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="86">
+        <v>2</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C39" s="54">
+        <v>11028</v>
+      </c>
+      <c r="D39" s="54">
+        <v>1</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F39" s="26">
+        <v>4500</v>
+      </c>
+      <c r="G39" s="61">
+        <f>F39*0.14</f>
+        <v>630.00000000000011</v>
+      </c>
+      <c r="H39" s="87">
+        <f>F39-G39</f>
+        <v>3870</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="86">
+        <v>4</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" s="54">
+        <v>11036</v>
+      </c>
+      <c r="D40" s="54">
+        <v>1</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F40" s="26">
+        <v>4450</v>
+      </c>
+      <c r="G40" s="61">
+        <f>F40*0.14</f>
+        <v>623.00000000000011</v>
+      </c>
+      <c r="H40" s="87">
+        <f>F40-G40</f>
+        <v>3827</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="88">
+        <v>13</v>
+      </c>
+      <c r="B41" s="89" t="s">
+        <v>137</v>
+      </c>
+      <c r="C41" s="90">
+        <v>11045</v>
+      </c>
+      <c r="D41" s="90">
+        <v>1</v>
+      </c>
+      <c r="E41" s="89" t="s">
+        <v>138</v>
+      </c>
+      <c r="F41" s="91">
+        <v>2800</v>
+      </c>
+      <c r="G41" s="92">
+        <f>F41*0.14</f>
+        <v>392.00000000000006</v>
+      </c>
+      <c r="H41" s="93">
+        <f>F41-G41</f>
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="94" t="s">
+        <v>150</v>
+      </c>
+      <c r="B43" s="95"/>
+      <c r="C43" s="95"/>
+      <c r="D43" s="95"/>
+      <c r="E43" s="95"/>
+      <c r="F43" s="95"/>
+      <c r="G43" s="95"/>
+      <c r="H43" s="96"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="81" t="s">
+        <v>68</v>
+      </c>
+      <c r="B44" s="82" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44" s="83" t="s">
+        <v>112</v>
+      </c>
+      <c r="D44" s="83" t="s">
+        <v>113</v>
+      </c>
+      <c r="E44" s="83" t="s">
+        <v>114</v>
+      </c>
+      <c r="F44" s="84" t="s">
+        <v>115</v>
+      </c>
+      <c r="G44" s="83" t="s">
+        <v>116</v>
+      </c>
+      <c r="H44" s="85" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="86">
+        <v>18</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C45" s="54">
+        <v>11003</v>
+      </c>
+      <c r="D45" s="54">
+        <v>1</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F45" s="26">
+        <v>7800</v>
+      </c>
+      <c r="G45" s="61">
+        <f>F45*0.14</f>
+        <v>1092</v>
+      </c>
+      <c r="H45" s="87">
+        <f>F45-G45</f>
+        <v>6708</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="86">
+        <v>4</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" s="54">
+        <v>11036</v>
+      </c>
+      <c r="D46" s="54">
+        <v>1</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F46" s="26">
+        <v>4450</v>
+      </c>
+      <c r="G46" s="61">
+        <f>F46*0.14</f>
+        <v>623.00000000000011</v>
+      </c>
+      <c r="H46" s="87">
+        <f>F46-G46</f>
+        <v>3827</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="86">
+        <v>17</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C47" s="54">
+        <v>11009</v>
+      </c>
+      <c r="D47" s="54">
+        <v>1</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F47" s="26">
+        <v>9850</v>
+      </c>
+      <c r="G47" s="61">
+        <f>F47*0.14</f>
+        <v>1379.0000000000002</v>
+      </c>
+      <c r="H47" s="87">
+        <f>F47-G47</f>
+        <v>8471</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="86">
+        <v>16</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C48" s="54">
+        <v>11002</v>
+      </c>
+      <c r="D48" s="54">
+        <v>2</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F48" s="26">
+        <v>4100</v>
+      </c>
+      <c r="G48" s="61">
+        <f>F48*0.14</f>
+        <v>574</v>
+      </c>
+      <c r="H48" s="87">
+        <f>F48-G48</f>
+        <v>3526</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="86">
+        <v>15</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C49" s="54">
+        <v>11010</v>
+      </c>
+      <c r="D49" s="54">
+        <v>3</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F49" s="26">
+        <v>3600</v>
+      </c>
+      <c r="G49" s="61">
+        <f>F49*0.14</f>
+        <v>504.00000000000006</v>
+      </c>
+      <c r="H49" s="87">
+        <f>F49-G49</f>
+        <v>3096</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="86">
+        <v>1</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C50" s="54">
+        <v>11043</v>
+      </c>
+      <c r="D50" s="54">
+        <v>3</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F50" s="26">
+        <v>3850</v>
+      </c>
+      <c r="G50" s="61">
+        <f>F50*0.14</f>
+        <v>539</v>
+      </c>
+      <c r="H50" s="87">
+        <f>F50-G50</f>
+        <v>3311</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="86">
+        <v>14</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C51" s="54">
+        <v>11023</v>
+      </c>
+      <c r="D51" s="39">
+        <v>1</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F51" s="26">
+        <v>7200</v>
+      </c>
+      <c r="G51" s="61">
+        <f>F51*0.14</f>
+        <v>1008.0000000000001</v>
+      </c>
+      <c r="H51" s="87">
+        <f>F51-G51</f>
+        <v>6192</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="86">
+        <v>13</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C52" s="54">
+        <v>11045</v>
+      </c>
+      <c r="D52" s="54">
+        <v>1</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F52" s="26">
+        <v>2800</v>
+      </c>
+      <c r="G52" s="61">
+        <f>F52*0.14</f>
+        <v>392.00000000000006</v>
+      </c>
+      <c r="H52" s="87">
+        <f>F52-G52</f>
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="86">
+        <v>9</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C53" s="54">
+        <v>11018</v>
+      </c>
+      <c r="D53" s="54">
+        <v>2</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F53" s="26">
+        <v>6840</v>
+      </c>
+      <c r="G53" s="61">
+        <f>F53*0.14</f>
+        <v>957.60000000000014</v>
+      </c>
+      <c r="H53" s="87">
+        <f>F53-G53</f>
+        <v>5882.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="86">
+        <v>3</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C54" s="54">
+        <v>11044</v>
+      </c>
+      <c r="D54" s="54">
+        <v>2</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F54" s="26">
+        <v>4200</v>
+      </c>
+      <c r="G54" s="61">
+        <f>F54*0.14</f>
+        <v>588</v>
+      </c>
+      <c r="H54" s="87">
+        <f>F54-G54</f>
+        <v>3612</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="86">
+        <v>12</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C55" s="54">
+        <v>11022</v>
+      </c>
+      <c r="D55" s="54">
+        <v>3</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F55" s="26">
+        <v>3740</v>
+      </c>
+      <c r="G55" s="61">
+        <f>F55*0.14</f>
+        <v>523.6</v>
+      </c>
+      <c r="H55" s="87">
+        <f>F55-G55</f>
+        <v>3216.4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="86">
+        <v>11</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C56" s="54">
+        <v>11012</v>
+      </c>
+      <c r="D56" s="54">
+        <v>3</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F56" s="26">
+        <v>3950</v>
+      </c>
+      <c r="G56" s="61">
+        <f>F56*0.14</f>
+        <v>553</v>
+      </c>
+      <c r="H56" s="87">
+        <f>F56-G56</f>
+        <v>3397</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="86">
+        <v>10</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C57" s="54">
+        <v>11033</v>
+      </c>
+      <c r="D57" s="54">
+        <v>2</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F57" s="26">
+        <v>3460</v>
+      </c>
+      <c r="G57" s="61">
+        <f>F57*0.14</f>
+        <v>484.40000000000003</v>
+      </c>
+      <c r="H57" s="87">
+        <f>F57-G57</f>
+        <v>2975.6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="86">
+        <v>8</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" s="54">
+        <v>11019</v>
+      </c>
+      <c r="D58" s="80">
+        <v>1</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F58" s="26">
+        <v>6450</v>
+      </c>
+      <c r="G58" s="61">
+        <f>F58*0.14</f>
+        <v>903.00000000000011</v>
+      </c>
+      <c r="H58" s="87">
+        <f>F58-G58</f>
+        <v>5547</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="86">
+        <v>7</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C59" s="54">
+        <v>11025</v>
+      </c>
+      <c r="D59" s="54">
+        <v>2</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F59" s="26">
+        <v>7480</v>
+      </c>
+      <c r="G59" s="61">
+        <f>F59*0.14</f>
+        <v>1047.2</v>
+      </c>
+      <c r="H59" s="87">
+        <f>F59-G59</f>
+        <v>6432.8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="86">
+        <v>2</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C60" s="54">
+        <v>11028</v>
+      </c>
+      <c r="D60" s="54">
+        <v>1</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F60" s="26">
+        <v>4500</v>
+      </c>
+      <c r="G60" s="61">
+        <f>F60*0.14</f>
+        <v>630.00000000000011</v>
+      </c>
+      <c r="H60" s="87">
+        <f>F60-G60</f>
+        <v>3870</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="86">
+        <v>6</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C61" s="54">
+        <v>11014</v>
+      </c>
+      <c r="D61" s="54">
+        <v>1</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F61" s="26">
+        <v>7600</v>
+      </c>
+      <c r="G61" s="61">
+        <f>F61*0.14</f>
+        <v>1064</v>
+      </c>
+      <c r="H61" s="87">
+        <f>F61-G61</f>
+        <v>6536</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="88">
+        <v>5</v>
+      </c>
+      <c r="B62" s="89" t="s">
+        <v>126</v>
+      </c>
+      <c r="C62" s="90">
+        <v>11017</v>
+      </c>
+      <c r="D62" s="90">
+        <v>3</v>
+      </c>
+      <c r="E62" s="89" t="s">
+        <v>127</v>
+      </c>
+      <c r="F62" s="91">
+        <v>6299</v>
+      </c>
+      <c r="G62" s="92">
+        <f>F62*0.14</f>
+        <v>881.86000000000013</v>
+      </c>
+      <c r="H62" s="93">
+        <f>F62-G62</f>
+        <v>5417.1399999999994</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="94" t="s">
+        <v>151</v>
+      </c>
+      <c r="B64" s="95"/>
+      <c r="C64" s="95"/>
+      <c r="D64" s="95"/>
+      <c r="E64" s="95"/>
+      <c r="F64" s="95"/>
+      <c r="G64" s="95"/>
+      <c r="H64" s="96"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="81" t="s">
+        <v>68</v>
+      </c>
+      <c r="B65" s="82" t="s">
+        <v>111</v>
+      </c>
+      <c r="C65" s="83" t="s">
+        <v>112</v>
+      </c>
+      <c r="D65" s="83" t="s">
+        <v>113</v>
+      </c>
+      <c r="E65" s="83" t="s">
+        <v>114</v>
+      </c>
+      <c r="F65" s="84" t="s">
+        <v>115</v>
+      </c>
+      <c r="G65" s="83" t="s">
+        <v>116</v>
+      </c>
+      <c r="H65" s="85" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="86">
+        <v>2</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C66" s="54">
+        <v>11028</v>
+      </c>
+      <c r="D66" s="54">
+        <v>1</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F66" s="26">
+        <v>4500</v>
+      </c>
+      <c r="G66" s="61">
+        <f>F66*0.14</f>
+        <v>630.00000000000011</v>
+      </c>
+      <c r="H66" s="87">
+        <f>F66-G66</f>
+        <v>3870</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="86">
+        <v>4</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C67" s="54">
+        <v>11036</v>
+      </c>
+      <c r="D67" s="54">
+        <v>1</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F67" s="26">
+        <v>4450</v>
+      </c>
+      <c r="G67" s="61">
+        <f>F67*0.14</f>
+        <v>623.00000000000011</v>
+      </c>
+      <c r="H67" s="87">
+        <f>F67-G67</f>
+        <v>3827</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="86">
+        <v>18</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C68" s="54">
+        <v>11003</v>
+      </c>
+      <c r="D68" s="54">
+        <v>1</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F68" s="26">
+        <v>7800</v>
+      </c>
+      <c r="G68" s="61">
+        <f>F68*0.14</f>
+        <v>1092</v>
+      </c>
+      <c r="H68" s="87">
+        <f>F68-G68</f>
+        <v>6708</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="86">
+        <v>17</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C69" s="54">
+        <v>11009</v>
+      </c>
+      <c r="D69" s="54">
+        <v>1</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F69" s="26">
+        <v>9850</v>
+      </c>
+      <c r="G69" s="61">
+        <f>F69*0.14</f>
+        <v>1379.0000000000002</v>
+      </c>
+      <c r="H69" s="87">
+        <f>F69-G69</f>
+        <v>8471</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="86">
+        <v>6</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C70" s="54">
+        <v>11014</v>
+      </c>
+      <c r="D70" s="54">
+        <v>1</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F70" s="26">
+        <v>7600</v>
+      </c>
+      <c r="G70" s="61">
+        <f>F70*0.14</f>
+        <v>1064</v>
+      </c>
+      <c r="H70" s="87">
+        <f>F70-G70</f>
+        <v>6536</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="86">
+        <v>8</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C71" s="54">
+        <v>11019</v>
+      </c>
+      <c r="D71" s="54">
+        <v>1</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F71" s="26">
+        <v>6450</v>
+      </c>
+      <c r="G71" s="61">
+        <f>F71*0.14</f>
+        <v>903.00000000000011</v>
+      </c>
+      <c r="H71" s="87">
+        <f>F71-G71</f>
+        <v>5547</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="86">
+        <v>13</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C72" s="54">
+        <v>11045</v>
+      </c>
+      <c r="D72" s="54">
+        <v>1</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F72" s="26">
+        <v>2800</v>
+      </c>
+      <c r="G72" s="61">
+        <f>F72*0.14</f>
+        <v>392.00000000000006</v>
+      </c>
+      <c r="H72" s="87">
+        <f>F72-G72</f>
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="86">
+        <v>14</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C73" s="54">
+        <v>11023</v>
+      </c>
+      <c r="D73" s="39">
+        <v>1</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F73" s="26">
+        <v>7200</v>
+      </c>
+      <c r="G73" s="61">
+        <f>F73*0.14</f>
+        <v>1008.0000000000001</v>
+      </c>
+      <c r="H73" s="87">
+        <f>F73-G73</f>
+        <v>6192</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="86">
+        <v>16</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C74" s="54">
+        <v>11002</v>
+      </c>
+      <c r="D74" s="54">
+        <v>2</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F74" s="26">
+        <v>4100</v>
+      </c>
+      <c r="G74" s="61">
+        <f>F74*0.14</f>
+        <v>574</v>
+      </c>
+      <c r="H74" s="87">
+        <f>F74-G74</f>
+        <v>3526</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="86">
+        <v>7</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C75" s="54">
+        <v>11025</v>
+      </c>
+      <c r="D75" s="54">
+        <v>2</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F75" s="26">
+        <v>7480</v>
+      </c>
+      <c r="G75" s="61">
+        <f>F75*0.14</f>
+        <v>1047.2</v>
+      </c>
+      <c r="H75" s="87">
+        <f>F75-G75</f>
+        <v>6432.8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="86">
+        <v>10</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C76" s="54">
+        <v>11033</v>
+      </c>
+      <c r="D76" s="54">
+        <v>2</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F76" s="26">
+        <v>3460</v>
+      </c>
+      <c r="G76" s="61">
+        <f>F76*0.14</f>
+        <v>484.40000000000003</v>
+      </c>
+      <c r="H76" s="87">
+        <f>F76-G76</f>
+        <v>2975.6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="86">
+        <v>9</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C77" s="54">
+        <v>11018</v>
+      </c>
+      <c r="D77" s="54">
+        <v>2</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F77" s="26">
+        <v>6840</v>
+      </c>
+      <c r="G77" s="61">
+        <f>F77*0.14</f>
+        <v>957.60000000000014</v>
+      </c>
+      <c r="H77" s="87">
+        <f>F77-G77</f>
+        <v>5882.4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="86">
+        <v>3</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C78" s="54">
+        <v>11044</v>
+      </c>
+      <c r="D78" s="54">
+        <v>2</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F78" s="26">
+        <v>4200</v>
+      </c>
+      <c r="G78" s="61">
+        <f>F78*0.14</f>
+        <v>588</v>
+      </c>
+      <c r="H78" s="87">
+        <f>F78-G78</f>
+        <v>3612</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="86">
+        <v>1</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C79" s="54">
+        <v>11043</v>
+      </c>
+      <c r="D79" s="80">
+        <v>3</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F79" s="26">
+        <v>3850</v>
+      </c>
+      <c r="G79" s="61">
+        <f>F79*0.14</f>
+        <v>539</v>
+      </c>
+      <c r="H79" s="87">
+        <f>F79-G79</f>
+        <v>3311</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="86">
+        <v>15</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C80" s="54">
+        <v>11010</v>
+      </c>
+      <c r="D80" s="54">
+        <v>3</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F80" s="26">
+        <v>3600</v>
+      </c>
+      <c r="G80" s="61">
+        <f>F80*0.14</f>
+        <v>504.00000000000006</v>
+      </c>
+      <c r="H80" s="87">
+        <f>F80-G80</f>
+        <v>3096</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="86">
+        <v>11</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C81" s="54">
+        <v>11012</v>
+      </c>
+      <c r="D81" s="54">
+        <v>3</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F81" s="26">
+        <v>3950</v>
+      </c>
+      <c r="G81" s="61">
+        <f>F81*0.14</f>
+        <v>553</v>
+      </c>
+      <c r="H81" s="87">
+        <f>F81-G81</f>
+        <v>3397</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="86">
+        <v>12</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C82" s="54">
+        <v>11022</v>
+      </c>
+      <c r="D82" s="54">
+        <v>3</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F82" s="26">
+        <v>3740</v>
+      </c>
+      <c r="G82" s="61">
+        <f>F82*0.14</f>
+        <v>523.6</v>
+      </c>
+      <c r="H82" s="87">
+        <f>F82-G82</f>
+        <v>3216.4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="88">
+        <v>5</v>
+      </c>
+      <c r="B83" s="89" t="s">
+        <v>126</v>
+      </c>
+      <c r="C83" s="90">
+        <v>11017</v>
+      </c>
+      <c r="D83" s="90">
+        <v>3</v>
+      </c>
+      <c r="E83" s="89" t="s">
+        <v>127</v>
+      </c>
+      <c r="F83" s="91">
+        <v>6299</v>
+      </c>
+      <c r="G83" s="92">
+        <f>F83*0.14</f>
+        <v>881.86000000000013</v>
+      </c>
+      <c r="H83" s="93">
+        <f>F83-G83</f>
+        <v>5417.1399999999994</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A66:H83">
+    <sortCondition ref="D23:D40"/>
+    <sortCondition ref="E23:E40"/>
+    <sortCondition ref="C23:C40"/>
+  </sortState>
+  <mergeCells count="4">
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="77" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+    </row>
+    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="53" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="97" t="s">
+        <v>156</v>
+      </c>
+      <c r="D2" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="98" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="100" t="s">
+        <v>157</v>
+      </c>
+      <c r="B3" s="99">
+        <v>8.5</v>
+      </c>
+      <c r="C3" s="56">
+        <v>125</v>
+      </c>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="100" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" s="99">
+        <v>8.5</v>
+      </c>
+      <c r="C4" s="56">
+        <v>240</v>
+      </c>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="100" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5" s="99">
+        <v>12.3</v>
+      </c>
+      <c r="C5" s="56">
+        <v>35</v>
+      </c>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="100" t="s">
+        <v>160</v>
+      </c>
+      <c r="B6" s="99">
+        <v>7.6</v>
+      </c>
+      <c r="C6" s="56">
+        <v>320</v>
+      </c>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="100" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7" s="99">
+        <v>7.8</v>
+      </c>
+      <c r="C7" s="56">
+        <v>450</v>
+      </c>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="56"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="100" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="99">
+        <v>24.5</v>
+      </c>
+      <c r="C8" s="56">
+        <v>450</v>
+      </c>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="100" t="s">
+        <v>163</v>
+      </c>
+      <c r="B9" s="99">
+        <v>8.5</v>
+      </c>
+      <c r="C9" s="56">
+        <v>500</v>
+      </c>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="100" t="s">
+        <v>164</v>
+      </c>
+      <c r="B10" s="99">
+        <v>8</v>
+      </c>
+      <c r="C10" s="56">
+        <v>370</v>
+      </c>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="100" t="s">
+        <v>165</v>
+      </c>
+      <c r="B11" s="99">
+        <v>31.2</v>
+      </c>
+      <c r="C11" s="56">
+        <v>270</v>
+      </c>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="100" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12" s="99">
+        <v>6.3</v>
+      </c>
+      <c r="C12" s="56">
+        <v>610</v>
+      </c>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="56"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="56"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -13363,15 +16117,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
@@ -13613,13 +16367,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -13797,22 +16551,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="57">
+      <c r="A1" s="72">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
+        <v>46149</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
@@ -13886,212 +16640,207 @@
       <c r="M4" s="35"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="55">
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="73">
         <f>COUNT(A3:M3)</f>
         <v>13</v>
       </c>
-      <c r="L5" s="55"/>
-      <c r="M5" s="55"/>
+      <c r="L5" s="73"/>
+      <c r="M5" s="73"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="55">
+      <c r="B6" s="71"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="73">
         <f>COUNTIF(A3:M3,"&gt;0")</f>
         <v>5</v>
       </c>
-      <c r="L6" s="55"/>
-      <c r="M6" s="55"/>
+      <c r="L6" s="73"/>
+      <c r="M6" s="73"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="54"/>
-      <c r="K7" s="55">
+      <c r="B7" s="71"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="73">
         <f>COUNTIF(A3:M3,"&lt;0")</f>
         <v>5</v>
       </c>
-      <c r="L7" s="55"/>
-      <c r="M7" s="55"/>
+      <c r="L7" s="73"/>
+      <c r="M7" s="73"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="54"/>
-      <c r="K8" s="55">
+      <c r="B8" s="71"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="71"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="71"/>
+      <c r="K8" s="73">
         <f>COUNTIF(A3:M3,"=0")</f>
         <v>3</v>
       </c>
-      <c r="L8" s="55"/>
-      <c r="M8" s="55"/>
+      <c r="L8" s="73"/>
+      <c r="M8" s="73"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="54" t="s">
+      <c r="A9" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="54"/>
-      <c r="K9" s="55">
+      <c r="B9" s="71"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="73">
         <f>MAX(A3:M3)</f>
         <v>30</v>
       </c>
-      <c r="L9" s="55"/>
-      <c r="M9" s="55"/>
+      <c r="L9" s="73"/>
+      <c r="M9" s="73"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="54"/>
-      <c r="K10" s="55">
+      <c r="B10" s="71"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="73">
         <f>MIN(A3:M3)</f>
         <v>-82</v>
       </c>
-      <c r="L10" s="55"/>
-      <c r="M10" s="55"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="73"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="54" t="s">
+      <c r="A11" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="56">
+      <c r="B11" s="71"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="74">
         <f>AVERAGE(A3:M3)</f>
         <v>-10.23076923076923</v>
       </c>
-      <c r="L11" s="56"/>
-      <c r="M11" s="56"/>
+      <c r="L11" s="74"/>
+      <c r="M11" s="74"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="54"/>
-      <c r="K12" s="55">
+      <c r="B12" s="71"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="71"/>
+      <c r="K12" s="73">
         <f>SUM(A3:M3)</f>
         <v>-133</v>
       </c>
-      <c r="L12" s="55"/>
-      <c r="M12" s="55"/>
+      <c r="L12" s="73"/>
+      <c r="M12" s="73"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="54" t="s">
+      <c r="A13" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="54"/>
-      <c r="K13" s="55">
+      <c r="B13" s="71"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="73">
         <f>SUMIF(A3:M3,"&gt;0")</f>
         <v>110</v>
       </c>
-      <c r="L13" s="55"/>
-      <c r="M13" s="55"/>
+      <c r="L13" s="73"/>
+      <c r="M13" s="73"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="54" t="s">
+      <c r="A14" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="54"/>
-      <c r="K14" s="55">
+      <c r="B14" s="71"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="73">
         <f>SUMIF(A3:M3,"&lt;0")</f>
         <v>-243</v>
       </c>
-      <c r="L14" s="55"/>
-      <c r="M14" s="55"/>
+      <c r="L14" s="73"/>
+      <c r="M14" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="K8:M8"/>
     <mergeCell ref="K14:M14"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A6:J6"/>
@@ -14108,6 +16857,11 @@
     <mergeCell ref="K11:M11"/>
     <mergeCell ref="K12:M12"/>
     <mergeCell ref="K13:M13"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="K8:M8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -14147,12 +16901,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -14309,12 +17063,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -14469,13 +17223,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">

--- a/Практические работы/exel/1.xlsx
+++ b/Практические работы/exel/1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="10" activeTab="14"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="11" activeTab="17"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -21,10 +21,14 @@
     <sheet name="Магазин" sheetId="12" r:id="rId12"/>
     <sheet name="Зарплата" sheetId="13" r:id="rId13"/>
     <sheet name="Сортировка" sheetId="14" r:id="rId14"/>
-    <sheet name="Лист3" sheetId="15" r:id="rId15"/>
+    <sheet name="Склад" sheetId="15" r:id="rId15"/>
+    <sheet name="Сортировка2" sheetId="16" r:id="rId16"/>
+    <sheet name="Поиск" sheetId="17" r:id="rId17"/>
+    <sheet name="Больница" sheetId="18" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">Зарплата!$A$1:$H$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">Склад!$A$2:$F$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">Сортировка!$A$44:$H$62</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -32,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="193">
   <si>
     <t>Учащиеся</t>
   </si>
@@ -531,6 +535,87 @@
   <si>
     <t>Зефир</t>
   </si>
+  <si>
+    <t>просроченно</t>
+  </si>
+  <si>
+    <t>не просроченно</t>
+  </si>
+  <si>
+    <t>все продукты с истекшим сроком реализации</t>
+  </si>
+  <si>
+    <t>все продукты, количество которых больше 300, а срок реализации еще не истек</t>
+  </si>
+  <si>
+    <t>все продукты, для которых общая сумма не меньше 300 р. и не больше 1000 р.</t>
+  </si>
+  <si>
+    <t>Все продукты сумма которых меньше 4000, и срок реализации истёк.</t>
+  </si>
+  <si>
+    <t>А</t>
+  </si>
+  <si>
+    <t>В</t>
+  </si>
+  <si>
+    <t>коэф.</t>
+  </si>
+  <si>
+    <t>зарплата сотрудников</t>
+  </si>
+  <si>
+    <t>кол-во сотрудников</t>
+  </si>
+  <si>
+    <t>сумм. з/плата</t>
+  </si>
+  <si>
+    <t>санитарка</t>
+  </si>
+  <si>
+    <t>медсестра</t>
+  </si>
+  <si>
+    <t>врач</t>
+  </si>
+  <si>
+    <t>завхоз</t>
+  </si>
+  <si>
+    <t>зав. отд.</t>
+  </si>
+  <si>
+    <t>зав. аптекой</t>
+  </si>
+  <si>
+    <t>глав. Врач.</t>
+  </si>
+  <si>
+    <t>зав. Больницей.</t>
+  </si>
+  <si>
+    <t>з/пл.</t>
+  </si>
+  <si>
+    <t>санитарки</t>
+  </si>
+  <si>
+    <t>суммарный месячный фондз/пл</t>
+  </si>
+  <si>
+    <t>Варианты штатного рассписания</t>
+  </si>
+  <si>
+    <t>Вариант</t>
+  </si>
+  <si>
+    <t>з/пл. санитарки</t>
+  </si>
+  <si>
+    <t>Количество сотр.</t>
+  </si>
 </sst>
 </file>
 
@@ -542,14 +627,22 @@
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="166" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0\ &quot;₽&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -607,7 +700,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -881,12 +974,175 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -897,7 +1153,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -948,10 +1204,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -982,7 +1238,7 @@
     <xf numFmtId="165" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1006,7 +1262,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
@@ -1017,22 +1273,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1042,10 +1295,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1075,52 +1328,28 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1147,6 +1376,174 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1156,17 +1553,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2092,11 +2543,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1078112400"/>
-        <c:axId val="1078103696"/>
+        <c:axId val="589918832"/>
+        <c:axId val="589914480"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1078112400"/>
+        <c:axId val="589918832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2139,7 +2590,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1078103696"/>
+        <c:crossAx val="589914480"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2147,7 +2598,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1078103696"/>
+        <c:axId val="589914480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2198,7 +2649,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1078112400"/>
+        <c:crossAx val="589918832"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2522,11 +2973,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1078098256"/>
-        <c:axId val="1078099888"/>
+        <c:axId val="589919920"/>
+        <c:axId val="589913392"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1078098256"/>
+        <c:axId val="589919920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2583,12 +3034,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1078099888"/>
+        <c:crossAx val="589913392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1078099888"/>
+        <c:axId val="589913392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2645,7 +3096,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1078098256"/>
+        <c:crossAx val="589919920"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2787,100 +3238,100 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>46149</c:v>
+                  <c:v>46174</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46150</c:v>
+                  <c:v>46175</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46151</c:v>
+                  <c:v>46176</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46152</c:v>
+                  <c:v>46177</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46153</c:v>
+                  <c:v>46178</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46154</c:v>
+                  <c:v>46179</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46155</c:v>
+                  <c:v>46180</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46156</c:v>
+                  <c:v>46181</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46157</c:v>
+                  <c:v>46182</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46158</c:v>
+                  <c:v>46183</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46159</c:v>
+                  <c:v>46184</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46160</c:v>
+                  <c:v>46185</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46161</c:v>
+                  <c:v>46186</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46162</c:v>
+                  <c:v>46187</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46163</c:v>
+                  <c:v>46188</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46164</c:v>
+                  <c:v>46189</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46165</c:v>
+                  <c:v>46190</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46166</c:v>
+                  <c:v>46191</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46167</c:v>
+                  <c:v>46192</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46168</c:v>
+                  <c:v>46193</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46169</c:v>
+                  <c:v>46194</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46170</c:v>
+                  <c:v>46195</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46171</c:v>
+                  <c:v>46196</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46172</c:v>
+                  <c:v>46197</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46173</c:v>
+                  <c:v>46198</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46174</c:v>
+                  <c:v>46199</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46175</c:v>
+                  <c:v>46200</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46176</c:v>
+                  <c:v>46201</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46177</c:v>
+                  <c:v>46202</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46178</c:v>
+                  <c:v>46203</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46179</c:v>
+                  <c:v>46204</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46180</c:v>
+                  <c:v>46205</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2892,100 +3343,100 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>-1.310530984569209E-2</c:v>
+                  <c:v>-0.52583651060970782</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.21490838694551764</c:v>
+                  <c:v>-0.31835581676799474</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.43163247335348037</c:v>
+                  <c:v>-9.4151191461850053E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.62568195630383827</c:v>
+                  <c:v>0.13499940307505373</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.78686298952995681</c:v>
+                  <c:v>0.35705818195524541</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.90670837874215282</c:v>
+                  <c:v>0.56035990897729226</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.97892238197578552</c:v>
+                  <c:v>0.73422469713462291</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.99971143876226276</c:v>
+                  <c:v>0.86951904658996171</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.96798345421102339</c:v>
+                  <c:v>0.95913564750187486</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.88540516915474554</c:v>
+                  <c:v>0.99836674266209258</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.75631460258748828</c:v>
+                  <c:v>0.98515143632913549</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.58749316598398182</c:v>
+                  <c:v>0.92018395761939165</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.38780942082950592</c:v>
+                  <c:v>0.80687719112291556</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.16775319358317134</c:v>
+                  <c:v>0.65118339057255836</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-6.1115477996687456E-2</c:v>
+                  <c:v>0.4612814938507932</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-0.28677361905753684</c:v>
+                  <c:v>0.247147465392664</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-0.49736691098015484</c:v>
+                  <c:v>2.0030236831431153E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-0.68183242481331585</c:v>
+                  <c:v>-0.20813922414073857</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-0.83047978127666067</c:v>
+                  <c:v>-0.42537467374442339</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-0.93550020769467779</c:v>
+                  <c:v>-0.62026425586851341</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-0.99137675001463232</c:v>
+                  <c:v>-0.78256999199219979</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-0.99517409053305272</c:v>
+                  <c:v>-0.90376560470981748</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-0.94669274659870006</c:v>
+                  <c:v>-0.97748442184166584</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-0.84847954987272134</c:v>
+                  <c:v>-0.99985383173658737</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-0.7056938556559238</c:v>
+                  <c:v>-0.96969872007675728</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-0.52583651060970782</c:v>
+                  <c:v>-0.88860320122307945</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-0.31835581676799474</c:v>
+                  <c:v>-0.76082740119863523</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-9.4151191461850053E-2</c:v>
+                  <c:v>-0.59308366389600731</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.13499940307505373</c:v>
+                  <c:v>-0.39418393689032771</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.35705818195524541</c:v>
+                  <c:v>-0.17457686043452625</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.56035990897729226</c:v>
+                  <c:v>5.4201122583866508E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.73422469713462291</c:v>
+                  <c:v>0.28013180138357635</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3025,100 +3476,100 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>46149</c:v>
+                  <c:v>46174</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46150</c:v>
+                  <c:v>46175</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46151</c:v>
+                  <c:v>46176</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46152</c:v>
+                  <c:v>46177</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46153</c:v>
+                  <c:v>46178</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46154</c:v>
+                  <c:v>46179</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46155</c:v>
+                  <c:v>46180</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46156</c:v>
+                  <c:v>46181</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46157</c:v>
+                  <c:v>46182</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46158</c:v>
+                  <c:v>46183</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46159</c:v>
+                  <c:v>46184</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46160</c:v>
+                  <c:v>46185</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46161</c:v>
+                  <c:v>46186</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46162</c:v>
+                  <c:v>46187</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46163</c:v>
+                  <c:v>46188</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46164</c:v>
+                  <c:v>46189</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46165</c:v>
+                  <c:v>46190</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46166</c:v>
+                  <c:v>46191</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46167</c:v>
+                  <c:v>46192</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46168</c:v>
+                  <c:v>46193</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46169</c:v>
+                  <c:v>46194</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46170</c:v>
+                  <c:v>46195</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46171</c:v>
+                  <c:v>46196</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46172</c:v>
+                  <c:v>46197</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46173</c:v>
+                  <c:v>46198</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46174</c:v>
+                  <c:v>46199</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46175</c:v>
+                  <c:v>46200</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46176</c:v>
+                  <c:v>46201</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46177</c:v>
+                  <c:v>46202</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46178</c:v>
+                  <c:v>46203</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46179</c:v>
+                  <c:v>46204</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46180</c:v>
+                  <c:v>46205</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3130,100 +3581,100 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>-0.77507420075117528</c:v>
+                  <c:v>0.62818870050726971</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.87983632219958507</c:v>
+                  <c:v>0.47110039354450584</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-0.95336724545588347</c:v>
+                  <c:v>0.29728962424790423</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-0.99305687273331744</c:v>
+                  <c:v>0.11292608400667616</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-0.99749635719846896</c:v>
+                  <c:v>-7.5445948291718232E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-0.96652811224653945</c:v>
+                  <c:v>-0.26113990592504333</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-0.90125140528845571</c:v>
+                  <c:v>-0.43756428471508418</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-0.80398333749508066</c:v>
+                  <c:v>-0.59845661901953251</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-0.678176594583485</c:v>
+                  <c:v>-0.73810577796530419</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-0.52829688821080356</c:v>
+                  <c:v>-0.85155469118820293</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-0.35966443839709628</c:v>
+                  <c:v>-0.93477630796747091</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-0.17826512380018317</c:v>
+                  <c:v>-0.98481654384348538</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9.4619966302357094E-3</c:v>
+                  <c:v>-0.99989914056818996</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.19685324834894555</c:v>
+                  <c:v>-0.97948871723501063</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.37725687900811905</c:v>
+                  <c:v>-0.92430977448173357</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.54426917305272549</c:v>
+                  <c:v>-0.83632097717908538</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.69196176184658986</c:v>
+                  <c:v>-0.71864562849084379</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.81509206060802042</c:v>
+                  <c:v>-0.57546080322497961</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.90928936234788582</c:v>
+                  <c:v>-0.41184907588051223</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.97120998310409967</c:v>
+                  <c:v>-0.233618106538173</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.99865595135611995</c:v>
+                  <c:v>-4.7094488662844047E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.990653028540603</c:v>
+                  <c:v>0.14110082345112784</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.94748529120921043</c:v>
+                  <c:v>0.32428753604189059</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.87068504727742035</c:v>
+                  <c:v>0.49596314360798688</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.76297844430097561</c:v>
+                  <c:v>0.65003374574072736</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.62818870050726971</c:v>
+                  <c:v>0.78103035986689673</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.47110039354450584</c:v>
+                  <c:v>0.88430305154567512</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.29728962424790423</c:v>
+                  <c:v>0.95618599132696547</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.11292608400667616</c:v>
+                  <c:v>0.99412757923300787</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-7.5445948291718232E-2</c:v>
+                  <c:v>0.99678101788672235</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-0.26113990592504333</c:v>
+                  <c:v>0.96405211923694689</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>-0.43756428471508418</c:v>
+                  <c:v>0.89710264791503724</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3263,100 +3714,100 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>46149</c:v>
+                  <c:v>46174</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46150</c:v>
+                  <c:v>46175</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46151</c:v>
+                  <c:v>46176</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46152</c:v>
+                  <c:v>46177</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46153</c:v>
+                  <c:v>46178</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46154</c:v>
+                  <c:v>46179</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46155</c:v>
+                  <c:v>46180</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46156</c:v>
+                  <c:v>46181</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46157</c:v>
+                  <c:v>46182</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46158</c:v>
+                  <c:v>46183</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46159</c:v>
+                  <c:v>46184</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46160</c:v>
+                  <c:v>46185</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46161</c:v>
+                  <c:v>46186</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46162</c:v>
+                  <c:v>46187</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46163</c:v>
+                  <c:v>46188</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46164</c:v>
+                  <c:v>46189</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46165</c:v>
+                  <c:v>46190</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46166</c:v>
+                  <c:v>46191</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46167</c:v>
+                  <c:v>46192</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46168</c:v>
+                  <c:v>46193</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46169</c:v>
+                  <c:v>46194</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46170</c:v>
+                  <c:v>46195</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46171</c:v>
+                  <c:v>46196</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46172</c:v>
+                  <c:v>46197</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46173</c:v>
+                  <c:v>46198</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46174</c:v>
+                  <c:v>46199</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46175</c:v>
+                  <c:v>46200</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46176</c:v>
+                  <c:v>46201</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46177</c:v>
+                  <c:v>46202</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>46178</c:v>
+                  <c:v>46203</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>46179</c:v>
+                  <c:v>46204</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>46180</c:v>
+                  <c:v>46205</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3368,100 +3819,100 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>0.29048494528460334</c:v>
+                  <c:v>0.53633344954541018</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.13423067729996951</c:v>
+                  <c:v>0.66402074105397657</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-2.5456701150971761E-2</c:v>
+                  <c:v>0.77472490617723277</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-0.18449299395978283</c:v>
+                  <c:v>0.86561455319766278</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-0.33881065730293269</c:v>
+                  <c:v>0.93436507044745232</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-0.48446283196870732</c:v>
+                  <c:v>0.97921808103946584</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-0.61772428900342335</c:v>
+                  <c:v>0.99902641546557536</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-0.7351867069089989</c:v>
+                  <c:v>0.9932834518286292</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-0.83384584355066604</c:v>
+                  <c:v>0.96213607330760054</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-0.91117837325136475</c:v>
+                  <c:v>0.90638091144318422</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-0.96520642386727651</c:v>
+                  <c:v>0.8274439713312276</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-0.99454816324394801</c:v>
+                  <c:v>0.727344159833197</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-0.99845314122621887</c:v>
+                  <c:v>0.60864164961178113</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-0.97682148332147356</c:v>
+                  <c:v>0.47437239965185901</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-0.93020644510950601</c:v>
+                  <c:v>0.32797050696232194</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-0.85980026206697457</c:v>
+                  <c:v>0.17318037543396361</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-0.76740365671946287</c:v>
+                  <c:v>1.3960948220479177E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-0.65537978299965449</c:v>
+                  <c:v>-0.14561554697809467</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-0.52659378575583204</c:v>
+                  <c:v>-0.30146775002173598</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-0.38433952123739623</c:v>
+                  <c:v>-0.44960955400115554</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-0.2322553127713233</c:v>
+                  <c:v>-0.58625205471056829</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-7.4230896288972642E-2</c:v>
+                  <c:v>-0.70790045640720956</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>8.5692064343151839E-2</c:v>
+                  <c:v>-0.81144345540330709</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.24342334771453841</c:v>
+                  <c:v>-0.89423281538727462</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.39492878718768215</c:v>
+                  <c:v>-0.95415109924224362</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.53633344954541018</c:v>
+                  <c:v>-0.9896658250359559</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.66402074105397657</c:v>
+                  <c:v>-0.99986866108717254</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.77472490617723277</c:v>
+                  <c:v>-0.98449865763421029</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.86561455319766278</c:v>
+                  <c:v>-0.94394892093869942</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.93436507044745232</c:v>
+                  <c:v>-0.87925655912087763</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.97921808103946584</c:v>
+                  <c:v>-0.79207615687948063</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.99902641546557536</c:v>
+                  <c:v>-0.68463745750039595</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3477,11 +3928,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1078106960"/>
-        <c:axId val="1078109680"/>
+        <c:axId val="589918288"/>
+        <c:axId val="589913936"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="1078106960"/>
+        <c:axId val="589918288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3524,14 +3975,14 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1078109680"/>
+        <c:crossAx val="589913936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="1078109680"/>
+        <c:axId val="589913936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3582,7 +4033,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1078106960"/>
+        <c:crossAx val="589918288"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8565,11 +9016,11 @@
       <c r="B1" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="77" t="s">
+      <c r="D1" s="146" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="146"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="37">
@@ -8591,7 +9042,7 @@
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="37">
         <f ca="1">TODAY()</f>
-        <v>46149</v>
+        <v>46174</v>
       </c>
       <c r="B3" s="38" t="s">
         <v>55</v>
@@ -8609,7 +9060,7 @@
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="35">
         <f ca="1">A3-A2</f>
-        <v>6428</v>
+        <v>6453</v>
       </c>
       <c r="B4" s="38" t="s">
         <v>56</v>
@@ -8625,13 +9076,13 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="147" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
+      <c r="B5" s="147"/>
+      <c r="C5" s="147"/>
+      <c r="D5" s="147"/>
+      <c r="E5" s="147"/>
     </row>
     <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
@@ -8653,705 +9104,705 @@
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="40">
         <f ca="1">A3</f>
-        <v>46149</v>
+        <v>46174</v>
       </c>
       <c r="B7" s="41">
         <f ca="1">A4</f>
-        <v>6428</v>
+        <v>6453</v>
       </c>
       <c r="C7" s="42">
         <f ca="1">SIN((2*PI()*A7-B7)/$D$2)</f>
-        <v>-1.310530984569209E-2</v>
+        <v>-0.52583651060970782</v>
       </c>
       <c r="D7" s="42">
         <f ca="1">SIN((2*PI()*A7-B7)/$D$3)</f>
-        <v>-0.77507420075117528</v>
+        <v>0.62818870050726971</v>
       </c>
       <c r="E7" s="42">
         <f ca="1">SIN((2*PI()*A7-B7)/$D$4)</f>
-        <v>0.29048494528460334</v>
+        <v>0.53633344954541018</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="40">
         <f ca="1">A7+1</f>
-        <v>46150</v>
+        <v>46175</v>
       </c>
       <c r="B8" s="41">
         <f ca="1">B7+1</f>
-        <v>6429</v>
+        <v>6454</v>
       </c>
       <c r="C8" s="42">
         <f ca="1">SIN((2*PI()*A8-B8)/$D$2)</f>
-        <v>0.21490838694551764</v>
+        <v>-0.31835581676799474</v>
       </c>
       <c r="D8" s="42">
         <f t="shared" ref="D8:D38" ca="1" si="0">SIN((2*PI()*A8-B8)/$D$3)</f>
-        <v>-0.87983632219958507</v>
+        <v>0.47110039354450584</v>
       </c>
       <c r="E8" s="42">
         <f t="shared" ref="E8:E38" ca="1" si="1">SIN((2*PI()*A8-B8)/$D$4)</f>
-        <v>0.13423067729996951</v>
+        <v>0.66402074105397657</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="40">
         <f t="shared" ref="A9:A38" ca="1" si="2">A8+1</f>
-        <v>46151</v>
+        <v>46176</v>
       </c>
       <c r="B9" s="41">
         <f t="shared" ref="B9:B38" ca="1" si="3">B8+1</f>
-        <v>6430</v>
+        <v>6455</v>
       </c>
       <c r="C9" s="42">
         <f t="shared" ref="C9:C38" ca="1" si="4">SIN((2*PI()*A9-B9)/$D$2)</f>
-        <v>0.43163247335348037</v>
+        <v>-9.4151191461850053E-2</v>
       </c>
       <c r="D9" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.95336724545588347</v>
+        <v>0.29728962424790423</v>
       </c>
       <c r="E9" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-2.5456701150971761E-2</v>
+        <v>0.77472490617723277</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46152</v>
+        <v>46177</v>
       </c>
       <c r="B10" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6431</v>
+        <v>6456</v>
       </c>
       <c r="C10" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.62568195630383827</v>
+        <v>0.13499940307505373</v>
       </c>
       <c r="D10" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.99305687273331744</v>
+        <v>0.11292608400667616</v>
       </c>
       <c r="E10" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.18449299395978283</v>
+        <v>0.86561455319766278</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46153</v>
+        <v>46178</v>
       </c>
       <c r="B11" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6432</v>
+        <v>6457</v>
       </c>
       <c r="C11" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.78686298952995681</v>
+        <v>0.35705818195524541</v>
       </c>
       <c r="D11" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.99749635719846896</v>
+        <v>-7.5445948291718232E-2</v>
       </c>
       <c r="E11" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.33881065730293269</v>
+        <v>0.93436507044745232</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46154</v>
+        <v>46179</v>
       </c>
       <c r="B12" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6433</v>
+        <v>6458</v>
       </c>
       <c r="C12" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.90670837874215282</v>
+        <v>0.56035990897729226</v>
       </c>
       <c r="D12" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.96652811224653945</v>
+        <v>-0.26113990592504333</v>
       </c>
       <c r="E12" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.48446283196870732</v>
+        <v>0.97921808103946584</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46155</v>
+        <v>46180</v>
       </c>
       <c r="B13" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6434</v>
+        <v>6459</v>
       </c>
       <c r="C13" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.97892238197578552</v>
+        <v>0.73422469713462291</v>
       </c>
       <c r="D13" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.90125140528845571</v>
+        <v>-0.43756428471508418</v>
       </c>
       <c r="E13" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.61772428900342335</v>
+        <v>0.99902641546557536</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46156</v>
+        <v>46181</v>
       </c>
       <c r="B14" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6435</v>
+        <v>6460</v>
       </c>
       <c r="C14" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.99971143876226276</v>
+        <v>0.86951904658996171</v>
       </c>
       <c r="D14" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.80398333749508066</v>
+        <v>-0.59845661901953251</v>
       </c>
       <c r="E14" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.7351867069089989</v>
+        <v>0.9932834518286292</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46157</v>
+        <v>46182</v>
       </c>
       <c r="B15" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6436</v>
+        <v>6461</v>
       </c>
       <c r="C15" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.96798345421102339</v>
+        <v>0.95913564750187486</v>
       </c>
       <c r="D15" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.678176594583485</v>
+        <v>-0.73810577796530419</v>
       </c>
       <c r="E15" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.83384584355066604</v>
+        <v>0.96213607330760054</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46158</v>
+        <v>46183</v>
       </c>
       <c r="B16" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="C16" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.88540516915474554</v>
+        <v>0.99836674266209258</v>
       </c>
       <c r="D16" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.52829688821080356</v>
+        <v>-0.85155469118820293</v>
       </c>
       <c r="E16" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.91117837325136475</v>
+        <v>0.90638091144318422</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46159</v>
+        <v>46184</v>
       </c>
       <c r="B17" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6438</v>
+        <v>6463</v>
       </c>
       <c r="C17" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.75631460258748828</v>
+        <v>0.98515143632913549</v>
       </c>
       <c r="D17" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.35966443839709628</v>
+        <v>-0.93477630796747091</v>
       </c>
       <c r="E17" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.96520642386727651</v>
+        <v>0.8274439713312276</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46160</v>
+        <v>46185</v>
       </c>
       <c r="B18" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6439</v>
+        <v>6464</v>
       </c>
       <c r="C18" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.58749316598398182</v>
+        <v>0.92018395761939165</v>
       </c>
       <c r="D18" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.17826512380018317</v>
+        <v>-0.98481654384348538</v>
       </c>
       <c r="E18" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.99454816324394801</v>
+        <v>0.727344159833197</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46161</v>
+        <v>46186</v>
       </c>
       <c r="B19" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6440</v>
+        <v>6465</v>
       </c>
       <c r="C19" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.38780942082950592</v>
+        <v>0.80687719112291556</v>
       </c>
       <c r="D19" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>9.4619966302357094E-3</v>
+        <v>-0.99989914056818996</v>
       </c>
       <c r="E19" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.99845314122621887</v>
+        <v>0.60864164961178113</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46162</v>
+        <v>46187</v>
       </c>
       <c r="B20" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6441</v>
+        <v>6466</v>
       </c>
       <c r="C20" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.16775319358317134</v>
+        <v>0.65118339057255836</v>
       </c>
       <c r="D20" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.19685324834894555</v>
+        <v>-0.97948871723501063</v>
       </c>
       <c r="E20" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.97682148332147356</v>
+        <v>0.47437239965185901</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46163</v>
+        <v>46188</v>
       </c>
       <c r="B21" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6442</v>
+        <v>6467</v>
       </c>
       <c r="C21" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-6.1115477996687456E-2</v>
+        <v>0.4612814938507932</v>
       </c>
       <c r="D21" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.37725687900811905</v>
+        <v>-0.92430977448173357</v>
       </c>
       <c r="E21" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.93020644510950601</v>
+        <v>0.32797050696232194</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <f ca="1">A21+1</f>
-        <v>46164</v>
+        <v>46189</v>
       </c>
       <c r="B22" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6443</v>
+        <v>6468</v>
       </c>
       <c r="C22" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.28677361905753684</v>
+        <v>0.247147465392664</v>
       </c>
       <c r="D22" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.54426917305272549</v>
+        <v>-0.83632097717908538</v>
       </c>
       <c r="E22" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.85980026206697457</v>
+        <v>0.17318037543396361</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46165</v>
+        <v>46190</v>
       </c>
       <c r="B23" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6444</v>
+        <v>6469</v>
       </c>
       <c r="C23" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.49736691098015484</v>
+        <v>2.0030236831431153E-2</v>
       </c>
       <c r="D23" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.69196176184658986</v>
+        <v>-0.71864562849084379</v>
       </c>
       <c r="E23" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.76740365671946287</v>
+        <v>1.3960948220479177E-2</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46166</v>
+        <v>46191</v>
       </c>
       <c r="B24" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6445</v>
+        <v>6470</v>
       </c>
       <c r="C24" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.68183242481331585</v>
+        <v>-0.20813922414073857</v>
       </c>
       <c r="D24" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.81509206060802042</v>
+        <v>-0.57546080322497961</v>
       </c>
       <c r="E24" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.65537978299965449</v>
+        <v>-0.14561554697809467</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="40">
         <f ca="1">A24+1</f>
-        <v>46167</v>
+        <v>46192</v>
       </c>
       <c r="B25" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6446</v>
+        <v>6471</v>
       </c>
       <c r="C25" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.83047978127666067</v>
+        <v>-0.42537467374442339</v>
       </c>
       <c r="D25" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.90928936234788582</v>
+        <v>-0.41184907588051223</v>
       </c>
       <c r="E25" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.52659378575583204</v>
+        <v>-0.30146775002173598</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46168</v>
+        <v>46193</v>
       </c>
       <c r="B26" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6447</v>
+        <v>6472</v>
       </c>
       <c r="C26" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.93550020769467779</v>
+        <v>-0.62026425586851341</v>
       </c>
       <c r="D26" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.97120998310409967</v>
+        <v>-0.233618106538173</v>
       </c>
       <c r="E26" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.38433952123739623</v>
+        <v>-0.44960955400115554</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46169</v>
+        <v>46194</v>
       </c>
       <c r="B27" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6448</v>
+        <v>6473</v>
       </c>
       <c r="C27" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.99137675001463232</v>
+        <v>-0.78256999199219979</v>
       </c>
       <c r="D27" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.99865595135611995</v>
+        <v>-4.7094488662844047E-2</v>
       </c>
       <c r="E27" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.2322553127713233</v>
+        <v>-0.58625205471056829</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46170</v>
+        <v>46195</v>
       </c>
       <c r="B28" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6449</v>
+        <v>6474</v>
       </c>
       <c r="C28" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.99517409053305272</v>
+        <v>-0.90376560470981748</v>
       </c>
       <c r="D28" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.990653028540603</v>
+        <v>0.14110082345112784</v>
       </c>
       <c r="E28" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>-7.4230896288972642E-2</v>
+        <v>-0.70790045640720956</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="40">
         <f ca="1">A28+1</f>
-        <v>46171</v>
+        <v>46196</v>
       </c>
       <c r="B29" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6450</v>
+        <v>6475</v>
       </c>
       <c r="C29" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.94669274659870006</v>
+        <v>-0.97748442184166584</v>
       </c>
       <c r="D29" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.94748529120921043</v>
+        <v>0.32428753604189059</v>
       </c>
       <c r="E29" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>8.5692064343151839E-2</v>
+        <v>-0.81144345540330709</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46172</v>
+        <v>46197</v>
       </c>
       <c r="B30" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6451</v>
+        <v>6476</v>
       </c>
       <c r="C30" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.84847954987272134</v>
+        <v>-0.99985383173658737</v>
       </c>
       <c r="D30" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.87068504727742035</v>
+        <v>0.49596314360798688</v>
       </c>
       <c r="E30" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>0.24342334771453841</v>
+        <v>-0.89423281538727462</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46173</v>
+        <v>46198</v>
       </c>
       <c r="B31" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6452</v>
+        <v>6477</v>
       </c>
       <c r="C31" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.7056938556559238</v>
+        <v>-0.96969872007675728</v>
       </c>
       <c r="D31" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.76297844430097561</v>
+        <v>0.65003374574072736</v>
       </c>
       <c r="E31" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>0.39492878718768215</v>
+        <v>-0.95415109924224362</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46174</v>
+        <v>46199</v>
       </c>
       <c r="B32" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6453</v>
+        <v>6478</v>
       </c>
       <c r="C32" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.52583651060970782</v>
+        <v>-0.88860320122307945</v>
       </c>
       <c r="D32" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.62818870050726971</v>
+        <v>0.78103035986689673</v>
       </c>
       <c r="E32" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>0.53633344954541018</v>
+        <v>-0.9896658250359559</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46175</v>
+        <v>46200</v>
       </c>
       <c r="B33" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6454</v>
+        <v>6479</v>
       </c>
       <c r="C33" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-0.31835581676799474</v>
+        <v>-0.76082740119863523</v>
       </c>
       <c r="D33" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.47110039354450584</v>
+        <v>0.88430305154567512</v>
       </c>
       <c r="E33" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>0.66402074105397657</v>
+        <v>-0.99986866108717254</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46176</v>
+        <v>46201</v>
       </c>
       <c r="B34" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6455</v>
+        <v>6480</v>
       </c>
       <c r="C34" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>-9.4151191461850053E-2</v>
+        <v>-0.59308366389600731</v>
       </c>
       <c r="D34" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.29728962424790423</v>
+        <v>0.95618599132696547</v>
       </c>
       <c r="E34" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77472490617723277</v>
+        <v>-0.98449865763421029</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46177</v>
+        <v>46202</v>
       </c>
       <c r="B35" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6456</v>
+        <v>6481</v>
       </c>
       <c r="C35" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.13499940307505373</v>
+        <v>-0.39418393689032771</v>
       </c>
       <c r="D35" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>0.11292608400667616</v>
+        <v>0.99412757923300787</v>
       </c>
       <c r="E35" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>0.86561455319766278</v>
+        <v>-0.94394892093869942</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46178</v>
+        <v>46203</v>
       </c>
       <c r="B36" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6457</v>
+        <v>6482</v>
       </c>
       <c r="C36" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.35705818195524541</v>
+        <v>-0.17457686043452625</v>
       </c>
       <c r="D36" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-7.5445948291718232E-2</v>
+        <v>0.99678101788672235</v>
       </c>
       <c r="E36" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93436507044745232</v>
+        <v>-0.87925655912087763</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46179</v>
+        <v>46204</v>
       </c>
       <c r="B37" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6458</v>
+        <v>6483</v>
       </c>
       <c r="C37" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.56035990897729226</v>
+        <v>5.4201122583866508E-2</v>
       </c>
       <c r="D37" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.26113990592504333</v>
+        <v>0.96405211923694689</v>
       </c>
       <c r="E37" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>0.97921808103946584</v>
+        <v>-0.79207615687948063</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="40">
         <f t="shared" ca="1" si="2"/>
-        <v>46180</v>
+        <v>46205</v>
       </c>
       <c r="B38" s="41">
         <f t="shared" ca="1" si="3"/>
-        <v>6459</v>
+        <v>6484</v>
       </c>
       <c r="C38" s="42">
         <f t="shared" ca="1" si="4"/>
-        <v>0.73422469713462291</v>
+        <v>0.28013180138357635</v>
       </c>
       <c r="D38" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.43756428471508418</v>
+        <v>0.89710264791503724</v>
       </c>
       <c r="E38" s="42">
         <f t="shared" ca="1" si="1"/>
-        <v>0.99902641546557536</v>
+        <v>-0.68463745750039595</v>
       </c>
     </row>
   </sheetData>
@@ -9375,12 +9826,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="148" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
+      <c r="B1" s="148"/>
+      <c r="C1" s="148"/>
+      <c r="D1" s="148"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="41"/>
@@ -9849,15 +10300,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="146" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
+      <c r="B1" s="148"/>
+      <c r="C1" s="148"/>
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="148"/>
+      <c r="G1" s="148"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
@@ -10033,16 +10484,16 @@
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
     <col min="3" max="3" width="14.5703125" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" style="58" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="57" customWidth="1"/>
     <col min="7" max="7" width="10.85546875" customWidth="1"/>
     <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="58" t="s">
         <v>111</v>
       </c>
       <c r="C1" s="52" t="s">
@@ -10054,7 +10505,7 @@
       <c r="E1" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="F1" s="60" t="s">
+      <c r="F1" s="59" t="s">
         <v>115</v>
       </c>
       <c r="G1" s="52" t="s">
@@ -10089,7 +10540,7 @@
       <c r="C2" s="51">
         <v>11014</v>
       </c>
-      <c r="D2" s="54">
+      <c r="D2" s="53">
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -10098,12 +10549,12 @@
       <c r="F2" s="26">
         <v>7600</v>
       </c>
-      <c r="G2" s="61">
-        <f>F2*0.14</f>
+      <c r="G2" s="60">
+        <f t="shared" ref="G2:G19" si="0">F2*0.14</f>
         <v>1064</v>
       </c>
-      <c r="H2" s="61">
-        <f>F2-G2</f>
+      <c r="H2" s="60">
+        <f t="shared" ref="H2:H19" si="1">F2-G2</f>
         <v>6536</v>
       </c>
       <c r="I2" s="46"/>
@@ -10141,12 +10592,12 @@
       <c r="F3" s="26">
         <v>4500</v>
       </c>
-      <c r="G3" s="61">
-        <f>F3*0.14</f>
+      <c r="G3" s="60">
+        <f t="shared" si="0"/>
         <v>630.00000000000011</v>
       </c>
-      <c r="H3" s="61">
-        <f>F3-G3</f>
+      <c r="H3" s="60">
+        <f t="shared" si="1"/>
         <v>3870</v>
       </c>
       <c r="I3" s="46"/>
@@ -10184,12 +10635,12 @@
       <c r="F4" s="26">
         <v>6450</v>
       </c>
-      <c r="G4" s="61">
-        <f>F4*0.14</f>
+      <c r="G4" s="60">
+        <f t="shared" si="0"/>
         <v>903.00000000000011</v>
       </c>
-      <c r="H4" s="61">
-        <f>F4-G4</f>
+      <c r="H4" s="60">
+        <f t="shared" si="1"/>
         <v>5547</v>
       </c>
       <c r="I4" s="46"/>
@@ -10227,12 +10678,12 @@
       <c r="F5" s="26">
         <v>2800</v>
       </c>
-      <c r="G5" s="61">
-        <f>F5*0.14</f>
+      <c r="G5" s="60">
+        <f t="shared" si="0"/>
         <v>392.00000000000006</v>
       </c>
-      <c r="H5" s="61">
-        <f>F5-G5</f>
+      <c r="H5" s="60">
+        <f t="shared" si="1"/>
         <v>2408</v>
       </c>
       <c r="I5" s="46"/>
@@ -10270,12 +10721,12 @@
       <c r="F6" s="26">
         <v>7200</v>
       </c>
-      <c r="G6" s="61">
-        <f>F6*0.14</f>
+      <c r="G6" s="60">
+        <f t="shared" si="0"/>
         <v>1008.0000000000001</v>
       </c>
-      <c r="H6" s="61">
-        <f>F6-G6</f>
+      <c r="H6" s="60">
+        <f t="shared" si="1"/>
         <v>6192</v>
       </c>
       <c r="I6" s="46"/>
@@ -10304,7 +10755,7 @@
       <c r="C7" s="51">
         <v>11009</v>
       </c>
-      <c r="D7" s="54">
+      <c r="D7" s="53">
         <v>1</v>
       </c>
       <c r="E7" s="5" t="s">
@@ -10313,12 +10764,12 @@
       <c r="F7" s="26">
         <v>9850</v>
       </c>
-      <c r="G7" s="61">
-        <f>F7*0.14</f>
+      <c r="G7" s="60">
+        <f t="shared" si="0"/>
         <v>1379.0000000000002</v>
       </c>
-      <c r="H7" s="61">
-        <f>F7-G7</f>
+      <c r="H7" s="60">
+        <f t="shared" si="1"/>
         <v>8471</v>
       </c>
       <c r="I7" s="46"/>
@@ -10356,12 +10807,12 @@
       <c r="F8" s="26">
         <v>4450</v>
       </c>
-      <c r="G8" s="61">
-        <f>F8*0.14</f>
+      <c r="G8" s="60">
+        <f t="shared" si="0"/>
         <v>623.00000000000011</v>
       </c>
-      <c r="H8" s="61">
-        <f>F8-G8</f>
+      <c r="H8" s="60">
+        <f t="shared" si="1"/>
         <v>3827</v>
       </c>
       <c r="I8" s="46"/>
@@ -10399,12 +10850,12 @@
       <c r="F9" s="26">
         <v>7800</v>
       </c>
-      <c r="G9" s="61">
-        <f>F9*0.14</f>
+      <c r="G9" s="60">
+        <f t="shared" si="0"/>
         <v>1092</v>
       </c>
-      <c r="H9" s="61">
-        <f>F9-G9</f>
+      <c r="H9" s="60">
+        <f t="shared" si="1"/>
         <v>6708</v>
       </c>
       <c r="I9" s="46"/>
@@ -10442,12 +10893,12 @@
       <c r="F10" s="26">
         <v>7480</v>
       </c>
-      <c r="G10" s="61">
-        <f>F10*0.14</f>
+      <c r="G10" s="60">
+        <f t="shared" si="0"/>
         <v>1047.2</v>
       </c>
-      <c r="H10" s="61">
-        <f>F10-G10</f>
+      <c r="H10" s="60">
+        <f t="shared" si="1"/>
         <v>6432.8</v>
       </c>
       <c r="I10" s="46"/>
@@ -10485,12 +10936,12 @@
       <c r="F11" s="26">
         <v>3460</v>
       </c>
-      <c r="G11" s="61">
-        <f>F11*0.14</f>
+      <c r="G11" s="60">
+        <f t="shared" si="0"/>
         <v>484.40000000000003</v>
       </c>
-      <c r="H11" s="61">
-        <f>F11-G11</f>
+      <c r="H11" s="60">
+        <f t="shared" si="1"/>
         <v>2975.6</v>
       </c>
       <c r="I11" s="46"/>
@@ -10528,12 +10979,12 @@
       <c r="F12" s="26">
         <v>4200</v>
       </c>
-      <c r="G12" s="61">
-        <f>F12*0.14</f>
+      <c r="G12" s="60">
+        <f t="shared" si="0"/>
         <v>588</v>
       </c>
-      <c r="H12" s="61">
-        <f>F12-G12</f>
+      <c r="H12" s="60">
+        <f t="shared" si="1"/>
         <v>3612</v>
       </c>
       <c r="I12" s="46"/>
@@ -10562,7 +11013,7 @@
       <c r="C13" s="51">
         <v>11018</v>
       </c>
-      <c r="D13" s="54">
+      <c r="D13" s="53">
         <v>2</v>
       </c>
       <c r="E13" s="5" t="s">
@@ -10571,12 +11022,12 @@
       <c r="F13" s="26">
         <v>6840</v>
       </c>
-      <c r="G13" s="61">
-        <f>F13*0.14</f>
+      <c r="G13" s="60">
+        <f t="shared" si="0"/>
         <v>957.60000000000014</v>
       </c>
-      <c r="H13" s="61">
-        <f>F13-G13</f>
+      <c r="H13" s="60">
+        <f t="shared" si="1"/>
         <v>5882.4</v>
       </c>
       <c r="I13" s="46"/>
@@ -10605,7 +11056,7 @@
       <c r="C14" s="51">
         <v>11002</v>
       </c>
-      <c r="D14" s="54">
+      <c r="D14" s="53">
         <v>2</v>
       </c>
       <c r="E14" s="5" t="s">
@@ -10614,12 +11065,12 @@
       <c r="F14" s="26">
         <v>4100</v>
       </c>
-      <c r="G14" s="61">
-        <f>F14*0.14</f>
+      <c r="G14" s="60">
+        <f t="shared" si="0"/>
         <v>574</v>
       </c>
-      <c r="H14" s="61">
-        <f>F14-G14</f>
+      <c r="H14" s="60">
+        <f t="shared" si="1"/>
         <v>3526</v>
       </c>
       <c r="I14" s="46"/>
@@ -10648,7 +11099,7 @@
       <c r="C15" s="51">
         <v>11017</v>
       </c>
-      <c r="D15" s="80">
+      <c r="D15" s="71">
         <v>3</v>
       </c>
       <c r="E15" s="5" t="s">
@@ -10657,12 +11108,12 @@
       <c r="F15" s="26">
         <v>6299</v>
       </c>
-      <c r="G15" s="61">
-        <f>F15*0.14</f>
+      <c r="G15" s="60">
+        <f t="shared" si="0"/>
         <v>881.86000000000013</v>
       </c>
-      <c r="H15" s="61">
-        <f>F15-G15</f>
+      <c r="H15" s="60">
+        <f t="shared" si="1"/>
         <v>5417.1399999999994</v>
       </c>
       <c r="I15" s="46"/>
@@ -10700,12 +11151,12 @@
       <c r="F16" s="26">
         <v>3950</v>
       </c>
-      <c r="G16" s="61">
-        <f>F16*0.14</f>
+      <c r="G16" s="60">
+        <f t="shared" si="0"/>
         <v>553</v>
       </c>
-      <c r="H16" s="61">
-        <f>F16-G16</f>
+      <c r="H16" s="60">
+        <f t="shared" si="1"/>
         <v>3397</v>
       </c>
       <c r="I16" s="46"/>
@@ -10743,12 +11194,12 @@
       <c r="F17" s="26">
         <v>3740</v>
       </c>
-      <c r="G17" s="61">
-        <f>F17*0.14</f>
+      <c r="G17" s="60">
+        <f t="shared" si="0"/>
         <v>523.6</v>
       </c>
-      <c r="H17" s="61">
-        <f>F17-G17</f>
+      <c r="H17" s="60">
+        <f t="shared" si="1"/>
         <v>3216.4</v>
       </c>
       <c r="I17" s="46"/>
@@ -10786,12 +11237,12 @@
       <c r="F18" s="26">
         <v>3850</v>
       </c>
-      <c r="G18" s="61">
-        <f>F18*0.14</f>
+      <c r="G18" s="60">
+        <f t="shared" si="0"/>
         <v>539</v>
       </c>
-      <c r="H18" s="61">
-        <f>F18-G18</f>
+      <c r="H18" s="60">
+        <f t="shared" si="1"/>
         <v>3311</v>
       </c>
       <c r="I18" s="46"/>
@@ -10820,7 +11271,7 @@
       <c r="C19" s="51">
         <v>11010</v>
       </c>
-      <c r="D19" s="54">
+      <c r="D19" s="53">
         <v>3</v>
       </c>
       <c r="E19" s="5" t="s">
@@ -10829,12 +11280,12 @@
       <c r="F19" s="26">
         <v>3600</v>
       </c>
-      <c r="G19" s="61">
-        <f>F19*0.14</f>
+      <c r="G19" s="60">
+        <f t="shared" si="0"/>
         <v>504.00000000000006</v>
       </c>
-      <c r="H19" s="61">
-        <f>F19-G19</f>
+      <c r="H19" s="60">
+        <f t="shared" si="1"/>
         <v>3096</v>
       </c>
       <c r="I19" s="46"/>
@@ -10859,7 +11310,7 @@
       <c r="C20" s="46"/>
       <c r="D20" s="46"/>
       <c r="E20" s="46"/>
-      <c r="F20" s="57"/>
+      <c r="F20" s="56"/>
       <c r="G20" s="46"/>
       <c r="H20" s="46"/>
       <c r="I20" s="46"/>
@@ -10884,7 +11335,7 @@
       <c r="C21" s="46"/>
       <c r="D21" s="46"/>
       <c r="E21" s="46"/>
-      <c r="F21" s="57"/>
+      <c r="F21" s="56"/>
       <c r="G21" s="46"/>
       <c r="H21" s="46"/>
       <c r="I21" s="46"/>
@@ -10904,10 +11355,10 @@
       <c r="W21" s="46"/>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="59" t="s">
+      <c r="B22" s="58" t="s">
         <v>111</v>
       </c>
       <c r="C22" s="52" t="s">
@@ -10919,7 +11370,7 @@
       <c r="E22" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="F22" s="60" t="s">
+      <c r="F22" s="59" t="s">
         <v>115</v>
       </c>
       <c r="G22" s="52" t="s">
@@ -10963,10 +11414,10 @@
       <c r="F23" s="26">
         <v>3850</v>
       </c>
-      <c r="G23" s="61">
+      <c r="G23" s="60">
         <v>539</v>
       </c>
-      <c r="H23" s="61">
+      <c r="H23" s="60">
         <v>3311</v>
       </c>
       <c r="I23" s="46"/>
@@ -11004,10 +11455,10 @@
       <c r="F24" s="26">
         <v>3460</v>
       </c>
-      <c r="G24" s="61">
+      <c r="G24" s="60">
         <v>484.40000000000003</v>
       </c>
-      <c r="H24" s="61">
+      <c r="H24" s="60">
         <v>2975.6</v>
       </c>
       <c r="I24" s="46"/>
@@ -11045,10 +11496,10 @@
       <c r="F25" s="26">
         <v>3950</v>
       </c>
-      <c r="G25" s="61">
+      <c r="G25" s="60">
         <v>553</v>
       </c>
-      <c r="H25" s="61">
+      <c r="H25" s="60">
         <v>3397</v>
       </c>
       <c r="I25" s="46"/>
@@ -11086,10 +11537,10 @@
       <c r="F26" s="26">
         <v>3740</v>
       </c>
-      <c r="G26" s="61">
+      <c r="G26" s="60">
         <v>523.6</v>
       </c>
-      <c r="H26" s="61">
+      <c r="H26" s="60">
         <v>3216.4</v>
       </c>
       <c r="I26" s="46"/>
@@ -11127,10 +11578,10 @@
       <c r="F27" s="26">
         <v>2800</v>
       </c>
-      <c r="G27" s="61">
+      <c r="G27" s="60">
         <v>392.00000000000006</v>
       </c>
-      <c r="H27" s="61">
+      <c r="H27" s="60">
         <v>2408</v>
       </c>
       <c r="I27" s="46"/>
@@ -11168,10 +11619,10 @@
       <c r="F28" s="26">
         <v>3600</v>
       </c>
-      <c r="G28" s="61">
+      <c r="G28" s="60">
         <v>504.00000000000006</v>
       </c>
-      <c r="H28" s="61">
+      <c r="H28" s="60">
         <v>3096</v>
       </c>
       <c r="I28" s="46"/>
@@ -11196,7 +11647,7 @@
       <c r="C29" s="46"/>
       <c r="D29" s="46"/>
       <c r="E29" s="46"/>
-      <c r="F29" s="57"/>
+      <c r="F29" s="56"/>
       <c r="G29" s="46"/>
       <c r="H29" s="46"/>
       <c r="I29" s="46"/>
@@ -11216,10 +11667,10 @@
       <c r="W29" s="46"/>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A30" s="59" t="s">
+      <c r="A30" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="59" t="s">
+      <c r="B30" s="58" t="s">
         <v>111</v>
       </c>
       <c r="C30" s="52" t="s">
@@ -11231,7 +11682,7 @@
       <c r="E30" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="F30" s="60" t="s">
+      <c r="F30" s="59" t="s">
         <v>115</v>
       </c>
       <c r="G30" s="52" t="s">
@@ -11275,10 +11726,10 @@
       <c r="F31" s="26">
         <v>4500</v>
       </c>
-      <c r="G31" s="61">
+      <c r="G31" s="60">
         <v>630.00000000000011</v>
       </c>
-      <c r="H31" s="61">
+      <c r="H31" s="60">
         <v>3870</v>
       </c>
       <c r="I31" s="46"/>
@@ -11316,10 +11767,10 @@
       <c r="F32" s="26">
         <v>4450</v>
       </c>
-      <c r="G32" s="61">
+      <c r="G32" s="60">
         <v>623.00000000000011</v>
       </c>
-      <c r="H32" s="61">
+      <c r="H32" s="60">
         <v>3827</v>
       </c>
       <c r="I32" s="46"/>
@@ -11357,10 +11808,10 @@
       <c r="F33" s="26">
         <v>7600</v>
       </c>
-      <c r="G33" s="61">
+      <c r="G33" s="60">
         <v>1064</v>
       </c>
-      <c r="H33" s="61">
+      <c r="H33" s="60">
         <v>6536</v>
       </c>
       <c r="I33" s="46"/>
@@ -11398,16 +11849,16 @@
       <c r="F34" s="26">
         <v>6450</v>
       </c>
-      <c r="G34" s="61">
+      <c r="G34" s="60">
         <v>903.00000000000011</v>
       </c>
-      <c r="H34" s="61">
+      <c r="H34" s="60">
         <v>5547</v>
       </c>
       <c r="I34" s="46"/>
       <c r="J34" s="46"/>
       <c r="K34" s="46"/>
-      <c r="L34" s="66"/>
+      <c r="L34" s="65"/>
       <c r="M34" s="46"/>
       <c r="N34" s="46"/>
       <c r="O34" s="46"/>
@@ -11439,10 +11890,10 @@
       <c r="F35" s="26">
         <v>2800</v>
       </c>
-      <c r="G35" s="61">
+      <c r="G35" s="60">
         <v>392.00000000000006</v>
       </c>
-      <c r="H35" s="61">
+      <c r="H35" s="60">
         <v>2408</v>
       </c>
       <c r="I35" s="46"/>
@@ -11471,7 +11922,7 @@
       <c r="C36" s="51">
         <v>11023</v>
       </c>
-      <c r="D36" s="62">
+      <c r="D36" s="61">
         <v>1</v>
       </c>
       <c r="E36" s="5" t="s">
@@ -11480,10 +11931,10 @@
       <c r="F36" s="26">
         <v>7200</v>
       </c>
-      <c r="G36" s="61">
+      <c r="G36" s="60">
         <v>1008.0000000000001</v>
       </c>
-      <c r="H36" s="61">
+      <c r="H36" s="60">
         <v>6192</v>
       </c>
       <c r="I36" s="46"/>
@@ -11521,10 +11972,10 @@
       <c r="F37" s="26">
         <v>9850</v>
       </c>
-      <c r="G37" s="61">
+      <c r="G37" s="60">
         <v>1379.0000000000002</v>
       </c>
-      <c r="H37" s="61">
+      <c r="H37" s="60">
         <v>8471</v>
       </c>
       <c r="I37" s="46"/>
@@ -11544,28 +11995,28 @@
       <c r="W37" s="46"/>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A38" s="63">
+      <c r="A38" s="62">
         <v>18</v>
       </c>
-      <c r="B38" s="64" t="s">
+      <c r="B38" s="63" t="s">
         <v>146</v>
       </c>
-      <c r="C38" s="63">
+      <c r="C38" s="62">
         <v>11003</v>
       </c>
-      <c r="D38" s="63">
+      <c r="D38" s="62">
         <v>1</v>
       </c>
-      <c r="E38" s="64" t="s">
+      <c r="E38" s="63" t="s">
         <v>147</v>
       </c>
       <c r="F38" s="30">
         <v>7800</v>
       </c>
-      <c r="G38" s="65">
+      <c r="G38" s="64">
         <v>1092</v>
       </c>
-      <c r="H38" s="65">
+      <c r="H38" s="64">
         <v>6708</v>
       </c>
       <c r="I38" s="46"/>
@@ -11586,14 +12037,14 @@
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" s="45"/>
-      <c r="B39" s="67"/>
+      <c r="B39" s="66"/>
       <c r="C39" s="45"/>
       <c r="D39" s="45"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="68"/>
-      <c r="G39" s="69"/>
-      <c r="H39" s="69"/>
-      <c r="I39" s="66"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="68"/>
+      <c r="H39" s="68"/>
+      <c r="I39" s="65"/>
       <c r="J39" s="46"/>
       <c r="K39" s="46"/>
       <c r="L39" s="46"/>
@@ -11610,10 +12061,10 @@
       <c r="W39" s="46"/>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A40" s="59" t="s">
+      <c r="A40" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="59" t="s">
+      <c r="B40" s="58" t="s">
         <v>111</v>
       </c>
       <c r="C40" s="52" t="s">
@@ -11625,7 +12076,7 @@
       <c r="E40" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="F40" s="60" t="s">
+      <c r="F40" s="59" t="s">
         <v>115</v>
       </c>
       <c r="G40" s="52" t="s">
@@ -11634,7 +12085,7 @@
       <c r="H40" s="52" t="s">
         <v>117</v>
       </c>
-      <c r="I40" s="66"/>
+      <c r="I40" s="65"/>
       <c r="J40" s="46"/>
       <c r="K40" s="46"/>
       <c r="L40" s="46"/>
@@ -11669,13 +12120,13 @@
       <c r="F41" s="26">
         <v>4200</v>
       </c>
-      <c r="G41" s="61">
+      <c r="G41" s="60">
         <v>588</v>
       </c>
-      <c r="H41" s="61">
+      <c r="H41" s="60">
         <v>3612</v>
       </c>
-      <c r="I41" s="66"/>
+      <c r="I41" s="65"/>
       <c r="J41" s="46"/>
       <c r="K41" s="46"/>
       <c r="L41" s="46"/>
@@ -11710,13 +12161,13 @@
       <c r="F42" s="26">
         <v>7480</v>
       </c>
-      <c r="G42" s="61">
+      <c r="G42" s="60">
         <v>1047.2</v>
       </c>
-      <c r="H42" s="61">
+      <c r="H42" s="60">
         <v>6432.8</v>
       </c>
-      <c r="I42" s="66"/>
+      <c r="I42" s="65"/>
       <c r="J42" s="46"/>
       <c r="K42" s="46"/>
       <c r="L42" s="46"/>
@@ -11751,10 +12202,10 @@
       <c r="F43" s="26">
         <v>6840</v>
       </c>
-      <c r="G43" s="61">
+      <c r="G43" s="60">
         <v>957.60000000000014</v>
       </c>
-      <c r="H43" s="61">
+      <c r="H43" s="60">
         <v>5882.4</v>
       </c>
       <c r="I43" s="46"/>
@@ -11792,10 +12243,10 @@
       <c r="F44" s="26">
         <v>3460</v>
       </c>
-      <c r="G44" s="61">
+      <c r="G44" s="60">
         <v>484.40000000000003</v>
       </c>
-      <c r="H44" s="61">
+      <c r="H44" s="60">
         <v>2975.6</v>
       </c>
       <c r="I44" s="46"/>
@@ -11833,10 +12284,10 @@
       <c r="F45" s="26">
         <v>4100</v>
       </c>
-      <c r="G45" s="61">
+      <c r="G45" s="60">
         <v>574</v>
       </c>
-      <c r="H45" s="61">
+      <c r="H45" s="60">
         <v>3526</v>
       </c>
       <c r="I45" s="46"/>
@@ -11861,7 +12312,7 @@
       <c r="C46" s="46"/>
       <c r="D46" s="46"/>
       <c r="E46" s="46"/>
-      <c r="F46" s="57"/>
+      <c r="F46" s="56"/>
       <c r="G46" s="46"/>
       <c r="H46" s="46"/>
       <c r="I46" s="46"/>
@@ -11881,28 +12332,28 @@
       <c r="W46" s="46"/>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A47" s="59" t="s">
+      <c r="A47" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="B47" s="59" t="s">
+      <c r="B47" s="58" t="s">
         <v>111</v>
       </c>
-      <c r="C47" s="55" t="s">
+      <c r="C47" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="D47" s="55" t="s">
+      <c r="D47" s="54" t="s">
         <v>113</v>
       </c>
-      <c r="E47" s="55" t="s">
+      <c r="E47" s="54" t="s">
         <v>114</v>
       </c>
-      <c r="F47" s="60" t="s">
+      <c r="F47" s="59" t="s">
         <v>115</v>
       </c>
-      <c r="G47" s="55" t="s">
+      <c r="G47" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="H47" s="55" t="s">
+      <c r="H47" s="54" t="s">
         <v>117</v>
       </c>
       <c r="I47" s="46"/>
@@ -11922,16 +12373,16 @@
       <c r="W47" s="46"/>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A48" s="54">
+      <c r="A48" s="53">
         <v>10</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C48" s="54">
+      <c r="C48" s="53">
         <v>11033</v>
       </c>
-      <c r="D48" s="54">
+      <c r="D48" s="53">
         <v>2</v>
       </c>
       <c r="E48" s="5" t="s">
@@ -11940,10 +12391,10 @@
       <c r="F48" s="26">
         <v>3460</v>
       </c>
-      <c r="G48" s="61">
+      <c r="G48" s="60">
         <v>484.40000000000003</v>
       </c>
-      <c r="H48" s="61">
+      <c r="H48" s="60">
         <v>2975.6</v>
       </c>
       <c r="I48" s="46"/>
@@ -11963,16 +12414,16 @@
       <c r="W48" s="46"/>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A49" s="54">
+      <c r="A49" s="53">
         <v>11</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C49" s="54">
+      <c r="C49" s="53">
         <v>11012</v>
       </c>
-      <c r="D49" s="54">
+      <c r="D49" s="53">
         <v>3</v>
       </c>
       <c r="E49" s="5" t="s">
@@ -11981,10 +12432,10 @@
       <c r="F49" s="26">
         <v>3950</v>
       </c>
-      <c r="G49" s="61">
+      <c r="G49" s="60">
         <v>553</v>
       </c>
-      <c r="H49" s="61">
+      <c r="H49" s="60">
         <v>3397</v>
       </c>
       <c r="I49" s="46"/>
@@ -12004,16 +12455,16 @@
       <c r="W49" s="46"/>
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A50" s="54">
+      <c r="A50" s="53">
         <v>12</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C50" s="54">
+      <c r="C50" s="53">
         <v>11022</v>
       </c>
-      <c r="D50" s="54">
+      <c r="D50" s="53">
         <v>3</v>
       </c>
       <c r="E50" s="5" t="s">
@@ -12022,10 +12473,10 @@
       <c r="F50" s="26">
         <v>3740</v>
       </c>
-      <c r="G50" s="61">
+      <c r="G50" s="60">
         <v>523.6</v>
       </c>
-      <c r="H50" s="61">
+      <c r="H50" s="60">
         <v>3216.4</v>
       </c>
       <c r="I50" s="46"/>
@@ -12050,7 +12501,7 @@
       <c r="C51" s="46"/>
       <c r="D51" s="46"/>
       <c r="E51" s="46"/>
-      <c r="F51" s="57"/>
+      <c r="F51" s="56"/>
       <c r="G51" s="46"/>
       <c r="H51" s="46"/>
       <c r="I51" s="46"/>
@@ -12075,7 +12526,7 @@
       <c r="C52" s="46"/>
       <c r="D52" s="46"/>
       <c r="E52" s="46"/>
-      <c r="F52" s="57"/>
+      <c r="F52" s="56"/>
       <c r="G52" s="46"/>
       <c r="H52" s="46"/>
       <c r="I52" s="46"/>
@@ -12100,7 +12551,7 @@
       <c r="C53" s="46"/>
       <c r="D53" s="46"/>
       <c r="E53" s="46"/>
-      <c r="F53" s="57"/>
+      <c r="F53" s="56"/>
       <c r="G53" s="46"/>
       <c r="H53" s="46"/>
       <c r="I53" s="46"/>
@@ -12125,7 +12576,7 @@
       <c r="C54" s="46"/>
       <c r="D54" s="46"/>
       <c r="E54" s="46"/>
-      <c r="F54" s="57"/>
+      <c r="F54" s="56"/>
       <c r="G54" s="46"/>
       <c r="H54" s="46"/>
       <c r="I54" s="46"/>
@@ -12150,7 +12601,7 @@
       <c r="C55" s="46"/>
       <c r="D55" s="46"/>
       <c r="E55" s="46"/>
-      <c r="F55" s="57"/>
+      <c r="F55" s="56"/>
       <c r="G55" s="46"/>
       <c r="H55" s="46"/>
       <c r="I55" s="46"/>
@@ -12175,7 +12626,7 @@
       <c r="C56" s="46"/>
       <c r="D56" s="46"/>
       <c r="E56" s="46"/>
-      <c r="F56" s="57"/>
+      <c r="F56" s="56"/>
       <c r="G56" s="46"/>
       <c r="H56" s="46"/>
       <c r="I56" s="46"/>
@@ -12200,7 +12651,7 @@
       <c r="C57" s="46"/>
       <c r="D57" s="46"/>
       <c r="E57" s="46"/>
-      <c r="F57" s="57"/>
+      <c r="F57" s="56"/>
       <c r="G57" s="46"/>
       <c r="H57" s="46"/>
       <c r="I57" s="46"/>
@@ -12225,7 +12676,7 @@
       <c r="C58" s="46"/>
       <c r="D58" s="46"/>
       <c r="E58" s="46"/>
-      <c r="F58" s="57"/>
+      <c r="F58" s="56"/>
       <c r="G58" s="46"/>
       <c r="H58" s="46"/>
       <c r="I58" s="46"/>
@@ -12250,7 +12701,7 @@
       <c r="C59" s="46"/>
       <c r="D59" s="46"/>
       <c r="E59" s="46"/>
-      <c r="F59" s="57"/>
+      <c r="F59" s="56"/>
       <c r="G59" s="46"/>
       <c r="H59" s="46"/>
       <c r="I59" s="46"/>
@@ -12275,7 +12726,7 @@
       <c r="C60" s="46"/>
       <c r="D60" s="46"/>
       <c r="E60" s="46"/>
-      <c r="F60" s="57"/>
+      <c r="F60" s="56"/>
       <c r="G60" s="46"/>
       <c r="H60" s="46"/>
       <c r="I60" s="46"/>
@@ -12300,7 +12751,7 @@
       <c r="C61" s="46"/>
       <c r="D61" s="46"/>
       <c r="E61" s="46"/>
-      <c r="F61" s="57"/>
+      <c r="F61" s="56"/>
       <c r="G61" s="46"/>
       <c r="H61" s="46"/>
       <c r="I61" s="46"/>
@@ -12325,7 +12776,7 @@
       <c r="C62" s="46"/>
       <c r="D62" s="46"/>
       <c r="E62" s="46"/>
-      <c r="F62" s="57"/>
+      <c r="F62" s="56"/>
       <c r="G62" s="46"/>
       <c r="H62" s="46"/>
       <c r="I62" s="46"/>
@@ -12350,7 +12801,7 @@
       <c r="C63" s="46"/>
       <c r="D63" s="46"/>
       <c r="E63" s="46"/>
-      <c r="F63" s="57"/>
+      <c r="F63" s="56"/>
       <c r="G63" s="46"/>
       <c r="H63" s="46"/>
       <c r="I63" s="46"/>
@@ -12375,7 +12826,7 @@
       <c r="C64" s="46"/>
       <c r="D64" s="46"/>
       <c r="E64" s="46"/>
-      <c r="F64" s="57"/>
+      <c r="F64" s="56"/>
       <c r="G64" s="46"/>
       <c r="H64" s="46"/>
       <c r="I64" s="46"/>
@@ -12400,7 +12851,7 @@
       <c r="C65" s="46"/>
       <c r="D65" s="46"/>
       <c r="E65" s="46"/>
-      <c r="F65" s="57"/>
+      <c r="F65" s="56"/>
       <c r="G65" s="46"/>
       <c r="H65" s="46"/>
       <c r="I65" s="46"/>
@@ -12425,7 +12876,7 @@
       <c r="C66" s="46"/>
       <c r="D66" s="46"/>
       <c r="E66" s="46"/>
-      <c r="F66" s="57"/>
+      <c r="F66" s="56"/>
       <c r="G66" s="46"/>
       <c r="H66" s="46"/>
       <c r="I66" s="46"/>
@@ -12450,7 +12901,7 @@
       <c r="C67" s="46"/>
       <c r="D67" s="46"/>
       <c r="E67" s="46"/>
-      <c r="F67" s="57"/>
+      <c r="F67" s="56"/>
       <c r="G67" s="46"/>
       <c r="H67" s="46"/>
       <c r="I67" s="46"/>
@@ -12475,7 +12926,7 @@
       <c r="C68" s="46"/>
       <c r="D68" s="46"/>
       <c r="E68" s="46"/>
-      <c r="F68" s="57"/>
+      <c r="F68" s="56"/>
       <c r="G68" s="46"/>
       <c r="H68" s="46"/>
       <c r="I68" s="46"/>
@@ -12500,7 +12951,7 @@
       <c r="C69" s="46"/>
       <c r="D69" s="46"/>
       <c r="E69" s="46"/>
-      <c r="F69" s="57"/>
+      <c r="F69" s="56"/>
       <c r="G69" s="46"/>
       <c r="H69" s="46"/>
       <c r="I69" s="46"/>
@@ -12525,7 +12976,7 @@
       <c r="C70" s="46"/>
       <c r="D70" s="46"/>
       <c r="E70" s="46"/>
-      <c r="F70" s="57"/>
+      <c r="F70" s="56"/>
       <c r="G70" s="46"/>
       <c r="H70" s="46"/>
       <c r="I70" s="46"/>
@@ -12550,7 +13001,7 @@
       <c r="C71" s="46"/>
       <c r="D71" s="46"/>
       <c r="E71" s="46"/>
-      <c r="F71" s="57"/>
+      <c r="F71" s="56"/>
       <c r="G71" s="46"/>
       <c r="H71" s="46"/>
       <c r="I71" s="46"/>
@@ -12575,7 +13026,7 @@
       <c r="C72" s="46"/>
       <c r="D72" s="46"/>
       <c r="E72" s="46"/>
-      <c r="F72" s="57"/>
+      <c r="F72" s="56"/>
       <c r="G72" s="46"/>
       <c r="H72" s="46"/>
       <c r="I72" s="46"/>
@@ -12600,7 +13051,7 @@
       <c r="C73" s="46"/>
       <c r="D73" s="46"/>
       <c r="E73" s="46"/>
-      <c r="F73" s="57"/>
+      <c r="F73" s="56"/>
       <c r="G73" s="46"/>
       <c r="H73" s="46"/>
       <c r="I73" s="46"/>
@@ -12625,7 +13076,7 @@
       <c r="C74" s="46"/>
       <c r="D74" s="46"/>
       <c r="E74" s="46"/>
-      <c r="F74" s="57"/>
+      <c r="F74" s="56"/>
       <c r="G74" s="46"/>
       <c r="H74" s="46"/>
       <c r="I74" s="46"/>
@@ -12650,7 +13101,7 @@
       <c r="C75" s="46"/>
       <c r="D75" s="46"/>
       <c r="E75" s="46"/>
-      <c r="F75" s="57"/>
+      <c r="F75" s="56"/>
       <c r="G75" s="46"/>
       <c r="H75" s="46"/>
       <c r="I75" s="46"/>
@@ -12675,7 +13126,7 @@
       <c r="C76" s="46"/>
       <c r="D76" s="46"/>
       <c r="E76" s="46"/>
-      <c r="F76" s="57"/>
+      <c r="F76" s="56"/>
       <c r="G76" s="46"/>
       <c r="H76" s="46"/>
       <c r="I76" s="46"/>
@@ -12700,7 +13151,7 @@
       <c r="C77" s="46"/>
       <c r="D77" s="46"/>
       <c r="E77" s="46"/>
-      <c r="F77" s="57"/>
+      <c r="F77" s="56"/>
       <c r="G77" s="46"/>
       <c r="H77" s="46"/>
       <c r="I77" s="46"/>
@@ -12725,7 +13176,7 @@
       <c r="C78" s="46"/>
       <c r="D78" s="46"/>
       <c r="E78" s="46"/>
-      <c r="F78" s="57"/>
+      <c r="F78" s="56"/>
       <c r="G78" s="46"/>
       <c r="H78" s="46"/>
       <c r="I78" s="46"/>
@@ -12750,7 +13201,7 @@
       <c r="C79" s="46"/>
       <c r="D79" s="46"/>
       <c r="E79" s="46"/>
-      <c r="F79" s="57"/>
+      <c r="F79" s="56"/>
       <c r="G79" s="46"/>
       <c r="H79" s="46"/>
       <c r="I79" s="46"/>
@@ -12775,7 +13226,7 @@
       <c r="C80" s="46"/>
       <c r="D80" s="46"/>
       <c r="E80" s="46"/>
-      <c r="F80" s="57"/>
+      <c r="F80" s="56"/>
       <c r="G80" s="46"/>
       <c r="H80" s="46"/>
       <c r="I80" s="46"/>
@@ -12800,7 +13251,7 @@
       <c r="C81" s="46"/>
       <c r="D81" s="46"/>
       <c r="E81" s="46"/>
-      <c r="F81" s="57"/>
+      <c r="F81" s="56"/>
       <c r="G81" s="46"/>
       <c r="H81" s="46"/>
       <c r="I81" s="46"/>
@@ -12825,7 +13276,7 @@
       <c r="C82" s="46"/>
       <c r="D82" s="46"/>
       <c r="E82" s="46"/>
-      <c r="F82" s="57"/>
+      <c r="F82" s="56"/>
       <c r="G82" s="46"/>
       <c r="H82" s="46"/>
       <c r="I82" s="46"/>
@@ -12850,7 +13301,7 @@
       <c r="C83" s="46"/>
       <c r="D83" s="46"/>
       <c r="E83" s="46"/>
-      <c r="F83" s="57"/>
+      <c r="F83" s="56"/>
       <c r="G83" s="46"/>
       <c r="H83" s="46"/>
       <c r="I83" s="46"/>
@@ -12875,7 +13326,7 @@
       <c r="C84" s="46"/>
       <c r="D84" s="46"/>
       <c r="E84" s="46"/>
-      <c r="F84" s="57"/>
+      <c r="F84" s="56"/>
       <c r="G84" s="46"/>
       <c r="H84" s="46"/>
       <c r="I84" s="46"/>
@@ -12900,7 +13351,7 @@
       <c r="C85" s="46"/>
       <c r="D85" s="46"/>
       <c r="E85" s="46"/>
-      <c r="F85" s="57"/>
+      <c r="F85" s="56"/>
       <c r="G85" s="46"/>
       <c r="H85" s="46"/>
       <c r="I85" s="46"/>
@@ -12925,7 +13376,7 @@
       <c r="C86" s="46"/>
       <c r="D86" s="46"/>
       <c r="E86" s="46"/>
-      <c r="F86" s="57"/>
+      <c r="F86" s="56"/>
       <c r="G86" s="46"/>
       <c r="H86" s="46"/>
       <c r="I86" s="46"/>
@@ -12950,7 +13401,7 @@
       <c r="C87" s="46"/>
       <c r="D87" s="46"/>
       <c r="E87" s="46"/>
-      <c r="F87" s="57"/>
+      <c r="F87" s="56"/>
       <c r="G87" s="46"/>
       <c r="H87" s="46"/>
       <c r="I87" s="46"/>
@@ -12975,7 +13426,7 @@
       <c r="C88" s="46"/>
       <c r="D88" s="46"/>
       <c r="E88" s="46"/>
-      <c r="F88" s="57"/>
+      <c r="F88" s="56"/>
       <c r="G88" s="46"/>
       <c r="H88" s="46"/>
       <c r="I88" s="46"/>
@@ -13000,7 +13451,7 @@
       <c r="C89" s="46"/>
       <c r="D89" s="46"/>
       <c r="E89" s="46"/>
-      <c r="F89" s="57"/>
+      <c r="F89" s="56"/>
       <c r="G89" s="46"/>
       <c r="H89" s="46"/>
       <c r="I89" s="46"/>
@@ -13025,7 +13476,7 @@
       <c r="C90" s="46"/>
       <c r="D90" s="46"/>
       <c r="E90" s="46"/>
-      <c r="F90" s="57"/>
+      <c r="F90" s="56"/>
       <c r="G90" s="46"/>
       <c r="H90" s="46"/>
       <c r="I90" s="46"/>
@@ -13050,7 +13501,7 @@
       <c r="C91" s="46"/>
       <c r="D91" s="46"/>
       <c r="E91" s="46"/>
-      <c r="F91" s="57"/>
+      <c r="F91" s="56"/>
       <c r="G91" s="46"/>
       <c r="H91" s="46"/>
       <c r="I91" s="46"/>
@@ -13075,7 +13526,7 @@
       <c r="C92" s="46"/>
       <c r="D92" s="46"/>
       <c r="E92" s="46"/>
-      <c r="F92" s="57"/>
+      <c r="F92" s="56"/>
       <c r="G92" s="46"/>
       <c r="H92" s="46"/>
       <c r="I92" s="46"/>
@@ -13100,7 +13551,7 @@
       <c r="C93" s="46"/>
       <c r="D93" s="46"/>
       <c r="E93" s="46"/>
-      <c r="F93" s="57"/>
+      <c r="F93" s="56"/>
       <c r="G93" s="46"/>
       <c r="H93" s="46"/>
       <c r="I93" s="46"/>
@@ -13125,7 +13576,7 @@
       <c r="C94" s="46"/>
       <c r="D94" s="46"/>
       <c r="E94" s="46"/>
-      <c r="F94" s="57"/>
+      <c r="F94" s="56"/>
       <c r="G94" s="46"/>
       <c r="H94" s="46"/>
       <c r="I94" s="46"/>
@@ -13150,7 +13601,7 @@
       <c r="C95" s="46"/>
       <c r="D95" s="46"/>
       <c r="E95" s="46"/>
-      <c r="F95" s="57"/>
+      <c r="F95" s="56"/>
       <c r="G95" s="46"/>
       <c r="H95" s="46"/>
       <c r="I95" s="46"/>
@@ -13175,7 +13626,7 @@
       <c r="C96" s="46"/>
       <c r="D96" s="46"/>
       <c r="E96" s="46"/>
-      <c r="F96" s="57"/>
+      <c r="F96" s="56"/>
       <c r="G96" s="46"/>
       <c r="H96" s="46"/>
       <c r="I96" s="46"/>
@@ -13200,7 +13651,7 @@
       <c r="C97" s="46"/>
       <c r="D97" s="46"/>
       <c r="E97" s="46"/>
-      <c r="F97" s="57"/>
+      <c r="F97" s="56"/>
       <c r="G97" s="46"/>
       <c r="H97" s="46"/>
       <c r="I97" s="46"/>
@@ -13225,7 +13676,7 @@
       <c r="C98" s="46"/>
       <c r="D98" s="46"/>
       <c r="E98" s="46"/>
-      <c r="F98" s="57"/>
+      <c r="F98" s="56"/>
       <c r="G98" s="46"/>
       <c r="H98" s="46"/>
       <c r="I98" s="46"/>
@@ -13250,7 +13701,7 @@
       <c r="C99" s="46"/>
       <c r="D99" s="46"/>
       <c r="E99" s="46"/>
-      <c r="F99" s="57"/>
+      <c r="F99" s="56"/>
       <c r="G99" s="46"/>
       <c r="H99" s="46"/>
       <c r="I99" s="46"/>
@@ -13275,7 +13726,7 @@
       <c r="C100" s="46"/>
       <c r="D100" s="46"/>
       <c r="E100" s="46"/>
-      <c r="F100" s="57"/>
+      <c r="F100" s="56"/>
       <c r="G100" s="46"/>
       <c r="H100" s="46"/>
       <c r="I100" s="46"/>
@@ -13300,7 +13751,7 @@
       <c r="C101" s="46"/>
       <c r="D101" s="46"/>
       <c r="E101" s="46"/>
-      <c r="F101" s="57"/>
+      <c r="F101" s="56"/>
       <c r="G101" s="46"/>
       <c r="H101" s="46"/>
       <c r="I101" s="46"/>
@@ -13325,7 +13776,7 @@
       <c r="C102" s="46"/>
       <c r="D102" s="46"/>
       <c r="E102" s="46"/>
-      <c r="F102" s="57"/>
+      <c r="F102" s="56"/>
       <c r="G102" s="46"/>
       <c r="H102" s="46"/>
       <c r="I102" s="46"/>
@@ -13350,7 +13801,7 @@
       <c r="C103" s="46"/>
       <c r="D103" s="46"/>
       <c r="E103" s="46"/>
-      <c r="F103" s="57"/>
+      <c r="F103" s="56"/>
       <c r="G103" s="46"/>
       <c r="H103" s="46"/>
       <c r="I103" s="46"/>
@@ -13375,7 +13826,7 @@
       <c r="C104" s="46"/>
       <c r="D104" s="46"/>
       <c r="E104" s="46"/>
-      <c r="F104" s="57"/>
+      <c r="F104" s="56"/>
       <c r="G104" s="46"/>
       <c r="H104" s="46"/>
       <c r="I104" s="46"/>
@@ -13400,7 +13851,7 @@
       <c r="C105" s="46"/>
       <c r="D105" s="46"/>
       <c r="E105" s="46"/>
-      <c r="F105" s="57"/>
+      <c r="F105" s="56"/>
       <c r="G105" s="46"/>
       <c r="H105" s="46"/>
       <c r="I105" s="46"/>
@@ -13425,7 +13876,7 @@
       <c r="C106" s="46"/>
       <c r="D106" s="46"/>
       <c r="E106" s="46"/>
-      <c r="F106" s="57"/>
+      <c r="F106" s="56"/>
       <c r="G106" s="46"/>
       <c r="H106" s="46"/>
       <c r="I106" s="46"/>
@@ -13450,7 +13901,7 @@
       <c r="C107" s="46"/>
       <c r="D107" s="46"/>
       <c r="E107" s="46"/>
-      <c r="F107" s="57"/>
+      <c r="F107" s="56"/>
       <c r="G107" s="46"/>
       <c r="H107" s="46"/>
       <c r="I107" s="46"/>
@@ -13475,7 +13926,7 @@
       <c r="C108" s="46"/>
       <c r="D108" s="46"/>
       <c r="E108" s="46"/>
-      <c r="F108" s="57"/>
+      <c r="F108" s="56"/>
       <c r="G108" s="46"/>
       <c r="H108" s="46"/>
       <c r="I108" s="46"/>
@@ -13500,7 +13951,7 @@
       <c r="C109" s="46"/>
       <c r="D109" s="46"/>
       <c r="E109" s="46"/>
-      <c r="F109" s="57"/>
+      <c r="F109" s="56"/>
       <c r="G109" s="46"/>
       <c r="H109" s="46"/>
       <c r="I109" s="46"/>
@@ -13525,7 +13976,7 @@
       <c r="C110" s="46"/>
       <c r="D110" s="46"/>
       <c r="E110" s="46"/>
-      <c r="F110" s="57"/>
+      <c r="F110" s="56"/>
       <c r="G110" s="46"/>
       <c r="H110" s="46"/>
       <c r="I110" s="46"/>
@@ -13550,7 +14001,7 @@
       <c r="C111" s="46"/>
       <c r="D111" s="46"/>
       <c r="E111" s="46"/>
-      <c r="F111" s="57"/>
+      <c r="F111" s="56"/>
       <c r="G111" s="46"/>
       <c r="H111" s="46"/>
       <c r="I111" s="46"/>
@@ -13575,7 +14026,7 @@
       <c r="C112" s="46"/>
       <c r="D112" s="46"/>
       <c r="E112" s="46"/>
-      <c r="F112" s="57"/>
+      <c r="F112" s="56"/>
       <c r="G112" s="46"/>
       <c r="H112" s="46"/>
       <c r="I112" s="46"/>
@@ -13600,7 +14051,7 @@
       <c r="C113" s="46"/>
       <c r="D113" s="46"/>
       <c r="E113" s="46"/>
-      <c r="F113" s="57"/>
+      <c r="F113" s="56"/>
       <c r="G113" s="46"/>
       <c r="H113" s="46"/>
       <c r="I113" s="46"/>
@@ -13625,7 +14076,7 @@
       <c r="C114" s="46"/>
       <c r="D114" s="46"/>
       <c r="E114" s="46"/>
-      <c r="F114" s="57"/>
+      <c r="F114" s="56"/>
       <c r="G114" s="46"/>
       <c r="H114" s="46"/>
       <c r="I114" s="46"/>
@@ -13650,7 +14101,7 @@
       <c r="C115" s="46"/>
       <c r="D115" s="46"/>
       <c r="E115" s="46"/>
-      <c r="F115" s="57"/>
+      <c r="F115" s="56"/>
       <c r="G115" s="46"/>
       <c r="H115" s="46"/>
       <c r="I115" s="46"/>
@@ -13675,7 +14126,7 @@
       <c r="C116" s="46"/>
       <c r="D116" s="46"/>
       <c r="E116" s="46"/>
-      <c r="F116" s="57"/>
+      <c r="F116" s="56"/>
       <c r="G116" s="46"/>
       <c r="H116" s="46"/>
       <c r="I116" s="46"/>
@@ -13719,54 +14170,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="149" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="96"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="151"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="73" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="83" t="s">
+      <c r="C2" s="74" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="83" t="s">
+      <c r="D2" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="E2" s="83" t="s">
+      <c r="E2" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="F2" s="84" t="s">
+      <c r="F2" s="75" t="s">
         <v>115</v>
       </c>
-      <c r="G2" s="83" t="s">
+      <c r="G2" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="H2" s="85" t="s">
+      <c r="H2" s="76" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="86">
+      <c r="A3" s="77">
         <v>18</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C3" s="54">
+      <c r="C3" s="53">
         <v>11003</v>
       </c>
-      <c r="D3" s="54">
+      <c r="D3" s="53">
         <v>1</v>
       </c>
       <c r="E3" s="5" t="s">
@@ -13775,26 +14226,26 @@
       <c r="F3" s="26">
         <v>7800</v>
       </c>
-      <c r="G3" s="61">
-        <f>F3*0.14</f>
+      <c r="G3" s="60">
+        <f t="shared" ref="G3:G20" si="0">F3*0.14</f>
         <v>1092</v>
       </c>
-      <c r="H3" s="87">
-        <f>F3-G3</f>
+      <c r="H3" s="78">
+        <f t="shared" ref="H3:H20" si="1">F3-G3</f>
         <v>6708</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="86">
+      <c r="A4" s="77">
         <v>4</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C4" s="54">
+      <c r="C4" s="53">
         <v>11036</v>
       </c>
-      <c r="D4" s="54">
+      <c r="D4" s="53">
         <v>1</v>
       </c>
       <c r="E4" s="5" t="s">
@@ -13803,26 +14254,26 @@
       <c r="F4" s="26">
         <v>4450</v>
       </c>
-      <c r="G4" s="61">
-        <f>F4*0.14</f>
+      <c r="G4" s="60">
+        <f t="shared" si="0"/>
         <v>623.00000000000011</v>
       </c>
-      <c r="H4" s="87">
-        <f>F4-G4</f>
+      <c r="H4" s="78">
+        <f t="shared" si="1"/>
         <v>3827</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="86">
+      <c r="A5" s="77">
         <v>17</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C5" s="54">
+      <c r="C5" s="53">
         <v>11009</v>
       </c>
-      <c r="D5" s="54">
+      <c r="D5" s="53">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
@@ -13831,26 +14282,26 @@
       <c r="F5" s="26">
         <v>9850</v>
       </c>
-      <c r="G5" s="61">
-        <f>F5*0.14</f>
+      <c r="G5" s="60">
+        <f t="shared" si="0"/>
         <v>1379.0000000000002</v>
       </c>
-      <c r="H5" s="87">
-        <f>F5-G5</f>
+      <c r="H5" s="78">
+        <f t="shared" si="1"/>
         <v>8471</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="86">
+      <c r="A6" s="77">
         <v>16</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C6" s="54">
+      <c r="C6" s="53">
         <v>11002</v>
       </c>
-      <c r="D6" s="54">
+      <c r="D6" s="53">
         <v>2</v>
       </c>
       <c r="E6" s="5" t="s">
@@ -13859,26 +14310,26 @@
       <c r="F6" s="26">
         <v>4100</v>
       </c>
-      <c r="G6" s="61">
-        <f>F6*0.14</f>
+      <c r="G6" s="60">
+        <f t="shared" si="0"/>
         <v>574</v>
       </c>
-      <c r="H6" s="87">
-        <f>F6-G6</f>
+      <c r="H6" s="78">
+        <f t="shared" si="1"/>
         <v>3526</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="86">
+      <c r="A7" s="77">
         <v>15</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C7" s="54">
+      <c r="C7" s="53">
         <v>11010</v>
       </c>
-      <c r="D7" s="54">
+      <c r="D7" s="53">
         <v>3</v>
       </c>
       <c r="E7" s="5" t="s">
@@ -13887,26 +14338,26 @@
       <c r="F7" s="26">
         <v>3600</v>
       </c>
-      <c r="G7" s="61">
-        <f>F7*0.14</f>
+      <c r="G7" s="60">
+        <f t="shared" si="0"/>
         <v>504.00000000000006</v>
       </c>
-      <c r="H7" s="87">
-        <f>F7-G7</f>
+      <c r="H7" s="78">
+        <f t="shared" si="1"/>
         <v>3096</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="86">
+      <c r="A8" s="77">
         <v>1</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C8" s="54">
+      <c r="C8" s="53">
         <v>11043</v>
       </c>
-      <c r="D8" s="54">
+      <c r="D8" s="53">
         <v>3</v>
       </c>
       <c r="E8" s="5" t="s">
@@ -13915,23 +14366,23 @@
       <c r="F8" s="26">
         <v>3850</v>
       </c>
-      <c r="G8" s="61">
-        <f>F8*0.14</f>
+      <c r="G8" s="60">
+        <f t="shared" si="0"/>
         <v>539</v>
       </c>
-      <c r="H8" s="87">
-        <f>F8-G8</f>
+      <c r="H8" s="78">
+        <f t="shared" si="1"/>
         <v>3311</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="86">
+      <c r="A9" s="77">
         <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C9" s="54">
+      <c r="C9" s="53">
         <v>11023</v>
       </c>
       <c r="D9" s="39">
@@ -13943,26 +14394,26 @@
       <c r="F9" s="26">
         <v>7200</v>
       </c>
-      <c r="G9" s="61">
-        <f>F9*0.14</f>
+      <c r="G9" s="60">
+        <f t="shared" si="0"/>
         <v>1008.0000000000001</v>
       </c>
-      <c r="H9" s="87">
-        <f>F9-G9</f>
+      <c r="H9" s="78">
+        <f t="shared" si="1"/>
         <v>6192</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="86">
+      <c r="A10" s="77">
         <v>13</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C10" s="54">
+      <c r="C10" s="53">
         <v>11045</v>
       </c>
-      <c r="D10" s="54">
+      <c r="D10" s="53">
         <v>1</v>
       </c>
       <c r="E10" s="5" t="s">
@@ -13971,26 +14422,26 @@
       <c r="F10" s="26">
         <v>2800</v>
       </c>
-      <c r="G10" s="61">
-        <f>F10*0.14</f>
+      <c r="G10" s="60">
+        <f t="shared" si="0"/>
         <v>392.00000000000006</v>
       </c>
-      <c r="H10" s="87">
-        <f>F10-G10</f>
+      <c r="H10" s="78">
+        <f t="shared" si="1"/>
         <v>2408</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="86">
+      <c r="A11" s="77">
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C11" s="54">
+      <c r="C11" s="53">
         <v>11018</v>
       </c>
-      <c r="D11" s="54">
+      <c r="D11" s="53">
         <v>2</v>
       </c>
       <c r="E11" s="5" t="s">
@@ -13999,26 +14450,26 @@
       <c r="F11" s="26">
         <v>6840</v>
       </c>
-      <c r="G11" s="61">
-        <f>F11*0.14</f>
+      <c r="G11" s="60">
+        <f t="shared" si="0"/>
         <v>957.60000000000014</v>
       </c>
-      <c r="H11" s="87">
-        <f>F11-G11</f>
+      <c r="H11" s="78">
+        <f t="shared" si="1"/>
         <v>5882.4</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="86">
+      <c r="A12" s="77">
         <v>3</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C12" s="54">
+      <c r="C12" s="53">
         <v>11044</v>
       </c>
-      <c r="D12" s="54">
+      <c r="D12" s="53">
         <v>2</v>
       </c>
       <c r="E12" s="5" t="s">
@@ -14027,26 +14478,26 @@
       <c r="F12" s="26">
         <v>4200</v>
       </c>
-      <c r="G12" s="61">
-        <f>F12*0.14</f>
+      <c r="G12" s="60">
+        <f t="shared" si="0"/>
         <v>588</v>
       </c>
-      <c r="H12" s="87">
-        <f>F12-G12</f>
+      <c r="H12" s="78">
+        <f t="shared" si="1"/>
         <v>3612</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="86">
+      <c r="A13" s="77">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C13" s="54">
+      <c r="C13" s="53">
         <v>11022</v>
       </c>
-      <c r="D13" s="54">
+      <c r="D13" s="53">
         <v>3</v>
       </c>
       <c r="E13" s="5" t="s">
@@ -14055,26 +14506,26 @@
       <c r="F13" s="26">
         <v>3740</v>
       </c>
-      <c r="G13" s="61">
-        <f>F13*0.14</f>
+      <c r="G13" s="60">
+        <f t="shared" si="0"/>
         <v>523.6</v>
       </c>
-      <c r="H13" s="87">
-        <f>F13-G13</f>
+      <c r="H13" s="78">
+        <f t="shared" si="1"/>
         <v>3216.4</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="86">
+      <c r="A14" s="77">
         <v>11</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C14" s="54">
+      <c r="C14" s="53">
         <v>11012</v>
       </c>
-      <c r="D14" s="54">
+      <c r="D14" s="53">
         <v>3</v>
       </c>
       <c r="E14" s="5" t="s">
@@ -14083,26 +14534,26 @@
       <c r="F14" s="26">
         <v>3950</v>
       </c>
-      <c r="G14" s="61">
-        <f>F14*0.14</f>
+      <c r="G14" s="60">
+        <f t="shared" si="0"/>
         <v>553</v>
       </c>
-      <c r="H14" s="87">
-        <f>F14-G14</f>
+      <c r="H14" s="78">
+        <f t="shared" si="1"/>
         <v>3397</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="86">
+      <c r="A15" s="77">
         <v>10</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C15" s="54">
+      <c r="C15" s="53">
         <v>11033</v>
       </c>
-      <c r="D15" s="54">
+      <c r="D15" s="53">
         <v>2</v>
       </c>
       <c r="E15" s="5" t="s">
@@ -14111,26 +14562,26 @@
       <c r="F15" s="26">
         <v>3460</v>
       </c>
-      <c r="G15" s="61">
-        <f>F15*0.14</f>
+      <c r="G15" s="60">
+        <f t="shared" si="0"/>
         <v>484.40000000000003</v>
       </c>
-      <c r="H15" s="87">
-        <f>F15-G15</f>
+      <c r="H15" s="78">
+        <f t="shared" si="1"/>
         <v>2975.6</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="86">
+      <c r="A16" s="77">
         <v>8</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C16" s="54">
+      <c r="C16" s="53">
         <v>11019</v>
       </c>
-      <c r="D16" s="80">
+      <c r="D16" s="71">
         <v>1</v>
       </c>
       <c r="E16" s="5" t="s">
@@ -14139,26 +14590,26 @@
       <c r="F16" s="26">
         <v>6450</v>
       </c>
-      <c r="G16" s="61">
-        <f>F16*0.14</f>
+      <c r="G16" s="60">
+        <f t="shared" si="0"/>
         <v>903.00000000000011</v>
       </c>
-      <c r="H16" s="87">
-        <f>F16-G16</f>
+      <c r="H16" s="78">
+        <f t="shared" si="1"/>
         <v>5547</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="86">
+      <c r="A17" s="77">
         <v>7</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C17" s="54">
+      <c r="C17" s="53">
         <v>11025</v>
       </c>
-      <c r="D17" s="54">
+      <c r="D17" s="53">
         <v>2</v>
       </c>
       <c r="E17" s="5" t="s">
@@ -14167,26 +14618,26 @@
       <c r="F17" s="26">
         <v>7480</v>
       </c>
-      <c r="G17" s="61">
-        <f>F17*0.14</f>
+      <c r="G17" s="60">
+        <f t="shared" si="0"/>
         <v>1047.2</v>
       </c>
-      <c r="H17" s="87">
-        <f>F17-G17</f>
+      <c r="H17" s="78">
+        <f t="shared" si="1"/>
         <v>6432.8</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="86">
+      <c r="A18" s="77">
         <v>2</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C18" s="54">
+      <c r="C18" s="53">
         <v>11028</v>
       </c>
-      <c r="D18" s="54">
+      <c r="D18" s="53">
         <v>1</v>
       </c>
       <c r="E18" s="5" t="s">
@@ -14195,26 +14646,26 @@
       <c r="F18" s="26">
         <v>4500</v>
       </c>
-      <c r="G18" s="61">
-        <f>F18*0.14</f>
+      <c r="G18" s="60">
+        <f t="shared" si="0"/>
         <v>630.00000000000011</v>
       </c>
-      <c r="H18" s="87">
-        <f>F18-G18</f>
+      <c r="H18" s="78">
+        <f t="shared" si="1"/>
         <v>3870</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="86">
+      <c r="A19" s="77">
         <v>6</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C19" s="54">
+      <c r="C19" s="53">
         <v>11014</v>
       </c>
-      <c r="D19" s="54">
+      <c r="D19" s="53">
         <v>1</v>
       </c>
       <c r="E19" s="5" t="s">
@@ -14223,93 +14674,93 @@
       <c r="F19" s="26">
         <v>7600</v>
       </c>
-      <c r="G19" s="61">
-        <f>F19*0.14</f>
+      <c r="G19" s="60">
+        <f t="shared" si="0"/>
         <v>1064</v>
       </c>
-      <c r="H19" s="87">
-        <f>F19-G19</f>
+      <c r="H19" s="78">
+        <f t="shared" si="1"/>
         <v>6536</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="88">
+      <c r="A20" s="79">
         <v>5</v>
       </c>
-      <c r="B20" s="89" t="s">
+      <c r="B20" s="80" t="s">
         <v>126</v>
       </c>
-      <c r="C20" s="90">
+      <c r="C20" s="81">
         <v>11017</v>
       </c>
-      <c r="D20" s="90">
+      <c r="D20" s="81">
         <v>3</v>
       </c>
-      <c r="E20" s="89" t="s">
+      <c r="E20" s="80" t="s">
         <v>127</v>
       </c>
-      <c r="F20" s="91">
+      <c r="F20" s="82">
         <v>6299</v>
       </c>
-      <c r="G20" s="92">
-        <f>F20*0.14</f>
+      <c r="G20" s="83">
+        <f t="shared" si="0"/>
         <v>881.86000000000013</v>
       </c>
-      <c r="H20" s="93">
-        <f>F20-G20</f>
+      <c r="H20" s="84">
+        <f t="shared" si="1"/>
         <v>5417.1399999999994</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="94" t="s">
+      <c r="A22" s="149" t="s">
         <v>148</v>
       </c>
-      <c r="B22" s="95"/>
-      <c r="C22" s="95"/>
-      <c r="D22" s="95"/>
-      <c r="E22" s="95"/>
-      <c r="F22" s="95"/>
-      <c r="G22" s="95"/>
-      <c r="H22" s="96"/>
+      <c r="B22" s="150"/>
+      <c r="C22" s="150"/>
+      <c r="D22" s="150"/>
+      <c r="E22" s="150"/>
+      <c r="F22" s="150"/>
+      <c r="G22" s="150"/>
+      <c r="H22" s="151"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="81" t="s">
+      <c r="A23" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="B23" s="82" t="s">
+      <c r="B23" s="73" t="s">
         <v>111</v>
       </c>
-      <c r="C23" s="83" t="s">
+      <c r="C23" s="74" t="s">
         <v>112</v>
       </c>
-      <c r="D23" s="83" t="s">
+      <c r="D23" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="E23" s="83" t="s">
+      <c r="E23" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="F23" s="84" t="s">
+      <c r="F23" s="75" t="s">
         <v>115</v>
       </c>
-      <c r="G23" s="83" t="s">
+      <c r="G23" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="H23" s="85" t="s">
+      <c r="H23" s="76" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="86">
+      <c r="A24" s="77">
         <v>5</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="54">
+      <c r="C24" s="53">
         <v>11017</v>
       </c>
-      <c r="D24" s="54">
+      <c r="D24" s="53">
         <v>3</v>
       </c>
       <c r="E24" s="5" t="s">
@@ -14318,26 +14769,26 @@
       <c r="F24" s="26">
         <v>6299</v>
       </c>
-      <c r="G24" s="61">
-        <f>F24*0.14</f>
+      <c r="G24" s="60">
+        <f t="shared" ref="G24:G41" si="2">F24*0.14</f>
         <v>881.86000000000013</v>
       </c>
-      <c r="H24" s="87">
-        <f>F24-G24</f>
+      <c r="H24" s="78">
+        <f t="shared" ref="H24:H41" si="3">F24-G24</f>
         <v>5417.1399999999994</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="86">
+      <c r="A25" s="77">
         <v>11</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C25" s="54">
+      <c r="C25" s="53">
         <v>11012</v>
       </c>
-      <c r="D25" s="54">
+      <c r="D25" s="53">
         <v>3</v>
       </c>
       <c r="E25" s="5" t="s">
@@ -14346,26 +14797,26 @@
       <c r="F25" s="26">
         <v>3950</v>
       </c>
-      <c r="G25" s="61">
-        <f>F25*0.14</f>
+      <c r="G25" s="60">
+        <f t="shared" si="2"/>
         <v>553</v>
       </c>
-      <c r="H25" s="87">
-        <f>F25-G25</f>
+      <c r="H25" s="78">
+        <f t="shared" si="3"/>
         <v>3397</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="86">
+      <c r="A26" s="77">
         <v>1</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C26" s="54">
+      <c r="C26" s="53">
         <v>11043</v>
       </c>
-      <c r="D26" s="54">
+      <c r="D26" s="53">
         <v>3</v>
       </c>
       <c r="E26" s="5" t="s">
@@ -14374,26 +14825,26 @@
       <c r="F26" s="26">
         <v>3850</v>
       </c>
-      <c r="G26" s="61">
-        <f>F26*0.14</f>
+      <c r="G26" s="60">
+        <f t="shared" si="2"/>
         <v>539</v>
       </c>
-      <c r="H26" s="87">
-        <f>F26-G26</f>
+      <c r="H26" s="78">
+        <f t="shared" si="3"/>
         <v>3311</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="86">
+      <c r="A27" s="77">
         <v>12</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C27" s="54">
+      <c r="C27" s="53">
         <v>11022</v>
       </c>
-      <c r="D27" s="54">
+      <c r="D27" s="53">
         <v>3</v>
       </c>
       <c r="E27" s="5" t="s">
@@ -14402,26 +14853,26 @@
       <c r="F27" s="26">
         <v>3740</v>
       </c>
-      <c r="G27" s="61">
-        <f>F27*0.14</f>
+      <c r="G27" s="60">
+        <f t="shared" si="2"/>
         <v>523.6</v>
       </c>
-      <c r="H27" s="87">
-        <f>F27-G27</f>
+      <c r="H27" s="78">
+        <f t="shared" si="3"/>
         <v>3216.4</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="86">
+      <c r="A28" s="77">
         <v>15</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C28" s="54">
+      <c r="C28" s="53">
         <v>11010</v>
       </c>
-      <c r="D28" s="54">
+      <c r="D28" s="53">
         <v>3</v>
       </c>
       <c r="E28" s="5" t="s">
@@ -14430,26 +14881,26 @@
       <c r="F28" s="26">
         <v>3600</v>
       </c>
-      <c r="G28" s="61">
-        <f>F28*0.14</f>
+      <c r="G28" s="60">
+        <f t="shared" si="2"/>
         <v>504.00000000000006</v>
       </c>
-      <c r="H28" s="87">
-        <f>F28-G28</f>
+      <c r="H28" s="78">
+        <f t="shared" si="3"/>
         <v>3096</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="86">
+      <c r="A29" s="77">
         <v>7</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C29" s="54">
+      <c r="C29" s="53">
         <v>11025</v>
       </c>
-      <c r="D29" s="54">
+      <c r="D29" s="53">
         <v>2</v>
       </c>
       <c r="E29" s="5" t="s">
@@ -14458,26 +14909,26 @@
       <c r="F29" s="26">
         <v>7480</v>
       </c>
-      <c r="G29" s="61">
-        <f>F29*0.14</f>
+      <c r="G29" s="60">
+        <f t="shared" si="2"/>
         <v>1047.2</v>
       </c>
-      <c r="H29" s="87">
-        <f>F29-G29</f>
+      <c r="H29" s="78">
+        <f t="shared" si="3"/>
         <v>6432.8</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="86">
+      <c r="A30" s="77">
         <v>9</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C30" s="54">
+      <c r="C30" s="53">
         <v>11018</v>
       </c>
-      <c r="D30" s="54">
+      <c r="D30" s="53">
         <v>2</v>
       </c>
       <c r="E30" s="5" t="s">
@@ -14486,26 +14937,26 @@
       <c r="F30" s="26">
         <v>6840</v>
       </c>
-      <c r="G30" s="61">
-        <f>F30*0.14</f>
+      <c r="G30" s="60">
+        <f t="shared" si="2"/>
         <v>957.60000000000014</v>
       </c>
-      <c r="H30" s="87">
-        <f>F30-G30</f>
+      <c r="H30" s="78">
+        <f t="shared" si="3"/>
         <v>5882.4</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="86">
+      <c r="A31" s="77">
         <v>3</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C31" s="54">
+      <c r="C31" s="53">
         <v>11044</v>
       </c>
-      <c r="D31" s="54">
+      <c r="D31" s="53">
         <v>2</v>
       </c>
       <c r="E31" s="5" t="s">
@@ -14514,26 +14965,26 @@
       <c r="F31" s="26">
         <v>4200</v>
       </c>
-      <c r="G31" s="61">
-        <f>F31*0.14</f>
+      <c r="G31" s="60">
+        <f t="shared" si="2"/>
         <v>588</v>
       </c>
-      <c r="H31" s="87">
-        <f>F31-G31</f>
+      <c r="H31" s="78">
+        <f t="shared" si="3"/>
         <v>3612</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="86">
+      <c r="A32" s="77">
         <v>16</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C32" s="54">
+      <c r="C32" s="53">
         <v>11002</v>
       </c>
-      <c r="D32" s="54">
+      <c r="D32" s="53">
         <v>2</v>
       </c>
       <c r="E32" s="5" t="s">
@@ -14542,26 +14993,26 @@
       <c r="F32" s="26">
         <v>4100</v>
       </c>
-      <c r="G32" s="61">
-        <f>F32*0.14</f>
+      <c r="G32" s="60">
+        <f t="shared" si="2"/>
         <v>574</v>
       </c>
-      <c r="H32" s="87">
-        <f>F32-G32</f>
+      <c r="H32" s="78">
+        <f t="shared" si="3"/>
         <v>3526</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="86">
+      <c r="A33" s="77">
         <v>10</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="54">
+      <c r="C33" s="53">
         <v>11033</v>
       </c>
-      <c r="D33" s="54">
+      <c r="D33" s="53">
         <v>2</v>
       </c>
       <c r="E33" s="5" t="s">
@@ -14570,26 +15021,26 @@
       <c r="F33" s="26">
         <v>3460</v>
       </c>
-      <c r="G33" s="61">
-        <f>F33*0.14</f>
+      <c r="G33" s="60">
+        <f t="shared" si="2"/>
         <v>484.40000000000003</v>
       </c>
-      <c r="H33" s="87">
-        <f>F33-G33</f>
+      <c r="H33" s="78">
+        <f t="shared" si="3"/>
         <v>2975.6</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="86">
+      <c r="A34" s="77">
         <v>17</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C34" s="54">
+      <c r="C34" s="53">
         <v>11009</v>
       </c>
-      <c r="D34" s="54">
+      <c r="D34" s="53">
         <v>1</v>
       </c>
       <c r="E34" s="5" t="s">
@@ -14598,26 +15049,26 @@
       <c r="F34" s="26">
         <v>9850</v>
       </c>
-      <c r="G34" s="61">
-        <f>F34*0.14</f>
+      <c r="G34" s="60">
+        <f t="shared" si="2"/>
         <v>1379.0000000000002</v>
       </c>
-      <c r="H34" s="87">
-        <f>F34-G34</f>
+      <c r="H34" s="78">
+        <f t="shared" si="3"/>
         <v>8471</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="86">
+      <c r="A35" s="77">
         <v>18</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C35" s="54">
+      <c r="C35" s="53">
         <v>11003</v>
       </c>
-      <c r="D35" s="54">
+      <c r="D35" s="53">
         <v>1</v>
       </c>
       <c r="E35" s="5" t="s">
@@ -14626,26 +15077,26 @@
       <c r="F35" s="26">
         <v>7800</v>
       </c>
-      <c r="G35" s="61">
-        <f>F35*0.14</f>
+      <c r="G35" s="60">
+        <f t="shared" si="2"/>
         <v>1092</v>
       </c>
-      <c r="H35" s="87">
-        <f>F35-G35</f>
+      <c r="H35" s="78">
+        <f t="shared" si="3"/>
         <v>6708</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="86">
+      <c r="A36" s="77">
         <v>6</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C36" s="54">
+      <c r="C36" s="53">
         <v>11014</v>
       </c>
-      <c r="D36" s="54">
+      <c r="D36" s="53">
         <v>1</v>
       </c>
       <c r="E36" s="5" t="s">
@@ -14654,26 +15105,26 @@
       <c r="F36" s="26">
         <v>7600</v>
       </c>
-      <c r="G36" s="61">
-        <f>F36*0.14</f>
+      <c r="G36" s="60">
+        <f t="shared" si="2"/>
         <v>1064</v>
       </c>
-      <c r="H36" s="87">
-        <f>F36-G36</f>
+      <c r="H36" s="78">
+        <f t="shared" si="3"/>
         <v>6536</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="86">
+      <c r="A37" s="77">
         <v>14</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C37" s="54">
+      <c r="C37" s="53">
         <v>11023</v>
       </c>
-      <c r="D37" s="62">
+      <c r="D37" s="61">
         <v>1</v>
       </c>
       <c r="E37" s="5" t="s">
@@ -14682,26 +15133,26 @@
       <c r="F37" s="26">
         <v>7200</v>
       </c>
-      <c r="G37" s="61">
-        <f>F37*0.14</f>
+      <c r="G37" s="60">
+        <f t="shared" si="2"/>
         <v>1008.0000000000001</v>
       </c>
-      <c r="H37" s="87">
-        <f>F37-G37</f>
+      <c r="H37" s="78">
+        <f t="shared" si="3"/>
         <v>6192</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="86">
+      <c r="A38" s="77">
         <v>8</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C38" s="54">
+      <c r="C38" s="53">
         <v>11019</v>
       </c>
-      <c r="D38" s="54">
+      <c r="D38" s="53">
         <v>1</v>
       </c>
       <c r="E38" s="5" t="s">
@@ -14710,26 +15161,26 @@
       <c r="F38" s="26">
         <v>6450</v>
       </c>
-      <c r="G38" s="61">
-        <f>F38*0.14</f>
+      <c r="G38" s="60">
+        <f t="shared" si="2"/>
         <v>903.00000000000011</v>
       </c>
-      <c r="H38" s="87">
-        <f>F38-G38</f>
+      <c r="H38" s="78">
+        <f t="shared" si="3"/>
         <v>5547</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="86">
+      <c r="A39" s="77">
         <v>2</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C39" s="54">
+      <c r="C39" s="53">
         <v>11028</v>
       </c>
-      <c r="D39" s="54">
+      <c r="D39" s="53">
         <v>1</v>
       </c>
       <c r="E39" s="5" t="s">
@@ -14738,26 +15189,26 @@
       <c r="F39" s="26">
         <v>4500</v>
       </c>
-      <c r="G39" s="61">
-        <f>F39*0.14</f>
+      <c r="G39" s="60">
+        <f t="shared" si="2"/>
         <v>630.00000000000011</v>
       </c>
-      <c r="H39" s="87">
-        <f>F39-G39</f>
+      <c r="H39" s="78">
+        <f t="shared" si="3"/>
         <v>3870</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="86">
+      <c r="A40" s="77">
         <v>4</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C40" s="54">
+      <c r="C40" s="53">
         <v>11036</v>
       </c>
-      <c r="D40" s="54">
+      <c r="D40" s="53">
         <v>1</v>
       </c>
       <c r="E40" s="5" t="s">
@@ -14766,93 +15217,93 @@
       <c r="F40" s="26">
         <v>4450</v>
       </c>
-      <c r="G40" s="61">
-        <f>F40*0.14</f>
+      <c r="G40" s="60">
+        <f t="shared" si="2"/>
         <v>623.00000000000011</v>
       </c>
-      <c r="H40" s="87">
-        <f>F40-G40</f>
+      <c r="H40" s="78">
+        <f t="shared" si="3"/>
         <v>3827</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="88">
+      <c r="A41" s="79">
         <v>13</v>
       </c>
-      <c r="B41" s="89" t="s">
+      <c r="B41" s="80" t="s">
         <v>137</v>
       </c>
-      <c r="C41" s="90">
+      <c r="C41" s="81">
         <v>11045</v>
       </c>
-      <c r="D41" s="90">
+      <c r="D41" s="81">
         <v>1</v>
       </c>
-      <c r="E41" s="89" t="s">
+      <c r="E41" s="80" t="s">
         <v>138</v>
       </c>
-      <c r="F41" s="91">
+      <c r="F41" s="82">
         <v>2800</v>
       </c>
-      <c r="G41" s="92">
-        <f>F41*0.14</f>
+      <c r="G41" s="83">
+        <f t="shared" si="2"/>
         <v>392.00000000000006</v>
       </c>
-      <c r="H41" s="93">
-        <f>F41-G41</f>
+      <c r="H41" s="84">
+        <f t="shared" si="3"/>
         <v>2408</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="94" t="s">
+      <c r="A43" s="149" t="s">
         <v>150</v>
       </c>
-      <c r="B43" s="95"/>
-      <c r="C43" s="95"/>
-      <c r="D43" s="95"/>
-      <c r="E43" s="95"/>
-      <c r="F43" s="95"/>
-      <c r="G43" s="95"/>
-      <c r="H43" s="96"/>
+      <c r="B43" s="150"/>
+      <c r="C43" s="150"/>
+      <c r="D43" s="150"/>
+      <c r="E43" s="150"/>
+      <c r="F43" s="150"/>
+      <c r="G43" s="150"/>
+      <c r="H43" s="151"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="81" t="s">
+      <c r="A44" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="B44" s="82" t="s">
+      <c r="B44" s="73" t="s">
         <v>111</v>
       </c>
-      <c r="C44" s="83" t="s">
+      <c r="C44" s="74" t="s">
         <v>112</v>
       </c>
-      <c r="D44" s="83" t="s">
+      <c r="D44" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="E44" s="83" t="s">
+      <c r="E44" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="F44" s="84" t="s">
+      <c r="F44" s="75" t="s">
         <v>115</v>
       </c>
-      <c r="G44" s="83" t="s">
+      <c r="G44" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="H44" s="85" t="s">
+      <c r="H44" s="76" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="86">
+      <c r="A45" s="77">
         <v>18</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C45" s="54">
+      <c r="C45" s="53">
         <v>11003</v>
       </c>
-      <c r="D45" s="54">
+      <c r="D45" s="53">
         <v>1</v>
       </c>
       <c r="E45" s="5" t="s">
@@ -14861,26 +15312,26 @@
       <c r="F45" s="26">
         <v>7800</v>
       </c>
-      <c r="G45" s="61">
-        <f>F45*0.14</f>
+      <c r="G45" s="60">
+        <f t="shared" ref="G45:G62" si="4">F45*0.14</f>
         <v>1092</v>
       </c>
-      <c r="H45" s="87">
-        <f>F45-G45</f>
+      <c r="H45" s="78">
+        <f t="shared" ref="H45:H62" si="5">F45-G45</f>
         <v>6708</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="86">
+      <c r="A46" s="77">
         <v>4</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C46" s="54">
+      <c r="C46" s="53">
         <v>11036</v>
       </c>
-      <c r="D46" s="54">
+      <c r="D46" s="53">
         <v>1</v>
       </c>
       <c r="E46" s="5" t="s">
@@ -14889,26 +15340,26 @@
       <c r="F46" s="26">
         <v>4450</v>
       </c>
-      <c r="G46" s="61">
-        <f>F46*0.14</f>
+      <c r="G46" s="60">
+        <f t="shared" si="4"/>
         <v>623.00000000000011</v>
       </c>
-      <c r="H46" s="87">
-        <f>F46-G46</f>
+      <c r="H46" s="78">
+        <f t="shared" si="5"/>
         <v>3827</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="86">
+      <c r="A47" s="77">
         <v>17</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C47" s="54">
+      <c r="C47" s="53">
         <v>11009</v>
       </c>
-      <c r="D47" s="54">
+      <c r="D47" s="53">
         <v>1</v>
       </c>
       <c r="E47" s="5" t="s">
@@ -14917,26 +15368,26 @@
       <c r="F47" s="26">
         <v>9850</v>
       </c>
-      <c r="G47" s="61">
-        <f>F47*0.14</f>
+      <c r="G47" s="60">
+        <f t="shared" si="4"/>
         <v>1379.0000000000002</v>
       </c>
-      <c r="H47" s="87">
-        <f>F47-G47</f>
+      <c r="H47" s="78">
+        <f t="shared" si="5"/>
         <v>8471</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="86">
+      <c r="A48" s="77">
         <v>16</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C48" s="54">
+      <c r="C48" s="53">
         <v>11002</v>
       </c>
-      <c r="D48" s="54">
+      <c r="D48" s="53">
         <v>2</v>
       </c>
       <c r="E48" s="5" t="s">
@@ -14945,26 +15396,26 @@
       <c r="F48" s="26">
         <v>4100</v>
       </c>
-      <c r="G48" s="61">
-        <f>F48*0.14</f>
+      <c r="G48" s="60">
+        <f t="shared" si="4"/>
         <v>574</v>
       </c>
-      <c r="H48" s="87">
-        <f>F48-G48</f>
+      <c r="H48" s="78">
+        <f t="shared" si="5"/>
         <v>3526</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="86">
+      <c r="A49" s="77">
         <v>15</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C49" s="54">
+      <c r="C49" s="53">
         <v>11010</v>
       </c>
-      <c r="D49" s="54">
+      <c r="D49" s="53">
         <v>3</v>
       </c>
       <c r="E49" s="5" t="s">
@@ -14973,26 +15424,26 @@
       <c r="F49" s="26">
         <v>3600</v>
       </c>
-      <c r="G49" s="61">
-        <f>F49*0.14</f>
+      <c r="G49" s="60">
+        <f t="shared" si="4"/>
         <v>504.00000000000006</v>
       </c>
-      <c r="H49" s="87">
-        <f>F49-G49</f>
+      <c r="H49" s="78">
+        <f t="shared" si="5"/>
         <v>3096</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="86">
+      <c r="A50" s="77">
         <v>1</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C50" s="54">
+      <c r="C50" s="53">
         <v>11043</v>
       </c>
-      <c r="D50" s="54">
+      <c r="D50" s="53">
         <v>3</v>
       </c>
       <c r="E50" s="5" t="s">
@@ -15001,23 +15452,23 @@
       <c r="F50" s="26">
         <v>3850</v>
       </c>
-      <c r="G50" s="61">
-        <f>F50*0.14</f>
+      <c r="G50" s="60">
+        <f t="shared" si="4"/>
         <v>539</v>
       </c>
-      <c r="H50" s="87">
-        <f>F50-G50</f>
+      <c r="H50" s="78">
+        <f t="shared" si="5"/>
         <v>3311</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="86">
+      <c r="A51" s="77">
         <v>14</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C51" s="54">
+      <c r="C51" s="53">
         <v>11023</v>
       </c>
       <c r="D51" s="39">
@@ -15029,26 +15480,26 @@
       <c r="F51" s="26">
         <v>7200</v>
       </c>
-      <c r="G51" s="61">
-        <f>F51*0.14</f>
+      <c r="G51" s="60">
+        <f t="shared" si="4"/>
         <v>1008.0000000000001</v>
       </c>
-      <c r="H51" s="87">
-        <f>F51-G51</f>
+      <c r="H51" s="78">
+        <f t="shared" si="5"/>
         <v>6192</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="86">
+      <c r="A52" s="77">
         <v>13</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C52" s="54">
+      <c r="C52" s="53">
         <v>11045</v>
       </c>
-      <c r="D52" s="54">
+      <c r="D52" s="53">
         <v>1</v>
       </c>
       <c r="E52" s="5" t="s">
@@ -15057,26 +15508,26 @@
       <c r="F52" s="26">
         <v>2800</v>
       </c>
-      <c r="G52" s="61">
-        <f>F52*0.14</f>
+      <c r="G52" s="60">
+        <f t="shared" si="4"/>
         <v>392.00000000000006</v>
       </c>
-      <c r="H52" s="87">
-        <f>F52-G52</f>
+      <c r="H52" s="78">
+        <f t="shared" si="5"/>
         <v>2408</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="86">
+      <c r="A53" s="77">
         <v>9</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C53" s="54">
+      <c r="C53" s="53">
         <v>11018</v>
       </c>
-      <c r="D53" s="54">
+      <c r="D53" s="53">
         <v>2</v>
       </c>
       <c r="E53" s="5" t="s">
@@ -15085,26 +15536,26 @@
       <c r="F53" s="26">
         <v>6840</v>
       </c>
-      <c r="G53" s="61">
-        <f>F53*0.14</f>
+      <c r="G53" s="60">
+        <f t="shared" si="4"/>
         <v>957.60000000000014</v>
       </c>
-      <c r="H53" s="87">
-        <f>F53-G53</f>
+      <c r="H53" s="78">
+        <f t="shared" si="5"/>
         <v>5882.4</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="86">
+      <c r="A54" s="77">
         <v>3</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C54" s="54">
+      <c r="C54" s="53">
         <v>11044</v>
       </c>
-      <c r="D54" s="54">
+      <c r="D54" s="53">
         <v>2</v>
       </c>
       <c r="E54" s="5" t="s">
@@ -15113,26 +15564,26 @@
       <c r="F54" s="26">
         <v>4200</v>
       </c>
-      <c r="G54" s="61">
-        <f>F54*0.14</f>
+      <c r="G54" s="60">
+        <f t="shared" si="4"/>
         <v>588</v>
       </c>
-      <c r="H54" s="87">
-        <f>F54-G54</f>
+      <c r="H54" s="78">
+        <f t="shared" si="5"/>
         <v>3612</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="86">
+      <c r="A55" s="77">
         <v>12</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C55" s="54">
+      <c r="C55" s="53">
         <v>11022</v>
       </c>
-      <c r="D55" s="54">
+      <c r="D55" s="53">
         <v>3</v>
       </c>
       <c r="E55" s="5" t="s">
@@ -15141,26 +15592,26 @@
       <c r="F55" s="26">
         <v>3740</v>
       </c>
-      <c r="G55" s="61">
-        <f>F55*0.14</f>
+      <c r="G55" s="60">
+        <f t="shared" si="4"/>
         <v>523.6</v>
       </c>
-      <c r="H55" s="87">
-        <f>F55-G55</f>
+      <c r="H55" s="78">
+        <f t="shared" si="5"/>
         <v>3216.4</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="86">
+      <c r="A56" s="77">
         <v>11</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C56" s="54">
+      <c r="C56" s="53">
         <v>11012</v>
       </c>
-      <c r="D56" s="54">
+      <c r="D56" s="53">
         <v>3</v>
       </c>
       <c r="E56" s="5" t="s">
@@ -15169,26 +15620,26 @@
       <c r="F56" s="26">
         <v>3950</v>
       </c>
-      <c r="G56" s="61">
-        <f>F56*0.14</f>
+      <c r="G56" s="60">
+        <f t="shared" si="4"/>
         <v>553</v>
       </c>
-      <c r="H56" s="87">
-        <f>F56-G56</f>
+      <c r="H56" s="78">
+        <f t="shared" si="5"/>
         <v>3397</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="86">
+      <c r="A57" s="77">
         <v>10</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C57" s="54">
+      <c r="C57" s="53">
         <v>11033</v>
       </c>
-      <c r="D57" s="54">
+      <c r="D57" s="53">
         <v>2</v>
       </c>
       <c r="E57" s="5" t="s">
@@ -15197,26 +15648,26 @@
       <c r="F57" s="26">
         <v>3460</v>
       </c>
-      <c r="G57" s="61">
-        <f>F57*0.14</f>
+      <c r="G57" s="60">
+        <f t="shared" si="4"/>
         <v>484.40000000000003</v>
       </c>
-      <c r="H57" s="87">
-        <f>F57-G57</f>
+      <c r="H57" s="78">
+        <f t="shared" si="5"/>
         <v>2975.6</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="86">
+      <c r="A58" s="77">
         <v>8</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C58" s="54">
+      <c r="C58" s="53">
         <v>11019</v>
       </c>
-      <c r="D58" s="80">
+      <c r="D58" s="71">
         <v>1</v>
       </c>
       <c r="E58" s="5" t="s">
@@ -15225,26 +15676,26 @@
       <c r="F58" s="26">
         <v>6450</v>
       </c>
-      <c r="G58" s="61">
-        <f>F58*0.14</f>
+      <c r="G58" s="60">
+        <f t="shared" si="4"/>
         <v>903.00000000000011</v>
       </c>
-      <c r="H58" s="87">
-        <f>F58-G58</f>
+      <c r="H58" s="78">
+        <f t="shared" si="5"/>
         <v>5547</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="86">
+      <c r="A59" s="77">
         <v>7</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C59" s="54">
+      <c r="C59" s="53">
         <v>11025</v>
       </c>
-      <c r="D59" s="54">
+      <c r="D59" s="53">
         <v>2</v>
       </c>
       <c r="E59" s="5" t="s">
@@ -15253,26 +15704,26 @@
       <c r="F59" s="26">
         <v>7480</v>
       </c>
-      <c r="G59" s="61">
-        <f>F59*0.14</f>
+      <c r="G59" s="60">
+        <f t="shared" si="4"/>
         <v>1047.2</v>
       </c>
-      <c r="H59" s="87">
-        <f>F59-G59</f>
+      <c r="H59" s="78">
+        <f t="shared" si="5"/>
         <v>6432.8</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="86">
+      <c r="A60" s="77">
         <v>2</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C60" s="54">
+      <c r="C60" s="53">
         <v>11028</v>
       </c>
-      <c r="D60" s="54">
+      <c r="D60" s="53">
         <v>1</v>
       </c>
       <c r="E60" s="5" t="s">
@@ -15281,26 +15732,26 @@
       <c r="F60" s="26">
         <v>4500</v>
       </c>
-      <c r="G60" s="61">
-        <f>F60*0.14</f>
+      <c r="G60" s="60">
+        <f t="shared" si="4"/>
         <v>630.00000000000011</v>
       </c>
-      <c r="H60" s="87">
-        <f>F60-G60</f>
+      <c r="H60" s="78">
+        <f t="shared" si="5"/>
         <v>3870</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="86">
+      <c r="A61" s="77">
         <v>6</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C61" s="54">
+      <c r="C61" s="53">
         <v>11014</v>
       </c>
-      <c r="D61" s="54">
+      <c r="D61" s="53">
         <v>1</v>
       </c>
       <c r="E61" s="5" t="s">
@@ -15309,93 +15760,93 @@
       <c r="F61" s="26">
         <v>7600</v>
       </c>
-      <c r="G61" s="61">
-        <f>F61*0.14</f>
+      <c r="G61" s="60">
+        <f t="shared" si="4"/>
         <v>1064</v>
       </c>
-      <c r="H61" s="87">
-        <f>F61-G61</f>
+      <c r="H61" s="78">
+        <f t="shared" si="5"/>
         <v>6536</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="88">
+      <c r="A62" s="79">
         <v>5</v>
       </c>
-      <c r="B62" s="89" t="s">
+      <c r="B62" s="80" t="s">
         <v>126</v>
       </c>
-      <c r="C62" s="90">
+      <c r="C62" s="81">
         <v>11017</v>
       </c>
-      <c r="D62" s="90">
+      <c r="D62" s="81">
         <v>3</v>
       </c>
-      <c r="E62" s="89" t="s">
+      <c r="E62" s="80" t="s">
         <v>127</v>
       </c>
-      <c r="F62" s="91">
+      <c r="F62" s="82">
         <v>6299</v>
       </c>
-      <c r="G62" s="92">
-        <f>F62*0.14</f>
+      <c r="G62" s="83">
+        <f t="shared" si="4"/>
         <v>881.86000000000013</v>
       </c>
-      <c r="H62" s="93">
-        <f>F62-G62</f>
+      <c r="H62" s="84">
+        <f t="shared" si="5"/>
         <v>5417.1399999999994</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="94" t="s">
+      <c r="A64" s="149" t="s">
         <v>151</v>
       </c>
-      <c r="B64" s="95"/>
-      <c r="C64" s="95"/>
-      <c r="D64" s="95"/>
-      <c r="E64" s="95"/>
-      <c r="F64" s="95"/>
-      <c r="G64" s="95"/>
-      <c r="H64" s="96"/>
+      <c r="B64" s="150"/>
+      <c r="C64" s="150"/>
+      <c r="D64" s="150"/>
+      <c r="E64" s="150"/>
+      <c r="F64" s="150"/>
+      <c r="G64" s="150"/>
+      <c r="H64" s="151"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="81" t="s">
+      <c r="A65" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="B65" s="82" t="s">
+      <c r="B65" s="73" t="s">
         <v>111</v>
       </c>
-      <c r="C65" s="83" t="s">
+      <c r="C65" s="74" t="s">
         <v>112</v>
       </c>
-      <c r="D65" s="83" t="s">
+      <c r="D65" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="E65" s="83" t="s">
+      <c r="E65" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="F65" s="84" t="s">
+      <c r="F65" s="75" t="s">
         <v>115</v>
       </c>
-      <c r="G65" s="83" t="s">
+      <c r="G65" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="H65" s="85" t="s">
+      <c r="H65" s="76" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="86">
+      <c r="A66" s="77">
         <v>2</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C66" s="54">
+      <c r="C66" s="53">
         <v>11028</v>
       </c>
-      <c r="D66" s="54">
+      <c r="D66" s="53">
         <v>1</v>
       </c>
       <c r="E66" s="5" t="s">
@@ -15404,26 +15855,26 @@
       <c r="F66" s="26">
         <v>4500</v>
       </c>
-      <c r="G66" s="61">
-        <f>F66*0.14</f>
+      <c r="G66" s="60">
+        <f t="shared" ref="G66:G83" si="6">F66*0.14</f>
         <v>630.00000000000011</v>
       </c>
-      <c r="H66" s="87">
-        <f>F66-G66</f>
+      <c r="H66" s="78">
+        <f t="shared" ref="H66:H83" si="7">F66-G66</f>
         <v>3870</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="86">
+      <c r="A67" s="77">
         <v>4</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C67" s="54">
+      <c r="C67" s="53">
         <v>11036</v>
       </c>
-      <c r="D67" s="54">
+      <c r="D67" s="53">
         <v>1</v>
       </c>
       <c r="E67" s="5" t="s">
@@ -15432,26 +15883,26 @@
       <c r="F67" s="26">
         <v>4450</v>
       </c>
-      <c r="G67" s="61">
-        <f>F67*0.14</f>
+      <c r="G67" s="60">
+        <f t="shared" si="6"/>
         <v>623.00000000000011</v>
       </c>
-      <c r="H67" s="87">
-        <f>F67-G67</f>
+      <c r="H67" s="78">
+        <f t="shared" si="7"/>
         <v>3827</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="86">
+      <c r="A68" s="77">
         <v>18</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C68" s="54">
+      <c r="C68" s="53">
         <v>11003</v>
       </c>
-      <c r="D68" s="54">
+      <c r="D68" s="53">
         <v>1</v>
       </c>
       <c r="E68" s="5" t="s">
@@ -15460,26 +15911,26 @@
       <c r="F68" s="26">
         <v>7800</v>
       </c>
-      <c r="G68" s="61">
-        <f>F68*0.14</f>
+      <c r="G68" s="60">
+        <f t="shared" si="6"/>
         <v>1092</v>
       </c>
-      <c r="H68" s="87">
-        <f>F68-G68</f>
+      <c r="H68" s="78">
+        <f t="shared" si="7"/>
         <v>6708</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="86">
+      <c r="A69" s="77">
         <v>17</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C69" s="54">
+      <c r="C69" s="53">
         <v>11009</v>
       </c>
-      <c r="D69" s="54">
+      <c r="D69" s="53">
         <v>1</v>
       </c>
       <c r="E69" s="5" t="s">
@@ -15488,26 +15939,26 @@
       <c r="F69" s="26">
         <v>9850</v>
       </c>
-      <c r="G69" s="61">
-        <f>F69*0.14</f>
+      <c r="G69" s="60">
+        <f t="shared" si="6"/>
         <v>1379.0000000000002</v>
       </c>
-      <c r="H69" s="87">
-        <f>F69-G69</f>
+      <c r="H69" s="78">
+        <f t="shared" si="7"/>
         <v>8471</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="86">
+      <c r="A70" s="77">
         <v>6</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C70" s="54">
+      <c r="C70" s="53">
         <v>11014</v>
       </c>
-      <c r="D70" s="54">
+      <c r="D70" s="53">
         <v>1</v>
       </c>
       <c r="E70" s="5" t="s">
@@ -15516,26 +15967,26 @@
       <c r="F70" s="26">
         <v>7600</v>
       </c>
-      <c r="G70" s="61">
-        <f>F70*0.14</f>
+      <c r="G70" s="60">
+        <f t="shared" si="6"/>
         <v>1064</v>
       </c>
-      <c r="H70" s="87">
-        <f>F70-G70</f>
+      <c r="H70" s="78">
+        <f t="shared" si="7"/>
         <v>6536</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="86">
+      <c r="A71" s="77">
         <v>8</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C71" s="54">
+      <c r="C71" s="53">
         <v>11019</v>
       </c>
-      <c r="D71" s="54">
+      <c r="D71" s="53">
         <v>1</v>
       </c>
       <c r="E71" s="5" t="s">
@@ -15544,26 +15995,26 @@
       <c r="F71" s="26">
         <v>6450</v>
       </c>
-      <c r="G71" s="61">
-        <f>F71*0.14</f>
+      <c r="G71" s="60">
+        <f t="shared" si="6"/>
         <v>903.00000000000011</v>
       </c>
-      <c r="H71" s="87">
-        <f>F71-G71</f>
+      <c r="H71" s="78">
+        <f t="shared" si="7"/>
         <v>5547</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="86">
+      <c r="A72" s="77">
         <v>13</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C72" s="54">
+      <c r="C72" s="53">
         <v>11045</v>
       </c>
-      <c r="D72" s="54">
+      <c r="D72" s="53">
         <v>1</v>
       </c>
       <c r="E72" s="5" t="s">
@@ -15572,23 +16023,23 @@
       <c r="F72" s="26">
         <v>2800</v>
       </c>
-      <c r="G72" s="61">
-        <f>F72*0.14</f>
+      <c r="G72" s="60">
+        <f t="shared" si="6"/>
         <v>392.00000000000006</v>
       </c>
-      <c r="H72" s="87">
-        <f>F72-G72</f>
+      <c r="H72" s="78">
+        <f t="shared" si="7"/>
         <v>2408</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="86">
+      <c r="A73" s="77">
         <v>14</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C73" s="54">
+      <c r="C73" s="53">
         <v>11023</v>
       </c>
       <c r="D73" s="39">
@@ -15600,26 +16051,26 @@
       <c r="F73" s="26">
         <v>7200</v>
       </c>
-      <c r="G73" s="61">
-        <f>F73*0.14</f>
+      <c r="G73" s="60">
+        <f t="shared" si="6"/>
         <v>1008.0000000000001</v>
       </c>
-      <c r="H73" s="87">
-        <f>F73-G73</f>
+      <c r="H73" s="78">
+        <f t="shared" si="7"/>
         <v>6192</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="86">
+      <c r="A74" s="77">
         <v>16</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C74" s="54">
+      <c r="C74" s="53">
         <v>11002</v>
       </c>
-      <c r="D74" s="54">
+      <c r="D74" s="53">
         <v>2</v>
       </c>
       <c r="E74" s="5" t="s">
@@ -15628,26 +16079,26 @@
       <c r="F74" s="26">
         <v>4100</v>
       </c>
-      <c r="G74" s="61">
-        <f>F74*0.14</f>
+      <c r="G74" s="60">
+        <f t="shared" si="6"/>
         <v>574</v>
       </c>
-      <c r="H74" s="87">
-        <f>F74-G74</f>
+      <c r="H74" s="78">
+        <f t="shared" si="7"/>
         <v>3526</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="86">
+      <c r="A75" s="77">
         <v>7</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C75" s="54">
+      <c r="C75" s="53">
         <v>11025</v>
       </c>
-      <c r="D75" s="54">
+      <c r="D75" s="53">
         <v>2</v>
       </c>
       <c r="E75" s="5" t="s">
@@ -15656,26 +16107,26 @@
       <c r="F75" s="26">
         <v>7480</v>
       </c>
-      <c r="G75" s="61">
-        <f>F75*0.14</f>
+      <c r="G75" s="60">
+        <f t="shared" si="6"/>
         <v>1047.2</v>
       </c>
-      <c r="H75" s="87">
-        <f>F75-G75</f>
+      <c r="H75" s="78">
+        <f t="shared" si="7"/>
         <v>6432.8</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="86">
+      <c r="A76" s="77">
         <v>10</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C76" s="54">
+      <c r="C76" s="53">
         <v>11033</v>
       </c>
-      <c r="D76" s="54">
+      <c r="D76" s="53">
         <v>2</v>
       </c>
       <c r="E76" s="5" t="s">
@@ -15684,26 +16135,26 @@
       <c r="F76" s="26">
         <v>3460</v>
       </c>
-      <c r="G76" s="61">
-        <f>F76*0.14</f>
+      <c r="G76" s="60">
+        <f t="shared" si="6"/>
         <v>484.40000000000003</v>
       </c>
-      <c r="H76" s="87">
-        <f>F76-G76</f>
+      <c r="H76" s="78">
+        <f t="shared" si="7"/>
         <v>2975.6</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="86">
+      <c r="A77" s="77">
         <v>9</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C77" s="54">
+      <c r="C77" s="53">
         <v>11018</v>
       </c>
-      <c r="D77" s="54">
+      <c r="D77" s="53">
         <v>2</v>
       </c>
       <c r="E77" s="5" t="s">
@@ -15712,26 +16163,26 @@
       <c r="F77" s="26">
         <v>6840</v>
       </c>
-      <c r="G77" s="61">
-        <f>F77*0.14</f>
+      <c r="G77" s="60">
+        <f t="shared" si="6"/>
         <v>957.60000000000014</v>
       </c>
-      <c r="H77" s="87">
-        <f>F77-G77</f>
+      <c r="H77" s="78">
+        <f t="shared" si="7"/>
         <v>5882.4</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="86">
+      <c r="A78" s="77">
         <v>3</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C78" s="54">
+      <c r="C78" s="53">
         <v>11044</v>
       </c>
-      <c r="D78" s="54">
+      <c r="D78" s="53">
         <v>2</v>
       </c>
       <c r="E78" s="5" t="s">
@@ -15740,26 +16191,26 @@
       <c r="F78" s="26">
         <v>4200</v>
       </c>
-      <c r="G78" s="61">
-        <f>F78*0.14</f>
+      <c r="G78" s="60">
+        <f t="shared" si="6"/>
         <v>588</v>
       </c>
-      <c r="H78" s="87">
-        <f>F78-G78</f>
+      <c r="H78" s="78">
+        <f t="shared" si="7"/>
         <v>3612</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="86">
+      <c r="A79" s="77">
         <v>1</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C79" s="54">
+      <c r="C79" s="53">
         <v>11043</v>
       </c>
-      <c r="D79" s="80">
+      <c r="D79" s="71">
         <v>3</v>
       </c>
       <c r="E79" s="5" t="s">
@@ -15768,26 +16219,26 @@
       <c r="F79" s="26">
         <v>3850</v>
       </c>
-      <c r="G79" s="61">
-        <f>F79*0.14</f>
+      <c r="G79" s="60">
+        <f t="shared" si="6"/>
         <v>539</v>
       </c>
-      <c r="H79" s="87">
-        <f>F79-G79</f>
+      <c r="H79" s="78">
+        <f t="shared" si="7"/>
         <v>3311</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="86">
+      <c r="A80" s="77">
         <v>15</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C80" s="54">
+      <c r="C80" s="53">
         <v>11010</v>
       </c>
-      <c r="D80" s="54">
+      <c r="D80" s="53">
         <v>3</v>
       </c>
       <c r="E80" s="5" t="s">
@@ -15796,26 +16247,26 @@
       <c r="F80" s="26">
         <v>3600</v>
       </c>
-      <c r="G80" s="61">
-        <f>F80*0.14</f>
+      <c r="G80" s="60">
+        <f t="shared" si="6"/>
         <v>504.00000000000006</v>
       </c>
-      <c r="H80" s="87">
-        <f>F80-G80</f>
+      <c r="H80" s="78">
+        <f t="shared" si="7"/>
         <v>3096</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="86">
+      <c r="A81" s="77">
         <v>11</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C81" s="54">
+      <c r="C81" s="53">
         <v>11012</v>
       </c>
-      <c r="D81" s="54">
+      <c r="D81" s="53">
         <v>3</v>
       </c>
       <c r="E81" s="5" t="s">
@@ -15824,26 +16275,26 @@
       <c r="F81" s="26">
         <v>3950</v>
       </c>
-      <c r="G81" s="61">
-        <f>F81*0.14</f>
+      <c r="G81" s="60">
+        <f t="shared" si="6"/>
         <v>553</v>
       </c>
-      <c r="H81" s="87">
-        <f>F81-G81</f>
+      <c r="H81" s="78">
+        <f t="shared" si="7"/>
         <v>3397</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="86">
+      <c r="A82" s="77">
         <v>12</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C82" s="54">
+      <c r="C82" s="53">
         <v>11022</v>
       </c>
-      <c r="D82" s="54">
+      <c r="D82" s="53">
         <v>3</v>
       </c>
       <c r="E82" s="5" t="s">
@@ -15852,40 +16303,40 @@
       <c r="F82" s="26">
         <v>3740</v>
       </c>
-      <c r="G82" s="61">
-        <f>F82*0.14</f>
+      <c r="G82" s="60">
+        <f t="shared" si="6"/>
         <v>523.6</v>
       </c>
-      <c r="H82" s="87">
-        <f>F82-G82</f>
+      <c r="H82" s="78">
+        <f t="shared" si="7"/>
         <v>3216.4</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="88">
+      <c r="A83" s="79">
         <v>5</v>
       </c>
-      <c r="B83" s="89" t="s">
+      <c r="B83" s="80" t="s">
         <v>126</v>
       </c>
-      <c r="C83" s="90">
+      <c r="C83" s="81">
         <v>11017</v>
       </c>
-      <c r="D83" s="90">
+      <c r="D83" s="81">
         <v>3</v>
       </c>
-      <c r="E83" s="89" t="s">
+      <c r="E83" s="80" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="91">
+      <c r="F83" s="82">
         <v>6299</v>
       </c>
-      <c r="G83" s="92">
-        <f>F83*0.14</f>
+      <c r="G83" s="83">
+        <f t="shared" si="6"/>
         <v>881.86000000000013</v>
       </c>
-      <c r="H83" s="93">
-        <f>F83-G83</f>
+      <c r="H83" s="84">
+        <f t="shared" si="7"/>
         <v>5417.1399999999994</v>
       </c>
     </row>
@@ -15907,197 +16358,2223 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
     <col min="2" max="2" width="7.7109375" customWidth="1"/>
     <col min="3" max="3" width="7.85546875" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
     <col min="5" max="5" width="12.28515625" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+    <row r="1" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="152" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-    </row>
-    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="B1" s="153"/>
+      <c r="C1" s="153"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="153"/>
+      <c r="F1" s="154"/>
+    </row>
+    <row r="2" spans="1:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="94" t="s">
         <v>153</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="97" t="s">
+      <c r="C2" s="96" t="s">
         <v>156</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="95" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="98" t="s">
+      <c r="E2" s="97" t="s">
         <v>154</v>
       </c>
-      <c r="F2" s="53" t="s">
+      <c r="F2" s="98" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="100" t="s">
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+    </row>
+    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="104" t="s">
+        <v>163</v>
+      </c>
+      <c r="B3" s="105">
+        <v>8.5</v>
+      </c>
+      <c r="C3" s="106">
+        <v>500</v>
+      </c>
+      <c r="D3" s="105">
+        <f t="shared" ref="D3:D12" si="0">B3*C3</f>
+        <v>4250</v>
+      </c>
+      <c r="E3" s="107">
+        <v>46169</v>
+      </c>
+      <c r="F3" s="108" t="str">
+        <f t="shared" ref="F3:F12" ca="1" si="1">IF(E3&lt;TODAY(),"просроченно","не просроченно")</f>
+        <v>просроченно</v>
+      </c>
+      <c r="H3" s="24"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+    </row>
+    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="86" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" s="85">
+        <v>31.2</v>
+      </c>
+      <c r="C4" s="7">
+        <v>270</v>
+      </c>
+      <c r="D4" s="91">
+        <f t="shared" si="0"/>
+        <v>8424</v>
+      </c>
+      <c r="E4" s="101">
+        <v>46171</v>
+      </c>
+      <c r="F4" s="93" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>просроченно</v>
+      </c>
+      <c r="H4" s="24"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="103"/>
+      <c r="L4" s="100"/>
+      <c r="M4" s="100"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="86" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5" s="85">
+        <v>12.3</v>
+      </c>
+      <c r="C5" s="7">
+        <v>35</v>
+      </c>
+      <c r="D5" s="91">
+        <f t="shared" si="0"/>
+        <v>430.5</v>
+      </c>
+      <c r="E5" s="101">
+        <v>46165</v>
+      </c>
+      <c r="F5" s="93" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>просроченно</v>
+      </c>
+      <c r="H5" s="24"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
+      <c r="L5" s="100"/>
+      <c r="M5" s="100"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="86" t="s">
         <v>157</v>
       </c>
-      <c r="B3" s="99">
+      <c r="B6" s="85">
         <v>8.5</v>
       </c>
-      <c r="C3" s="56">
+      <c r="C6" s="7">
         <v>125</v>
       </c>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="100" t="s">
+      <c r="D6" s="91">
+        <f t="shared" si="0"/>
+        <v>1062.5</v>
+      </c>
+      <c r="E6" s="101">
+        <v>46163</v>
+      </c>
+      <c r="F6" s="93" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>просроченно</v>
+      </c>
+      <c r="H6" s="24"/>
+      <c r="I6" s="103"/>
+      <c r="J6" s="103"/>
+      <c r="K6" s="24"/>
+    </row>
+    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="86" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7" s="85">
+        <v>24.5</v>
+      </c>
+      <c r="C7" s="7">
+        <v>450</v>
+      </c>
+      <c r="D7" s="91">
+        <f t="shared" si="0"/>
+        <v>11025</v>
+      </c>
+      <c r="E7" s="101">
+        <v>46168</v>
+      </c>
+      <c r="F7" s="93" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>просроченно</v>
+      </c>
+      <c r="H7" s="24"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="103"/>
+      <c r="K7" s="24"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="86" t="s">
+        <v>160</v>
+      </c>
+      <c r="B8" s="85">
+        <v>7.6</v>
+      </c>
+      <c r="C8" s="7">
+        <v>320</v>
+      </c>
+      <c r="D8" s="91">
+        <f t="shared" si="0"/>
+        <v>2432</v>
+      </c>
+      <c r="E8" s="101">
+        <v>46166</v>
+      </c>
+      <c r="F8" s="93" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>просроченно</v>
+      </c>
+      <c r="H8" s="24"/>
+      <c r="I8" s="103"/>
+      <c r="J8" s="103"/>
+      <c r="K8" s="24"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="86" t="s">
         <v>158</v>
       </c>
-      <c r="B4" s="99">
+      <c r="B9" s="85">
         <v>8.5</v>
       </c>
-      <c r="C4" s="56">
+      <c r="C9" s="7">
         <v>240</v>
       </c>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="100" t="s">
-        <v>159</v>
-      </c>
-      <c r="B5" s="99">
-        <v>12.3</v>
-      </c>
-      <c r="C5" s="56">
-        <v>35</v>
-      </c>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="100" t="s">
-        <v>160</v>
-      </c>
-      <c r="B6" s="99">
-        <v>7.6</v>
-      </c>
-      <c r="C6" s="56">
-        <v>320</v>
-      </c>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="100" t="s">
+      <c r="D9" s="91">
+        <f t="shared" si="0"/>
+        <v>2040</v>
+      </c>
+      <c r="E9" s="101">
+        <v>46164</v>
+      </c>
+      <c r="F9" s="93" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>просроченно</v>
+      </c>
+      <c r="H9" s="24"/>
+      <c r="I9" s="103"/>
+      <c r="J9" s="103"/>
+      <c r="K9" s="24"/>
+    </row>
+    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="86" t="s">
+        <v>158</v>
+      </c>
+      <c r="B10" s="85">
+        <v>6.3</v>
+      </c>
+      <c r="C10" s="7">
+        <v>610</v>
+      </c>
+      <c r="D10" s="91">
+        <f t="shared" si="0"/>
+        <v>3843</v>
+      </c>
+      <c r="E10" s="101">
+        <v>46172</v>
+      </c>
+      <c r="F10" s="93" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>просроченно</v>
+      </c>
+      <c r="I10" s="100"/>
+      <c r="J10" s="100"/>
+    </row>
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="86" t="s">
         <v>161</v>
       </c>
-      <c r="B7" s="99">
+      <c r="B11" s="85">
         <v>7.8</v>
       </c>
-      <c r="C7" s="56">
+      <c r="C11" s="7">
         <v>450</v>
       </c>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="100" t="s">
-        <v>162</v>
-      </c>
-      <c r="B8" s="99">
-        <v>24.5</v>
-      </c>
-      <c r="C8" s="56">
-        <v>450</v>
-      </c>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="100" t="s">
-        <v>163</v>
-      </c>
-      <c r="B9" s="99">
-        <v>8.5</v>
-      </c>
-      <c r="C9" s="56">
-        <v>500</v>
-      </c>
-      <c r="D9" s="56"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="100" t="s">
+      <c r="D11" s="91">
+        <f t="shared" si="0"/>
+        <v>3510</v>
+      </c>
+      <c r="E11" s="101">
+        <v>46167</v>
+      </c>
+      <c r="F11" s="93" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>просроченно</v>
+      </c>
+      <c r="I11" s="100"/>
+      <c r="J11" s="100"/>
+    </row>
+    <row r="12" spans="1:16" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="87" t="s">
         <v>164</v>
       </c>
-      <c r="B10" s="99">
+      <c r="B12" s="88">
         <v>8</v>
       </c>
-      <c r="C10" s="56">
+      <c r="C12" s="89">
         <v>370</v>
       </c>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="100" t="s">
-        <v>165</v>
-      </c>
-      <c r="B11" s="99">
-        <v>31.2</v>
-      </c>
-      <c r="C11" s="56">
-        <v>270</v>
-      </c>
-      <c r="D11" s="56"/>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="100" t="s">
-        <v>158</v>
-      </c>
-      <c r="B12" s="99">
-        <v>6.3</v>
-      </c>
-      <c r="C12" s="56">
-        <v>610</v>
-      </c>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="56"/>
-      <c r="B13" s="56"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
+      <c r="D12" s="109">
+        <f t="shared" si="0"/>
+        <v>2960</v>
+      </c>
+      <c r="E12" s="110">
+        <v>46170</v>
+      </c>
+      <c r="F12" s="111" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>просроченно</v>
+      </c>
+      <c r="I12" s="100"/>
+      <c r="J12" s="100"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="55"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="I13" s="100"/>
+      <c r="J13" s="100"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I14" s="100"/>
+      <c r="J14" s="100"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N16" s="100"/>
+      <c r="O16" s="100"/>
+      <c r="P16" s="100"/>
+    </row>
+    <row r="17" spans="14:16" x14ac:dyDescent="0.25">
+      <c r="N17" s="100"/>
+      <c r="O17" s="100"/>
+      <c r="P17" s="100"/>
+    </row>
+    <row r="18" spans="14:16" x14ac:dyDescent="0.25">
+      <c r="N18" s="100"/>
+      <c r="O18" s="100"/>
+      <c r="P18" s="100"/>
+    </row>
+    <row r="19" spans="14:16" x14ac:dyDescent="0.25">
+      <c r="N19" s="100"/>
+      <c r="O19" s="100"/>
+      <c r="P19" s="100"/>
+    </row>
+    <row r="20" spans="14:16" x14ac:dyDescent="0.25">
+      <c r="N20" s="100"/>
+      <c r="O20" s="100"/>
+      <c r="P20" s="100"/>
+    </row>
+    <row r="21" spans="14:16" x14ac:dyDescent="0.25">
+      <c r="N21" s="100"/>
+      <c r="O21" s="100"/>
+      <c r="P21" s="100"/>
+    </row>
+    <row r="22" spans="14:16" x14ac:dyDescent="0.25">
+      <c r="N22" s="100"/>
+      <c r="O22" s="100"/>
+      <c r="P22" s="100"/>
+    </row>
+    <row r="23" spans="14:16" x14ac:dyDescent="0.25">
+      <c r="N23" s="100"/>
+      <c r="O23" s="100"/>
+      <c r="P23" s="100"/>
+    </row>
+    <row r="24" spans="14:16" x14ac:dyDescent="0.25">
+      <c r="N24" s="100"/>
+      <c r="O24" s="100"/>
+      <c r="P24" s="100"/>
     </row>
   </sheetData>
+  <autoFilter ref="A2:F12">
+    <filterColumn colId="3">
+      <customFilters>
+        <customFilter operator="lessThan" val="4000"/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="5">
+      <filters>
+        <filter val="просроченно"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState ref="A3:F12">
+    <sortCondition ref="A3:A12"/>
+    <sortCondition descending="1" ref="B3:B12"/>
+  </sortState>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="94" t="s">
+        <v>153</v>
+      </c>
+      <c r="B1" s="95" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="96" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1" s="95" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="97" t="s">
+        <v>154</v>
+      </c>
+      <c r="F1" s="98" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="104" t="s">
+        <v>163</v>
+      </c>
+      <c r="B2" s="105">
+        <v>8.5</v>
+      </c>
+      <c r="C2" s="106">
+        <v>500</v>
+      </c>
+      <c r="D2" s="105">
+        <f t="shared" ref="D2:D11" si="0">B2*C2</f>
+        <v>4250</v>
+      </c>
+      <c r="E2" s="107">
+        <v>46169</v>
+      </c>
+      <c r="F2" s="108" t="str">
+        <f t="shared" ref="F2:F11" ca="1" si="1">IF(E2&lt;TODAY(),"просроченно","не просроченно")</f>
+        <v>просроченно</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="86" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" s="85">
+        <v>31.2</v>
+      </c>
+      <c r="C3" s="7">
+        <v>270</v>
+      </c>
+      <c r="D3" s="91">
+        <f t="shared" si="0"/>
+        <v>8424</v>
+      </c>
+      <c r="E3" s="101">
+        <v>46171</v>
+      </c>
+      <c r="F3" s="93" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>просроченно</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="86" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="85">
+        <v>12.3</v>
+      </c>
+      <c r="C4" s="7">
+        <v>35</v>
+      </c>
+      <c r="D4" s="91">
+        <f t="shared" si="0"/>
+        <v>430.5</v>
+      </c>
+      <c r="E4" s="101">
+        <v>46165</v>
+      </c>
+      <c r="F4" s="93" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>просроченно</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="86" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="85">
+        <v>8.5</v>
+      </c>
+      <c r="C5" s="7">
+        <v>125</v>
+      </c>
+      <c r="D5" s="91">
+        <f t="shared" si="0"/>
+        <v>1062.5</v>
+      </c>
+      <c r="E5" s="101">
+        <v>46163</v>
+      </c>
+      <c r="F5" s="93" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>просроченно</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="86" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" s="85">
+        <v>24.5</v>
+      </c>
+      <c r="C6" s="7">
+        <v>450</v>
+      </c>
+      <c r="D6" s="91">
+        <f t="shared" si="0"/>
+        <v>11025</v>
+      </c>
+      <c r="E6" s="101">
+        <v>46168</v>
+      </c>
+      <c r="F6" s="93" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>просроченно</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="86" t="s">
+        <v>160</v>
+      </c>
+      <c r="B7" s="85">
+        <v>7.6</v>
+      </c>
+      <c r="C7" s="7">
+        <v>320</v>
+      </c>
+      <c r="D7" s="91">
+        <f t="shared" si="0"/>
+        <v>2432</v>
+      </c>
+      <c r="E7" s="101">
+        <v>46166</v>
+      </c>
+      <c r="F7" s="93" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>просроченно</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="86" t="s">
+        <v>158</v>
+      </c>
+      <c r="B8" s="85">
+        <v>8.5</v>
+      </c>
+      <c r="C8" s="7">
+        <v>240</v>
+      </c>
+      <c r="D8" s="91">
+        <f t="shared" si="0"/>
+        <v>2040</v>
+      </c>
+      <c r="E8" s="101">
+        <v>46164</v>
+      </c>
+      <c r="F8" s="93" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>просроченно</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="86" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9" s="85">
+        <v>6.3</v>
+      </c>
+      <c r="C9" s="7">
+        <v>610</v>
+      </c>
+      <c r="D9" s="91">
+        <f t="shared" si="0"/>
+        <v>3843</v>
+      </c>
+      <c r="E9" s="101">
+        <v>46172</v>
+      </c>
+      <c r="F9" s="93" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>просроченно</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="86" t="s">
+        <v>161</v>
+      </c>
+      <c r="B10" s="85">
+        <v>7.8</v>
+      </c>
+      <c r="C10" s="7">
+        <v>450</v>
+      </c>
+      <c r="D10" s="91">
+        <f t="shared" si="0"/>
+        <v>3510</v>
+      </c>
+      <c r="E10" s="101">
+        <v>46167</v>
+      </c>
+      <c r="F10" s="93" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>просроченно</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="87" t="s">
+        <v>164</v>
+      </c>
+      <c r="B11" s="88">
+        <v>8</v>
+      </c>
+      <c r="C11" s="89">
+        <v>370</v>
+      </c>
+      <c r="D11" s="109">
+        <f t="shared" si="0"/>
+        <v>2960</v>
+      </c>
+      <c r="E11" s="110">
+        <v>46170</v>
+      </c>
+      <c r="F11" s="111" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>просроченно</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="70"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="112"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="113"/>
+      <c r="F13" s="70"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="114"/>
+      <c r="B14" s="115"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="115"/>
+      <c r="E14" s="102"/>
+      <c r="F14" s="65"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="114"/>
+      <c r="B15" s="115"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="115"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="65"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="114"/>
+      <c r="B16" s="115"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="115"/>
+      <c r="E16" s="102"/>
+      <c r="F16" s="65"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="114"/>
+      <c r="B17" s="115"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="115"/>
+      <c r="E17" s="102"/>
+      <c r="F17" s="65"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" customWidth="1"/>
+    <col min="12" max="12" width="16.85546875" customWidth="1"/>
+    <col min="13" max="13" width="21.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="161" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
+      <c r="H1" s="155" t="s">
+        <v>169</v>
+      </c>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="156"/>
+      <c r="M1" s="157"/>
+    </row>
+    <row r="2" spans="1:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="94" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="95" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="96" t="s">
+        <v>156</v>
+      </c>
+      <c r="D2" s="95" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="97" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" s="98" t="s">
+        <v>155</v>
+      </c>
+      <c r="H2" s="116" t="s">
+        <v>153</v>
+      </c>
+      <c r="I2" s="95" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="96" t="s">
+        <v>156</v>
+      </c>
+      <c r="K2" s="95" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="97" t="s">
+        <v>154</v>
+      </c>
+      <c r="M2" s="98" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="86" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="85">
+        <v>12.3</v>
+      </c>
+      <c r="C3" s="7">
+        <v>35</v>
+      </c>
+      <c r="D3" s="91">
+        <v>430.5</v>
+      </c>
+      <c r="E3" s="101">
+        <v>46165</v>
+      </c>
+      <c r="F3" s="93" t="s">
+        <v>166</v>
+      </c>
+      <c r="H3" s="90" t="s">
+        <v>163</v>
+      </c>
+      <c r="I3" s="91">
+        <v>8.5</v>
+      </c>
+      <c r="J3" s="92">
+        <v>500</v>
+      </c>
+      <c r="K3" s="91">
+        <v>4250</v>
+      </c>
+      <c r="L3" s="101">
+        <v>46169</v>
+      </c>
+      <c r="M3" s="93" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="86" t="s">
+        <v>157</v>
+      </c>
+      <c r="B4" s="85">
+        <v>8.5</v>
+      </c>
+      <c r="C4" s="7">
+        <v>125</v>
+      </c>
+      <c r="D4" s="91">
+        <v>1062.5</v>
+      </c>
+      <c r="E4" s="101">
+        <v>46163</v>
+      </c>
+      <c r="F4" s="93" t="s">
+        <v>166</v>
+      </c>
+      <c r="H4" s="86" t="s">
+        <v>162</v>
+      </c>
+      <c r="I4" s="85">
+        <v>24.5</v>
+      </c>
+      <c r="J4" s="7">
+        <v>450</v>
+      </c>
+      <c r="K4" s="91">
+        <v>11025</v>
+      </c>
+      <c r="L4" s="101">
+        <v>46168</v>
+      </c>
+      <c r="M4" s="93" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="86" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" s="85">
+        <v>7.6</v>
+      </c>
+      <c r="C5" s="7">
+        <v>320</v>
+      </c>
+      <c r="D5" s="91">
+        <v>2432</v>
+      </c>
+      <c r="E5" s="101">
+        <v>46166</v>
+      </c>
+      <c r="F5" s="93" t="s">
+        <v>166</v>
+      </c>
+      <c r="H5" s="86" t="s">
+        <v>158</v>
+      </c>
+      <c r="I5" s="85">
+        <v>6.3</v>
+      </c>
+      <c r="J5" s="7">
+        <v>610</v>
+      </c>
+      <c r="K5" s="91">
+        <v>3843</v>
+      </c>
+      <c r="L5" s="101">
+        <v>46172</v>
+      </c>
+      <c r="M5" s="93" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="87" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6" s="88">
+        <v>8.5</v>
+      </c>
+      <c r="C6" s="89">
+        <v>240</v>
+      </c>
+      <c r="D6" s="109">
+        <v>2040</v>
+      </c>
+      <c r="E6" s="110">
+        <v>46164</v>
+      </c>
+      <c r="F6" s="111" t="s">
+        <v>166</v>
+      </c>
+      <c r="H6" s="86" t="s">
+        <v>161</v>
+      </c>
+      <c r="I6" s="85">
+        <v>7.8</v>
+      </c>
+      <c r="J6" s="7">
+        <v>450</v>
+      </c>
+      <c r="K6" s="91">
+        <v>3510</v>
+      </c>
+      <c r="L6" s="101">
+        <v>46167</v>
+      </c>
+      <c r="M6" s="93" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H7" s="87" t="s">
+        <v>164</v>
+      </c>
+      <c r="I7" s="88">
+        <v>8</v>
+      </c>
+      <c r="J7" s="89">
+        <v>370</v>
+      </c>
+      <c r="K7" s="109">
+        <v>2960</v>
+      </c>
+      <c r="L7" s="110">
+        <v>46170</v>
+      </c>
+      <c r="M7" s="111" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="158" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" s="159"/>
+      <c r="C8" s="159"/>
+      <c r="D8" s="159"/>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+    </row>
+    <row r="9" spans="1:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="94" t="s">
+        <v>153</v>
+      </c>
+      <c r="B9" s="95" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="96" t="s">
+        <v>156</v>
+      </c>
+      <c r="D9" s="95" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="97" t="s">
+        <v>154</v>
+      </c>
+      <c r="F9" s="98" t="s">
+        <v>155</v>
+      </c>
+      <c r="H9" s="161" t="s">
+        <v>171</v>
+      </c>
+      <c r="I9" s="162"/>
+      <c r="J9" s="162"/>
+      <c r="K9" s="162"/>
+      <c r="L9" s="162"/>
+      <c r="M9" s="163"/>
+    </row>
+    <row r="10" spans="1:13" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="87" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="88">
+        <v>12.3</v>
+      </c>
+      <c r="C10" s="89">
+        <v>35</v>
+      </c>
+      <c r="D10" s="109">
+        <v>430.5</v>
+      </c>
+      <c r="E10" s="110">
+        <v>46165</v>
+      </c>
+      <c r="F10" s="111" t="s">
+        <v>166</v>
+      </c>
+      <c r="H10" s="94" t="s">
+        <v>153</v>
+      </c>
+      <c r="I10" s="95" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="96" t="s">
+        <v>156</v>
+      </c>
+      <c r="K10" s="95" t="s">
+        <v>33</v>
+      </c>
+      <c r="L10" s="97" t="s">
+        <v>154</v>
+      </c>
+      <c r="M10" s="98" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H11" s="117" t="s">
+        <v>159</v>
+      </c>
+      <c r="I11" s="118">
+        <v>12.3</v>
+      </c>
+      <c r="J11" s="20">
+        <v>35</v>
+      </c>
+      <c r="K11" s="118">
+        <v>430.5</v>
+      </c>
+      <c r="L11" s="119">
+        <v>46165</v>
+      </c>
+      <c r="M11" s="120" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H12" s="121" t="s">
+        <v>157</v>
+      </c>
+      <c r="I12" s="122">
+        <v>8.5</v>
+      </c>
+      <c r="J12" s="69">
+        <v>125</v>
+      </c>
+      <c r="K12" s="118">
+        <v>1062.5</v>
+      </c>
+      <c r="L12" s="119">
+        <v>46163</v>
+      </c>
+      <c r="M12" s="120" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H13" s="121" t="s">
+        <v>160</v>
+      </c>
+      <c r="I13" s="122">
+        <v>7.6</v>
+      </c>
+      <c r="J13" s="69">
+        <v>320</v>
+      </c>
+      <c r="K13" s="118">
+        <v>2432</v>
+      </c>
+      <c r="L13" s="119">
+        <v>46166</v>
+      </c>
+      <c r="M13" s="120" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H14" s="123" t="s">
+        <v>158</v>
+      </c>
+      <c r="I14" s="124">
+        <v>8.5</v>
+      </c>
+      <c r="J14" s="81">
+        <v>240</v>
+      </c>
+      <c r="K14" s="125">
+        <v>2040</v>
+      </c>
+      <c r="L14" s="126">
+        <v>46164</v>
+      </c>
+      <c r="M14" s="127" t="s">
+        <v>166</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="H9:M9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.5703125" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" customWidth="1"/>
+    <col min="3" max="3" width="36.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" customWidth="1"/>
+    <col min="7" max="7" width="1.7109375" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" customWidth="1"/>
+    <col min="14" max="14" width="16.28515625" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1" s="172" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1" s="173" t="s">
+        <v>175</v>
+      </c>
+      <c r="E1" s="173" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1" s="173" t="s">
+        <v>177</v>
+      </c>
+      <c r="H1" s="99" t="s">
+        <v>186</v>
+      </c>
+      <c r="L1" s="152" t="s">
+        <v>189</v>
+      </c>
+      <c r="M1" s="164"/>
+      <c r="N1" s="164"/>
+      <c r="O1" s="165"/>
+    </row>
+    <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="58" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2" s="172"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
+      <c r="F2" s="173"/>
+      <c r="H2" s="99" t="s">
+        <v>187</v>
+      </c>
+      <c r="L2" s="137" t="s">
+        <v>190</v>
+      </c>
+      <c r="M2" s="134" t="s">
+        <v>114</v>
+      </c>
+      <c r="N2" s="134" t="s">
+        <v>192</v>
+      </c>
+      <c r="O2" s="138" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="129">
+        <v>1</v>
+      </c>
+      <c r="B3" s="129">
+        <v>0</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="D3" s="131">
+        <f>H3</f>
+        <v>151.29770992366412</v>
+      </c>
+      <c r="E3" s="41">
+        <v>5</v>
+      </c>
+      <c r="F3" s="131">
+        <f>D3*E3</f>
+        <v>756.48854961832058</v>
+      </c>
+      <c r="H3" s="132">
+        <v>151.29770992366412</v>
+      </c>
+      <c r="L3" s="166">
+        <v>1</v>
+      </c>
+      <c r="M3" s="135" t="s">
+        <v>178</v>
+      </c>
+      <c r="N3" s="135">
+        <v>5</v>
+      </c>
+      <c r="O3" s="169">
+        <f>H3</f>
+        <v>151.29770992366412</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="129">
+        <v>1.5</v>
+      </c>
+      <c r="B4" s="129">
+        <v>0</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" s="131">
+        <f>$H$3*A4+B4</f>
+        <v>226.94656488549617</v>
+      </c>
+      <c r="E4" s="41">
+        <v>8</v>
+      </c>
+      <c r="F4" s="131">
+        <f t="shared" ref="F4:F10" si="0">D4*E4</f>
+        <v>1815.5725190839694</v>
+      </c>
+      <c r="L4" s="167"/>
+      <c r="M4" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="N4" s="41">
+        <v>8</v>
+      </c>
+      <c r="O4" s="170"/>
+    </row>
+    <row r="5" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="129">
+        <v>3</v>
+      </c>
+      <c r="B5" s="129">
+        <v>0</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="131">
+        <f t="shared" ref="D5:D10" si="1">$H$3*A5+B5</f>
+        <v>453.89312977099235</v>
+      </c>
+      <c r="E5" s="41">
+        <v>10</v>
+      </c>
+      <c r="F5" s="131">
+        <f t="shared" si="0"/>
+        <v>4538.9312977099235</v>
+      </c>
+      <c r="L5" s="168"/>
+      <c r="M5" s="136" t="s">
+        <v>180</v>
+      </c>
+      <c r="N5" s="136">
+        <v>10</v>
+      </c>
+      <c r="O5" s="171"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="129">
+        <v>3</v>
+      </c>
+      <c r="B6" s="129">
+        <v>30</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>182</v>
+      </c>
+      <c r="D6" s="131">
+        <f t="shared" si="1"/>
+        <v>483.89312977099235</v>
+      </c>
+      <c r="E6" s="41">
+        <v>1</v>
+      </c>
+      <c r="F6" s="131">
+        <f t="shared" si="0"/>
+        <v>483.89312977099235</v>
+      </c>
+      <c r="L6" s="166">
+        <v>2</v>
+      </c>
+      <c r="M6" s="135" t="s">
+        <v>178</v>
+      </c>
+      <c r="N6" s="135">
+        <v>6</v>
+      </c>
+      <c r="O6" s="169">
+        <f>H16</f>
+        <v>12.608142493638798</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="129">
+        <v>2</v>
+      </c>
+      <c r="B7" s="129">
+        <v>0</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" s="131">
+        <f t="shared" si="1"/>
+        <v>302.59541984732823</v>
+      </c>
+      <c r="E7" s="41">
+        <v>3</v>
+      </c>
+      <c r="F7" s="131">
+        <f t="shared" si="0"/>
+        <v>907.78625954198469</v>
+      </c>
+      <c r="L7" s="167"/>
+      <c r="M7" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="N7" s="41">
+        <v>9</v>
+      </c>
+      <c r="O7" s="170"/>
+    </row>
+    <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="129">
+        <v>1.5</v>
+      </c>
+      <c r="B8" s="129">
+        <v>40</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>181</v>
+      </c>
+      <c r="D8" s="131">
+        <f t="shared" si="1"/>
+        <v>266.94656488549617</v>
+      </c>
+      <c r="E8" s="41">
+        <v>1</v>
+      </c>
+      <c r="F8" s="131">
+        <f t="shared" si="0"/>
+        <v>266.94656488549617</v>
+      </c>
+      <c r="L8" s="168"/>
+      <c r="M8" s="136" t="s">
+        <v>180</v>
+      </c>
+      <c r="N8" s="136">
+        <v>11</v>
+      </c>
+      <c r="O8" s="171"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="129">
+        <v>4</v>
+      </c>
+      <c r="B9" s="129">
+        <v>0</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" s="131">
+        <f t="shared" si="1"/>
+        <v>605.19083969465646</v>
+      </c>
+      <c r="E9" s="41">
+        <v>1</v>
+      </c>
+      <c r="F9" s="131">
+        <f t="shared" si="0"/>
+        <v>605.19083969465646</v>
+      </c>
+      <c r="L9" s="166">
+        <v>3</v>
+      </c>
+      <c r="M9" s="135" t="s">
+        <v>178</v>
+      </c>
+      <c r="N9" s="135">
+        <v>7</v>
+      </c>
+      <c r="O9" s="169">
+        <f>H29</f>
+        <v>-86.455834242093786</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="129">
+        <v>4</v>
+      </c>
+      <c r="B10" s="129">
+        <v>20</v>
+      </c>
+      <c r="C10" s="130" t="s">
+        <v>185</v>
+      </c>
+      <c r="D10" s="131">
+        <f t="shared" si="1"/>
+        <v>625.19083969465646</v>
+      </c>
+      <c r="E10" s="41">
+        <v>1</v>
+      </c>
+      <c r="F10" s="131">
+        <f t="shared" si="0"/>
+        <v>625.19083969465646</v>
+      </c>
+      <c r="L10" s="167"/>
+      <c r="M10" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="N10" s="41">
+        <v>10</v>
+      </c>
+      <c r="O10" s="170"/>
+    </row>
+    <row r="11" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="128"/>
+      <c r="B11" s="128"/>
+      <c r="D11" s="57"/>
+      <c r="L11" s="168"/>
+      <c r="M11" s="136" t="s">
+        <v>180</v>
+      </c>
+      <c r="N11" s="136">
+        <v>12</v>
+      </c>
+      <c r="O11" s="171"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C12" s="99" t="s">
+        <v>188</v>
+      </c>
+      <c r="D12" s="57">
+        <f>SUM(D3:D10)</f>
+        <v>3115.9541984732823</v>
+      </c>
+      <c r="F12" s="57">
+        <f>SUM(F3:F10)</f>
+        <v>10000</v>
+      </c>
+      <c r="L12" s="166">
+        <v>4</v>
+      </c>
+      <c r="M12" s="135" t="s">
+        <v>178</v>
+      </c>
+      <c r="N12" s="135">
+        <v>7</v>
+      </c>
+      <c r="O12" s="169">
+        <f>H42</f>
+        <v>-21.613958560523393</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L13" s="167"/>
+      <c r="M13" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="N13" s="41">
+        <v>10</v>
+      </c>
+      <c r="O13" s="170"/>
+    </row>
+    <row r="14" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="B14" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="C14" s="172" t="s">
+        <v>114</v>
+      </c>
+      <c r="D14" s="173" t="s">
+        <v>175</v>
+      </c>
+      <c r="E14" s="173" t="s">
+        <v>176</v>
+      </c>
+      <c r="F14" s="173" t="s">
+        <v>177</v>
+      </c>
+      <c r="H14" s="99" t="s">
+        <v>186</v>
+      </c>
+      <c r="L14" s="168"/>
+      <c r="M14" s="136" t="s">
+        <v>180</v>
+      </c>
+      <c r="N14" s="136">
+        <v>11</v>
+      </c>
+      <c r="O14" s="171"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="B15" s="58" t="s">
+        <v>173</v>
+      </c>
+      <c r="C15" s="172"/>
+      <c r="D15" s="173"/>
+      <c r="E15" s="173"/>
+      <c r="F15" s="173"/>
+      <c r="H15" s="99" t="s">
+        <v>187</v>
+      </c>
+      <c r="L15" s="133"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="129">
+        <v>1</v>
+      </c>
+      <c r="B16" s="129">
+        <v>0</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="D16" s="131">
+        <f>H16</f>
+        <v>12.608142493638798</v>
+      </c>
+      <c r="E16" s="41">
+        <v>6</v>
+      </c>
+      <c r="F16" s="131">
+        <f>D16*E16</f>
+        <v>75.648854961832797</v>
+      </c>
+      <c r="H16" s="132">
+        <v>12.608142493638798</v>
+      </c>
+      <c r="L16" s="133"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="129">
+        <v>1.5</v>
+      </c>
+      <c r="B17" s="129">
+        <v>0</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="D17" s="131">
+        <f>$H$3*A17+B17</f>
+        <v>226.94656488549617</v>
+      </c>
+      <c r="E17" s="41">
+        <v>9</v>
+      </c>
+      <c r="F17" s="131">
+        <f t="shared" ref="F17:F23" si="2">D17*E17</f>
+        <v>2042.5190839694656</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="129">
+        <v>3</v>
+      </c>
+      <c r="B18" s="129">
+        <v>0</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>180</v>
+      </c>
+      <c r="D18" s="131">
+        <f t="shared" ref="D18:D23" si="3">$H$3*A18+B18</f>
+        <v>453.89312977099235</v>
+      </c>
+      <c r="E18" s="41">
+        <v>11</v>
+      </c>
+      <c r="F18" s="131">
+        <f t="shared" si="2"/>
+        <v>4992.8244274809158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="129">
+        <v>3</v>
+      </c>
+      <c r="B19" s="129">
+        <v>30</v>
+      </c>
+      <c r="C19" s="41" t="s">
+        <v>182</v>
+      </c>
+      <c r="D19" s="131">
+        <f t="shared" si="3"/>
+        <v>483.89312977099235</v>
+      </c>
+      <c r="E19" s="41">
+        <v>1</v>
+      </c>
+      <c r="F19" s="131">
+        <f t="shared" si="2"/>
+        <v>483.89312977099235</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="129">
+        <v>2</v>
+      </c>
+      <c r="B20" s="129">
+        <v>0</v>
+      </c>
+      <c r="C20" s="130" t="s">
+        <v>183</v>
+      </c>
+      <c r="D20" s="131">
+        <f t="shared" si="3"/>
+        <v>302.59541984732823</v>
+      </c>
+      <c r="E20" s="41">
+        <v>3</v>
+      </c>
+      <c r="F20" s="131">
+        <f t="shared" si="2"/>
+        <v>907.78625954198469</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="129">
+        <v>1.5</v>
+      </c>
+      <c r="B21" s="129">
+        <v>40</v>
+      </c>
+      <c r="C21" s="130" t="s">
+        <v>181</v>
+      </c>
+      <c r="D21" s="131">
+        <f t="shared" si="3"/>
+        <v>266.94656488549617</v>
+      </c>
+      <c r="E21" s="41">
+        <v>1</v>
+      </c>
+      <c r="F21" s="131">
+        <f t="shared" si="2"/>
+        <v>266.94656488549617</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="129">
+        <v>4</v>
+      </c>
+      <c r="B22" s="129">
+        <v>0</v>
+      </c>
+      <c r="C22" s="130" t="s">
+        <v>184</v>
+      </c>
+      <c r="D22" s="131">
+        <f t="shared" si="3"/>
+        <v>605.19083969465646</v>
+      </c>
+      <c r="E22" s="41">
+        <v>1</v>
+      </c>
+      <c r="F22" s="131">
+        <f t="shared" si="2"/>
+        <v>605.19083969465646</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="129">
+        <v>4</v>
+      </c>
+      <c r="B23" s="129">
+        <v>20</v>
+      </c>
+      <c r="C23" s="130" t="s">
+        <v>185</v>
+      </c>
+      <c r="D23" s="131">
+        <f t="shared" si="3"/>
+        <v>625.19083969465646</v>
+      </c>
+      <c r="E23" s="41">
+        <v>1</v>
+      </c>
+      <c r="F23" s="131">
+        <f t="shared" si="2"/>
+        <v>625.19083969465646</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="128"/>
+      <c r="B24" s="128"/>
+      <c r="D24" s="57"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C25" s="99" t="s">
+        <v>188</v>
+      </c>
+      <c r="D25" s="57">
+        <f>SUM(D16:D23)</f>
+        <v>2977.2646310432569</v>
+      </c>
+      <c r="F25" s="57">
+        <f>SUM(F16:F23)</f>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="B27" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="C27" s="172" t="s">
+        <v>114</v>
+      </c>
+      <c r="D27" s="173" t="s">
+        <v>175</v>
+      </c>
+      <c r="E27" s="173" t="s">
+        <v>176</v>
+      </c>
+      <c r="F27" s="173" t="s">
+        <v>177</v>
+      </c>
+      <c r="H27" s="99" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="B28" s="58" t="s">
+        <v>173</v>
+      </c>
+      <c r="C28" s="172"/>
+      <c r="D28" s="173"/>
+      <c r="E28" s="173"/>
+      <c r="F28" s="173"/>
+      <c r="H28" s="99" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="129">
+        <v>1</v>
+      </c>
+      <c r="B29" s="129">
+        <v>0</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="D29" s="131">
+        <f>H29</f>
+        <v>-86.455834242093786</v>
+      </c>
+      <c r="E29" s="41">
+        <v>7</v>
+      </c>
+      <c r="F29" s="131">
+        <f>D29*E29</f>
+        <v>-605.19083969465646</v>
+      </c>
+      <c r="H29" s="132">
+        <v>-86.455834242093786</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="129">
+        <v>1.5</v>
+      </c>
+      <c r="B30" s="129">
+        <v>0</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="D30" s="131">
+        <f>$H$3*A30+B30</f>
+        <v>226.94656488549617</v>
+      </c>
+      <c r="E30" s="41">
+        <v>10</v>
+      </c>
+      <c r="F30" s="131">
+        <f t="shared" ref="F30:F36" si="4">D30*E30</f>
+        <v>2269.4656488549617</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="129">
+        <v>3</v>
+      </c>
+      <c r="B31" s="129">
+        <v>0</v>
+      </c>
+      <c r="C31" s="41" t="s">
+        <v>180</v>
+      </c>
+      <c r="D31" s="131">
+        <f t="shared" ref="D31:D36" si="5">$H$3*A31+B31</f>
+        <v>453.89312977099235</v>
+      </c>
+      <c r="E31" s="41">
+        <v>12</v>
+      </c>
+      <c r="F31" s="131">
+        <f t="shared" si="4"/>
+        <v>5446.7175572519081</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="129">
+        <v>3</v>
+      </c>
+      <c r="B32" s="129">
+        <v>30</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>182</v>
+      </c>
+      <c r="D32" s="131">
+        <f t="shared" si="5"/>
+        <v>483.89312977099235</v>
+      </c>
+      <c r="E32" s="41">
+        <v>1</v>
+      </c>
+      <c r="F32" s="131">
+        <f t="shared" si="4"/>
+        <v>483.89312977099235</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="129">
+        <v>2</v>
+      </c>
+      <c r="B33" s="129">
+        <v>0</v>
+      </c>
+      <c r="C33" s="130" t="s">
+        <v>183</v>
+      </c>
+      <c r="D33" s="131">
+        <f t="shared" si="5"/>
+        <v>302.59541984732823</v>
+      </c>
+      <c r="E33" s="41">
+        <v>3</v>
+      </c>
+      <c r="F33" s="131">
+        <f t="shared" si="4"/>
+        <v>907.78625954198469</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="129">
+        <v>1.5</v>
+      </c>
+      <c r="B34" s="129">
+        <v>40</v>
+      </c>
+      <c r="C34" s="130" t="s">
+        <v>181</v>
+      </c>
+      <c r="D34" s="131">
+        <f t="shared" si="5"/>
+        <v>266.94656488549617</v>
+      </c>
+      <c r="E34" s="41">
+        <v>1</v>
+      </c>
+      <c r="F34" s="131">
+        <f t="shared" si="4"/>
+        <v>266.94656488549617</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="129">
+        <v>4</v>
+      </c>
+      <c r="B35" s="129">
+        <v>0</v>
+      </c>
+      <c r="C35" s="130" t="s">
+        <v>184</v>
+      </c>
+      <c r="D35" s="131">
+        <f t="shared" si="5"/>
+        <v>605.19083969465646</v>
+      </c>
+      <c r="E35" s="41">
+        <v>1</v>
+      </c>
+      <c r="F35" s="131">
+        <f t="shared" si="4"/>
+        <v>605.19083969465646</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="129">
+        <v>4</v>
+      </c>
+      <c r="B36" s="129">
+        <v>20</v>
+      </c>
+      <c r="C36" s="130" t="s">
+        <v>185</v>
+      </c>
+      <c r="D36" s="131">
+        <f t="shared" si="5"/>
+        <v>625.19083969465646</v>
+      </c>
+      <c r="E36" s="41">
+        <v>1</v>
+      </c>
+      <c r="F36" s="131">
+        <f t="shared" si="4"/>
+        <v>625.19083969465646</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="128"/>
+      <c r="B37" s="128"/>
+      <c r="D37" s="57"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C38" s="99" t="s">
+        <v>188</v>
+      </c>
+      <c r="D38" s="57">
+        <f>SUM(D29:D36)</f>
+        <v>2878.2006543075245</v>
+      </c>
+      <c r="F38" s="57">
+        <f>SUM(F29:F36)</f>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="B40" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="C40" s="172" t="s">
+        <v>114</v>
+      </c>
+      <c r="D40" s="173" t="s">
+        <v>175</v>
+      </c>
+      <c r="E40" s="173" t="s">
+        <v>176</v>
+      </c>
+      <c r="F40" s="173" t="s">
+        <v>177</v>
+      </c>
+      <c r="H40" s="99" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="B41" s="58" t="s">
+        <v>173</v>
+      </c>
+      <c r="C41" s="172"/>
+      <c r="D41" s="173"/>
+      <c r="E41" s="173"/>
+      <c r="F41" s="173"/>
+      <c r="H41" s="99" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="129">
+        <v>1</v>
+      </c>
+      <c r="B42" s="129">
+        <v>0</v>
+      </c>
+      <c r="C42" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="D42" s="131">
+        <f>H42</f>
+        <v>-21.613958560523393</v>
+      </c>
+      <c r="E42" s="41">
+        <v>7</v>
+      </c>
+      <c r="F42" s="131">
+        <f>D42*E42</f>
+        <v>-151.29770992366375</v>
+      </c>
+      <c r="H42" s="132">
+        <v>-21.613958560523393</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="129">
+        <v>1.5</v>
+      </c>
+      <c r="B43" s="129">
+        <v>0</v>
+      </c>
+      <c r="C43" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="D43" s="131">
+        <f>$H$3*A43+B43</f>
+        <v>226.94656488549617</v>
+      </c>
+      <c r="E43" s="41">
+        <v>10</v>
+      </c>
+      <c r="F43" s="131">
+        <f t="shared" ref="F43:F49" si="6">D43*E43</f>
+        <v>2269.4656488549617</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="129">
+        <v>3</v>
+      </c>
+      <c r="B44" s="129">
+        <v>0</v>
+      </c>
+      <c r="C44" s="41" t="s">
+        <v>180</v>
+      </c>
+      <c r="D44" s="131">
+        <f t="shared" ref="D44:D49" si="7">$H$3*A44+B44</f>
+        <v>453.89312977099235</v>
+      </c>
+      <c r="E44" s="41">
+        <v>11</v>
+      </c>
+      <c r="F44" s="131">
+        <f t="shared" si="6"/>
+        <v>4992.8244274809158</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="129">
+        <v>3</v>
+      </c>
+      <c r="B45" s="129">
+        <v>30</v>
+      </c>
+      <c r="C45" s="41" t="s">
+        <v>182</v>
+      </c>
+      <c r="D45" s="131">
+        <f t="shared" si="7"/>
+        <v>483.89312977099235</v>
+      </c>
+      <c r="E45" s="41">
+        <v>1</v>
+      </c>
+      <c r="F45" s="131">
+        <f t="shared" si="6"/>
+        <v>483.89312977099235</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="129">
+        <v>2</v>
+      </c>
+      <c r="B46" s="129">
+        <v>0</v>
+      </c>
+      <c r="C46" s="130" t="s">
+        <v>183</v>
+      </c>
+      <c r="D46" s="131">
+        <f t="shared" si="7"/>
+        <v>302.59541984732823</v>
+      </c>
+      <c r="E46" s="41">
+        <v>3</v>
+      </c>
+      <c r="F46" s="131">
+        <f t="shared" si="6"/>
+        <v>907.78625954198469</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="129">
+        <v>1.5</v>
+      </c>
+      <c r="B47" s="129">
+        <v>40</v>
+      </c>
+      <c r="C47" s="130" t="s">
+        <v>181</v>
+      </c>
+      <c r="D47" s="131">
+        <f t="shared" si="7"/>
+        <v>266.94656488549617</v>
+      </c>
+      <c r="E47" s="41">
+        <v>1</v>
+      </c>
+      <c r="F47" s="131">
+        <f t="shared" si="6"/>
+        <v>266.94656488549617</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="129">
+        <v>4</v>
+      </c>
+      <c r="B48" s="129">
+        <v>0</v>
+      </c>
+      <c r="C48" s="130" t="s">
+        <v>184</v>
+      </c>
+      <c r="D48" s="131">
+        <f t="shared" si="7"/>
+        <v>605.19083969465646</v>
+      </c>
+      <c r="E48" s="41">
+        <v>1</v>
+      </c>
+      <c r="F48" s="131">
+        <f t="shared" si="6"/>
+        <v>605.19083969465646</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="129">
+        <v>4</v>
+      </c>
+      <c r="B49" s="129">
+        <v>20</v>
+      </c>
+      <c r="C49" s="130" t="s">
+        <v>185</v>
+      </c>
+      <c r="D49" s="131">
+        <f t="shared" si="7"/>
+        <v>625.19083969465646</v>
+      </c>
+      <c r="E49" s="41">
+        <v>1</v>
+      </c>
+      <c r="F49" s="131">
+        <f t="shared" si="6"/>
+        <v>625.19083969465646</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="128"/>
+      <c r="B50" s="128"/>
+      <c r="D50" s="57"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C51" s="99" t="s">
+        <v>188</v>
+      </c>
+      <c r="D51" s="57">
+        <f>SUM(D42:D49)</f>
+        <v>2943.0425299890949</v>
+      </c>
+      <c r="F51" s="57">
+        <f>SUM(F42:F49)</f>
+        <v>10000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="L3:L5"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="L12:L14"/>
+    <mergeCell ref="O3:O5"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="O12:O14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -16117,15 +18594,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="139" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
@@ -16367,13 +18844,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="140" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -16551,22 +19028,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="72">
+      <c r="A1" s="143">
         <f ca="1">TODAY()</f>
-        <v>46149</v>
-      </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
+        <v>46174</v>
+      </c>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
+      <c r="K1" s="143"/>
+      <c r="L1" s="143"/>
+      <c r="M1" s="143"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
@@ -16640,207 +19117,212 @@
       <c r="M4" s="35"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="140" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="71"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="73">
+      <c r="B5" s="140"/>
+      <c r="C5" s="140"/>
+      <c r="D5" s="140"/>
+      <c r="E5" s="140"/>
+      <c r="F5" s="140"/>
+      <c r="G5" s="140"/>
+      <c r="H5" s="140"/>
+      <c r="I5" s="140"/>
+      <c r="J5" s="140"/>
+      <c r="K5" s="141">
         <f>COUNT(A3:M3)</f>
         <v>13</v>
       </c>
-      <c r="L5" s="73"/>
-      <c r="M5" s="73"/>
+      <c r="L5" s="141"/>
+      <c r="M5" s="141"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="71" t="s">
+      <c r="A6" s="140" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="73">
+      <c r="B6" s="140"/>
+      <c r="C6" s="140"/>
+      <c r="D6" s="140"/>
+      <c r="E6" s="140"/>
+      <c r="F6" s="140"/>
+      <c r="G6" s="140"/>
+      <c r="H6" s="140"/>
+      <c r="I6" s="140"/>
+      <c r="J6" s="140"/>
+      <c r="K6" s="141">
         <f>COUNTIF(A3:M3,"&gt;0")</f>
         <v>5</v>
       </c>
-      <c r="L6" s="73"/>
-      <c r="M6" s="73"/>
+      <c r="L6" s="141"/>
+      <c r="M6" s="141"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="140" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="71"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="71"/>
-      <c r="H7" s="71"/>
-      <c r="I7" s="71"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="73">
+      <c r="B7" s="140"/>
+      <c r="C7" s="140"/>
+      <c r="D7" s="140"/>
+      <c r="E7" s="140"/>
+      <c r="F7" s="140"/>
+      <c r="G7" s="140"/>
+      <c r="H7" s="140"/>
+      <c r="I7" s="140"/>
+      <c r="J7" s="140"/>
+      <c r="K7" s="141">
         <f>COUNTIF(A3:M3,"&lt;0")</f>
         <v>5</v>
       </c>
-      <c r="L7" s="73"/>
-      <c r="M7" s="73"/>
+      <c r="L7" s="141"/>
+      <c r="M7" s="141"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="140" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="71"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="71"/>
-      <c r="K8" s="73">
+      <c r="B8" s="140"/>
+      <c r="C8" s="140"/>
+      <c r="D8" s="140"/>
+      <c r="E8" s="140"/>
+      <c r="F8" s="140"/>
+      <c r="G8" s="140"/>
+      <c r="H8" s="140"/>
+      <c r="I8" s="140"/>
+      <c r="J8" s="140"/>
+      <c r="K8" s="141">
         <f>COUNTIF(A3:M3,"=0")</f>
         <v>3</v>
       </c>
-      <c r="L8" s="73"/>
-      <c r="M8" s="73"/>
+      <c r="L8" s="141"/>
+      <c r="M8" s="141"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="140" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="71"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="71"/>
-      <c r="K9" s="73">
+      <c r="B9" s="140"/>
+      <c r="C9" s="140"/>
+      <c r="D9" s="140"/>
+      <c r="E9" s="140"/>
+      <c r="F9" s="140"/>
+      <c r="G9" s="140"/>
+      <c r="H9" s="140"/>
+      <c r="I9" s="140"/>
+      <c r="J9" s="140"/>
+      <c r="K9" s="141">
         <f>MAX(A3:M3)</f>
         <v>30</v>
       </c>
-      <c r="L9" s="73"/>
-      <c r="M9" s="73"/>
+      <c r="L9" s="141"/>
+      <c r="M9" s="141"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="71" t="s">
+      <c r="A10" s="140" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="71"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="71"/>
-      <c r="I10" s="71"/>
-      <c r="J10" s="71"/>
-      <c r="K10" s="73">
+      <c r="B10" s="140"/>
+      <c r="C10" s="140"/>
+      <c r="D10" s="140"/>
+      <c r="E10" s="140"/>
+      <c r="F10" s="140"/>
+      <c r="G10" s="140"/>
+      <c r="H10" s="140"/>
+      <c r="I10" s="140"/>
+      <c r="J10" s="140"/>
+      <c r="K10" s="141">
         <f>MIN(A3:M3)</f>
         <v>-82</v>
       </c>
-      <c r="L10" s="73"/>
-      <c r="M10" s="73"/>
+      <c r="L10" s="141"/>
+      <c r="M10" s="141"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="71" t="s">
+      <c r="A11" s="140" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="71"/>
-      <c r="K11" s="74">
+      <c r="B11" s="140"/>
+      <c r="C11" s="140"/>
+      <c r="D11" s="140"/>
+      <c r="E11" s="140"/>
+      <c r="F11" s="140"/>
+      <c r="G11" s="140"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="140"/>
+      <c r="K11" s="142">
         <f>AVERAGE(A3:M3)</f>
         <v>-10.23076923076923</v>
       </c>
-      <c r="L11" s="74"/>
-      <c r="M11" s="74"/>
+      <c r="L11" s="142"/>
+      <c r="M11" s="142"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="71" t="s">
+      <c r="A12" s="140" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="71"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="71"/>
-      <c r="I12" s="71"/>
-      <c r="J12" s="71"/>
-      <c r="K12" s="73">
+      <c r="B12" s="140"/>
+      <c r="C12" s="140"/>
+      <c r="D12" s="140"/>
+      <c r="E12" s="140"/>
+      <c r="F12" s="140"/>
+      <c r="G12" s="140"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="140"/>
+      <c r="K12" s="141">
         <f>SUM(A3:M3)</f>
         <v>-133</v>
       </c>
-      <c r="L12" s="73"/>
-      <c r="M12" s="73"/>
+      <c r="L12" s="141"/>
+      <c r="M12" s="141"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="71" t="s">
+      <c r="A13" s="140" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="71"/>
-      <c r="K13" s="73">
+      <c r="B13" s="140"/>
+      <c r="C13" s="140"/>
+      <c r="D13" s="140"/>
+      <c r="E13" s="140"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="140"/>
+      <c r="J13" s="140"/>
+      <c r="K13" s="141">
         <f>SUMIF(A3:M3,"&gt;0")</f>
         <v>110</v>
       </c>
-      <c r="L13" s="73"/>
-      <c r="M13" s="73"/>
+      <c r="L13" s="141"/>
+      <c r="M13" s="141"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="71" t="s">
+      <c r="A14" s="140" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="73">
+      <c r="B14" s="140"/>
+      <c r="C14" s="140"/>
+      <c r="D14" s="140"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="140"/>
+      <c r="G14" s="140"/>
+      <c r="H14" s="140"/>
+      <c r="I14" s="140"/>
+      <c r="J14" s="140"/>
+      <c r="K14" s="141">
         <f>SUMIF(A3:M3,"&lt;0")</f>
         <v>-243</v>
       </c>
-      <c r="L14" s="73"/>
-      <c r="M14" s="73"/>
+      <c r="L14" s="141"/>
+      <c r="M14" s="141"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="K8:M8"/>
     <mergeCell ref="K14:M14"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A6:J6"/>
@@ -16857,11 +19339,6 @@
     <mergeCell ref="K11:M11"/>
     <mergeCell ref="K12:M12"/>
     <mergeCell ref="K13:M13"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="K8:M8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -16901,12 +19378,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -17063,12 +19540,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -17223,13 +19700,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="140" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
